--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/insightsgraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806D13F0-3BD1-4B45-95ED-2C11A83CE7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26ADAEA-E6D5-2A4E-A8DA-DC25201B4735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sweets" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Master!$A$1:$P$468</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Master!$A$1:$P$486</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8794" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9407" uniqueCount="1042">
   <si>
     <t>Customer Name</t>
   </si>
@@ -3071,13 +3071,106 @@
   </si>
   <si>
     <t>He ordered it for his kids</t>
+  </si>
+  <si>
+    <t>Priyanka Chaudhari</t>
+  </si>
+  <si>
+    <t>Simi goyal</t>
+  </si>
+  <si>
+    <t>syeda lubna</t>
+  </si>
+  <si>
+    <t>Bindusree </t>
+  </si>
+  <si>
+    <t>Divya ameta</t>
+  </si>
+  <si>
+    <t>Jayanthiganesh -</t>
+  </si>
+  <si>
+    <t>Ibapdianghun khongwir</t>
+  </si>
+  <si>
+    <t>Kapil New Diver</t>
+  </si>
+  <si>
+    <t>Murli Banjara</t>
+  </si>
+  <si>
+    <t>Abhinash patro</t>
+  </si>
+  <si>
+    <t>MADAKA SHIVA KUMARI</t>
+  </si>
+  <si>
+    <t>Sumit Bhaskar</t>
+  </si>
+  <si>
+    <t>Kind of a chatpata snack</t>
+  </si>
+  <si>
+    <t>Guilt free snack</t>
+  </si>
+  <si>
+    <t>In the evening as snack</t>
+  </si>
+  <si>
+    <t>When I'm bored, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>He found this at the best price</t>
+  </si>
+  <si>
+    <t>Snack</t>
+  </si>
+  <si>
+    <t>Jagrit kashyap</t>
+  </si>
+  <si>
+    <t>Prasanna n</t>
+  </si>
+  <si>
+    <t>Shubham agarwal</t>
+  </si>
+  <si>
+    <t>Rajiv Taneja</t>
+  </si>
+  <si>
+    <t>Gautam kumar</t>
+  </si>
+  <si>
+    <t>Nishant Sehgal</t>
+  </si>
+  <si>
+    <t>Veena sethi</t>
+  </si>
+  <si>
+    <t>To curb my sweet cravings, Festivals</t>
+  </si>
+  <si>
+    <t>Prefers whatever's convenient, Sri Gopal krishna sweet house</t>
+  </si>
+  <si>
+    <t>Kanti Sweets</t>
+  </si>
+  <si>
+    <t>Haldiram's, Kanti Sweets, Prefers whatever's convenient</t>
+  </si>
+  <si>
+    <t>Haldiram's, GODESi</t>
+  </si>
+  <si>
+    <t>Oh My Millets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3122,6 +3215,11 @@
       <name val="Roboto"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3149,7 +3247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3173,6 +3271,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -30644,7 +30743,7 @@
         <v>194</v>
       </c>
       <c r="O456" s="5" t="s">
-        <v>260</v>
+        <v>92</v>
       </c>
       <c r="P456" s="5" t="s">
         <v>260</v>
@@ -30704,7 +30803,7 @@
         <v>963</v>
       </c>
       <c r="O457" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P457" s="5" t="s">
         <v>262</v>
@@ -30764,7 +30863,7 @@
         <v>963</v>
       </c>
       <c r="O458" s="5" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
       <c r="P458" s="5" t="s">
         <v>262</v>
@@ -30824,7 +30923,7 @@
         <v>963</v>
       </c>
       <c r="O459" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="P459" s="5" t="s">
         <v>266</v>
@@ -30884,7 +30983,7 @@
         <v>963</v>
       </c>
       <c r="O460" s="5" t="s">
-        <v>983</v>
+        <v>162</v>
       </c>
       <c r="P460" s="5" t="s">
         <v>983</v>
@@ -30944,7 +31043,7 @@
         <v>963</v>
       </c>
       <c r="O461" s="5" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P461" s="5" t="s">
         <v>265</v>
@@ -31004,7 +31103,7 @@
         <v>194</v>
       </c>
       <c r="O462" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P462" s="5" t="s">
         <v>262</v>
@@ -31064,7 +31163,7 @@
         <v>963</v>
       </c>
       <c r="O463" s="5" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P463" s="5" t="s">
         <v>265</v>
@@ -31124,7 +31223,7 @@
         <v>963</v>
       </c>
       <c r="O464" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P464" s="5" t="s">
         <v>262</v>
@@ -31184,7 +31283,7 @@
         <v>641</v>
       </c>
       <c r="O465" s="5" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="P465" s="5" t="s">
         <v>267</v>
@@ -31244,7 +31343,7 @@
         <v>242</v>
       </c>
       <c r="O466" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="P466" s="5" t="s">
         <v>266</v>
@@ -31304,7 +31403,7 @@
         <v>963</v>
       </c>
       <c r="O467" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="P467" s="5" t="s">
         <v>266</v>
@@ -31320,65 +31419,65 @@
       <c r="Y467" s="2"/>
       <c r="Z467" s="2"/>
     </row>
-    <row r="468" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A468" s="5" t="s">
+    <row r="468" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A468" s="10" t="s">
         <v>982</v>
       </c>
-      <c r="B468" s="5" t="s">
+      <c r="B468" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C468" s="5" t="s">
+      <c r="C468" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D468" s="5" t="s">
+      <c r="D468" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E468" s="2" t="s">
+      <c r="E468" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F468" s="5" t="s">
+      <c r="F468" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="G468" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H468" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I468" s="2" t="s">
+      <c r="G468" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H468" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I468" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J468" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K468" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L468" s="5" t="s">
+      <c r="J468" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K468" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L468" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="M468" s="5" t="s">
+      <c r="M468" s="10" t="s">
         <v>987</v>
       </c>
-      <c r="N468" s="5" t="s">
+      <c r="N468" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="O468" s="5" t="s">
+      <c r="O468" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="P468" s="5" t="s">
+      <c r="P468" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="Q468" s="2"/>
-      <c r="R468" s="2"/>
-      <c r="S468" s="2"/>
-      <c r="T468" s="2"/>
-      <c r="U468" s="2"/>
-      <c r="V468" s="2"/>
-      <c r="W468" s="2"/>
-      <c r="X468" s="2"/>
-      <c r="Y468" s="2"/>
-      <c r="Z468" s="2"/>
+      <c r="Q468" s="8"/>
+      <c r="R468" s="8"/>
+      <c r="S468" s="8"/>
+      <c r="T468" s="8"/>
+      <c r="U468" s="8"/>
+      <c r="V468" s="8"/>
+      <c r="W468" s="8"/>
+      <c r="X468" s="8"/>
+      <c r="Y468" s="8"/>
+      <c r="Z468" s="8"/>
     </row>
     <row r="469" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A469" s="5" t="s">
@@ -32380,83 +32479,115 @@
       <c r="Y485" s="2"/>
       <c r="Z485" s="2"/>
     </row>
-    <row r="486" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A486" s="5" t="s">
+    <row r="486" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A486" s="10" t="s">
         <v>1004</v>
       </c>
-      <c r="B486" s="5" t="s">
+      <c r="B486" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C486" s="5" t="s">
+      <c r="C486" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D486" s="5" t="s">
+      <c r="D486" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E486" s="2" t="s">
+      <c r="E486" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F486" s="5" t="s">
+      <c r="F486" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="G486" s="5" t="s">
+      <c r="G486" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="H486" s="5" t="s">
+      <c r="H486" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="I486" s="5" t="s">
+      <c r="I486" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="J486" s="5" t="s">
+      <c r="J486" s="10" t="s">
         <v>1010</v>
       </c>
-      <c r="K486" s="5" t="s">
+      <c r="K486" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L486" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M486" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N486" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O486" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P486" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q486" s="2"/>
-      <c r="R486" s="2"/>
-      <c r="S486" s="2"/>
-      <c r="T486" s="2"/>
-      <c r="U486" s="2"/>
-      <c r="V486" s="2"/>
-      <c r="W486" s="2"/>
-      <c r="X486" s="2"/>
-      <c r="Y486" s="2"/>
-      <c r="Z486" s="2"/>
+      <c r="L486" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M486" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N486" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O486" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P486" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q486" s="8"/>
+      <c r="R486" s="8"/>
+      <c r="S486" s="8"/>
+      <c r="T486" s="8"/>
+      <c r="U486" s="8"/>
+      <c r="V486" s="8"/>
+      <c r="W486" s="8"/>
+      <c r="X486" s="8"/>
+      <c r="Y486" s="8"/>
+      <c r="Z486" s="8"/>
     </row>
     <row r="487" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A487" s="2"/>
-      <c r="B487" s="2"/>
-      <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
-      <c r="E487" s="2"/>
-      <c r="F487" s="2"/>
-      <c r="G487" s="2"/>
-      <c r="H487" s="2"/>
-      <c r="I487" s="2"/>
-      <c r="J487" s="2"/>
-      <c r="K487" s="2"/>
-      <c r="L487" s="2"/>
-      <c r="M487" s="2"/>
-      <c r="N487" s="2"/>
-      <c r="O487" s="2"/>
-      <c r="P487" s="2"/>
+      <c r="A487" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="B487" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D487" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E487" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F487" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G487" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H487" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I487" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J487" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K487" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L487" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M487" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N487" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O487" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P487" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q487" s="2"/>
       <c r="R487" s="2"/>
       <c r="S487" s="2"/>
@@ -32469,22 +32600,54 @@
       <c r="Z487" s="2"/>
     </row>
     <row r="488" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A488" s="2"/>
-      <c r="B488" s="2"/>
-      <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
-      <c r="E488" s="2"/>
-      <c r="F488" s="2"/>
-      <c r="G488" s="2"/>
-      <c r="H488" s="2"/>
-      <c r="I488" s="2"/>
-      <c r="J488" s="2"/>
-      <c r="K488" s="2"/>
-      <c r="L488" s="2"/>
-      <c r="M488" s="2"/>
-      <c r="N488" s="2"/>
-      <c r="O488" s="2"/>
-      <c r="P488" s="2"/>
+      <c r="A488" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C488" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D488" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E488" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F488" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G488" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H488" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="I488" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J488" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K488" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L488" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M488" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N488" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O488" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P488" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q488" s="2"/>
       <c r="R488" s="2"/>
       <c r="S488" s="2"/>
@@ -32497,22 +32660,48 @@
       <c r="Z488" s="2"/>
     </row>
     <row r="489" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A489" s="2"/>
-      <c r="B489" s="2"/>
-      <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
-      <c r="E489" s="2"/>
-      <c r="F489" s="2"/>
-      <c r="G489" s="2"/>
-      <c r="H489" s="2"/>
-      <c r="I489" s="2"/>
-      <c r="J489" s="2"/>
-      <c r="K489" s="2"/>
-      <c r="L489" s="2"/>
-      <c r="M489" s="2"/>
-      <c r="N489" s="2"/>
-      <c r="O489" s="2"/>
-      <c r="P489" s="2"/>
+      <c r="A489" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="B489" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D489" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E489" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F489" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G489" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H489" s="6"/>
+      <c r="I489" s="6"/>
+      <c r="J489" s="6"/>
+      <c r="K489" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L489" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M489" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N489" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O489" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P489" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q489" s="2"/>
       <c r="R489" s="2"/>
       <c r="S489" s="2"/>
@@ -32525,22 +32714,54 @@
       <c r="Z489" s="2"/>
     </row>
     <row r="490" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A490" s="2"/>
-      <c r="B490" s="2"/>
-      <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
-      <c r="E490" s="2"/>
-      <c r="F490" s="2"/>
-      <c r="G490" s="2"/>
-      <c r="H490" s="2"/>
-      <c r="I490" s="2"/>
-      <c r="J490" s="2"/>
-      <c r="K490" s="2"/>
-      <c r="L490" s="2"/>
-      <c r="M490" s="2"/>
-      <c r="N490" s="2"/>
-      <c r="O490" s="2"/>
-      <c r="P490" s="2"/>
+      <c r="A490" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="B490" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D490" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F490" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G490" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H490" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I490" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J490" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K490" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L490" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M490" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N490" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O490" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P490" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q490" s="2"/>
       <c r="R490" s="2"/>
       <c r="S490" s="2"/>
@@ -32553,22 +32774,54 @@
       <c r="Z490" s="2"/>
     </row>
     <row r="491" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A491" s="2"/>
-      <c r="B491" s="2"/>
-      <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
-      <c r="E491" s="2"/>
-      <c r="F491" s="2"/>
-      <c r="G491" s="2"/>
-      <c r="H491" s="2"/>
-      <c r="I491" s="2"/>
-      <c r="J491" s="2"/>
-      <c r="K491" s="2"/>
-      <c r="L491" s="2"/>
-      <c r="M491" s="2"/>
-      <c r="N491" s="2"/>
-      <c r="O491" s="2"/>
-      <c r="P491" s="2"/>
+      <c r="A491" s="5" t="s">
+        <v>992</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D491" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E491" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F491" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G491" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H491" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I491" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J491" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K491" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L491" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M491" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N491" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O491" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P491" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q491" s="2"/>
       <c r="R491" s="2"/>
       <c r="S491" s="2"/>
@@ -32581,22 +32834,54 @@
       <c r="Z491" s="2"/>
     </row>
     <row r="492" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A492" s="2"/>
-      <c r="B492" s="2"/>
-      <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
-      <c r="E492" s="2"/>
-      <c r="F492" s="2"/>
-      <c r="G492" s="2"/>
-      <c r="H492" s="2"/>
-      <c r="I492" s="2"/>
-      <c r="J492" s="2"/>
-      <c r="K492" s="2"/>
-      <c r="L492" s="2"/>
-      <c r="M492" s="2"/>
-      <c r="N492" s="2"/>
-      <c r="O492" s="2"/>
-      <c r="P492" s="2"/>
+      <c r="A492" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D492" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E492" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F492" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G492" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H492" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I492" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J492" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K492" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L492" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M492" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N492" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O492" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P492" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q492" s="2"/>
       <c r="R492" s="2"/>
       <c r="S492" s="2"/>
@@ -32609,22 +32894,48 @@
       <c r="Z492" s="2"/>
     </row>
     <row r="493" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A493" s="2"/>
-      <c r="B493" s="2"/>
-      <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
-      <c r="E493" s="2"/>
-      <c r="F493" s="2"/>
-      <c r="G493" s="2"/>
-      <c r="H493" s="2"/>
-      <c r="I493" s="2"/>
-      <c r="J493" s="2"/>
-      <c r="K493" s="2"/>
-      <c r="L493" s="2"/>
-      <c r="M493" s="2"/>
-      <c r="N493" s="2"/>
-      <c r="O493" s="2"/>
-      <c r="P493" s="2"/>
+      <c r="A493" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="B493" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D493" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E493" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F493" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G493" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H493" s="6"/>
+      <c r="I493" s="6"/>
+      <c r="J493" s="6"/>
+      <c r="K493" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L493" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M493" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N493" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O493" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P493" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q493" s="2"/>
       <c r="R493" s="2"/>
       <c r="S493" s="2"/>
@@ -32637,22 +32948,52 @@
       <c r="Z493" s="2"/>
     </row>
     <row r="494" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A494" s="2"/>
-      <c r="B494" s="2"/>
-      <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
-      <c r="E494" s="2"/>
-      <c r="F494" s="2"/>
-      <c r="G494" s="2"/>
-      <c r="H494" s="2"/>
-      <c r="I494" s="2"/>
-      <c r="J494" s="2"/>
-      <c r="K494" s="2"/>
-      <c r="L494" s="2"/>
-      <c r="M494" s="2"/>
-      <c r="N494" s="2"/>
-      <c r="O494" s="2"/>
-      <c r="P494" s="2"/>
+      <c r="A494" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D494" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E494" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F494" s="6"/>
+      <c r="G494" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H494" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I494" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J494" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K494" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L494" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M494" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N494" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O494" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P494" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q494" s="2"/>
       <c r="R494" s="2"/>
       <c r="S494" s="2"/>
@@ -32665,22 +33006,54 @@
       <c r="Z494" s="2"/>
     </row>
     <row r="495" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A495" s="2"/>
-      <c r="B495" s="2"/>
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
-      <c r="F495" s="2"/>
-      <c r="G495" s="2"/>
-      <c r="H495" s="2"/>
-      <c r="I495" s="2"/>
-      <c r="J495" s="2"/>
-      <c r="K495" s="2"/>
-      <c r="L495" s="2"/>
-      <c r="M495" s="2"/>
-      <c r="N495" s="2"/>
-      <c r="O495" s="2"/>
-      <c r="P495" s="2"/>
+      <c r="A495" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D495" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E495" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F495" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G495" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H495" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I495" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J495" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="K495" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L495" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M495" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N495" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O495" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P495" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q495" s="2"/>
       <c r="R495" s="2"/>
       <c r="S495" s="2"/>
@@ -32693,22 +33066,54 @@
       <c r="Z495" s="2"/>
     </row>
     <row r="496" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A496" s="2"/>
-      <c r="B496" s="2"/>
-      <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
-      <c r="E496" s="2"/>
-      <c r="F496" s="2"/>
-      <c r="G496" s="2"/>
-      <c r="H496" s="2"/>
-      <c r="I496" s="2"/>
-      <c r="J496" s="2"/>
-      <c r="K496" s="2"/>
-      <c r="L496" s="2"/>
-      <c r="M496" s="2"/>
-      <c r="N496" s="2"/>
-      <c r="O496" s="2"/>
-      <c r="P496" s="2"/>
+      <c r="A496" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D496" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F496" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G496" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H496" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I496" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J496" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K496" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L496" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M496" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N496" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O496" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P496" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q496" s="2"/>
       <c r="R496" s="2"/>
       <c r="S496" s="2"/>
@@ -32721,22 +33126,54 @@
       <c r="Z496" s="2"/>
     </row>
     <row r="497" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A497" s="2"/>
-      <c r="B497" s="2"/>
-      <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
-      <c r="E497" s="2"/>
-      <c r="F497" s="2"/>
-      <c r="G497" s="2"/>
-      <c r="H497" s="2"/>
-      <c r="I497" s="2"/>
-      <c r="J497" s="2"/>
-      <c r="K497" s="2"/>
-      <c r="L497" s="2"/>
-      <c r="M497" s="2"/>
-      <c r="N497" s="2"/>
-      <c r="O497" s="2"/>
-      <c r="P497" s="2"/>
+      <c r="A497" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D497" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F497" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G497" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H497" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I497" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J497" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="K497" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L497" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M497" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N497" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O497" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P497" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q497" s="2"/>
       <c r="R497" s="2"/>
       <c r="S497" s="2"/>
@@ -32749,22 +33186,54 @@
       <c r="Z497" s="2"/>
     </row>
     <row r="498" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A498" s="2"/>
-      <c r="B498" s="2"/>
-      <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
-      <c r="E498" s="2"/>
-      <c r="F498" s="2"/>
-      <c r="G498" s="2"/>
-      <c r="H498" s="2"/>
-      <c r="I498" s="2"/>
-      <c r="J498" s="2"/>
-      <c r="K498" s="2"/>
-      <c r="L498" s="2"/>
-      <c r="M498" s="2"/>
-      <c r="N498" s="2"/>
-      <c r="O498" s="2"/>
-      <c r="P498" s="2"/>
+      <c r="A498" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D498" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E498" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F498" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G498" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H498" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="I498" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J498" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K498" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L498" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M498" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N498" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O498" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P498" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q498" s="2"/>
       <c r="R498" s="2"/>
       <c r="S498" s="2"/>
@@ -32777,22 +33246,48 @@
       <c r="Z498" s="2"/>
     </row>
     <row r="499" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A499" s="2"/>
-      <c r="B499" s="2"/>
-      <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
-      <c r="E499" s="2"/>
-      <c r="F499" s="2"/>
-      <c r="G499" s="2"/>
-      <c r="H499" s="2"/>
-      <c r="I499" s="2"/>
-      <c r="J499" s="2"/>
-      <c r="K499" s="2"/>
-      <c r="L499" s="2"/>
-      <c r="M499" s="2"/>
-      <c r="N499" s="2"/>
-      <c r="O499" s="2"/>
-      <c r="P499" s="2"/>
+      <c r="A499" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D499" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E499" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F499" s="6"/>
+      <c r="G499" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H499" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I499" s="6"/>
+      <c r="J499" s="6"/>
+      <c r="K499" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L499" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M499" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N499" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O499" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P499" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q499" s="2"/>
       <c r="R499" s="2"/>
       <c r="S499" s="2"/>
@@ -32805,22 +33300,54 @@
       <c r="Z499" s="2"/>
     </row>
     <row r="500" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
-      <c r="E500" s="2"/>
-      <c r="F500" s="2"/>
-      <c r="G500" s="2"/>
-      <c r="H500" s="2"/>
-      <c r="I500" s="2"/>
-      <c r="J500" s="2"/>
-      <c r="K500" s="2"/>
-      <c r="L500" s="2"/>
-      <c r="M500" s="2"/>
-      <c r="N500" s="2"/>
-      <c r="O500" s="2"/>
-      <c r="P500" s="2"/>
+      <c r="A500" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D500" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E500" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F500" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G500" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H500" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I500" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J500" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K500" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L500" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M500" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N500" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O500" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P500" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q500" s="2"/>
       <c r="R500" s="2"/>
       <c r="S500" s="2"/>
@@ -32833,22 +33360,54 @@
       <c r="Z500" s="2"/>
     </row>
     <row r="501" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A501" s="2"/>
-      <c r="B501" s="2"/>
-      <c r="C501" s="2"/>
-      <c r="D501" s="2"/>
-      <c r="E501" s="2"/>
-      <c r="F501" s="2"/>
-      <c r="G501" s="2"/>
-      <c r="H501" s="2"/>
-      <c r="I501" s="2"/>
-      <c r="J501" s="2"/>
-      <c r="K501" s="2"/>
-      <c r="L501" s="2"/>
-      <c r="M501" s="2"/>
-      <c r="N501" s="2"/>
-      <c r="O501" s="2"/>
-      <c r="P501" s="2"/>
+      <c r="A501" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B501" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D501" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E501" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F501" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G501" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H501" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I501" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J501" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K501" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L501" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M501" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N501" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O501" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P501" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q501" s="2"/>
       <c r="R501" s="2"/>
       <c r="S501" s="2"/>
@@ -32861,22 +33420,54 @@
       <c r="Z501" s="2"/>
     </row>
     <row r="502" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A502" s="2"/>
-      <c r="B502" s="2"/>
-      <c r="C502" s="2"/>
-      <c r="D502" s="2"/>
-      <c r="E502" s="2"/>
-      <c r="F502" s="2"/>
-      <c r="G502" s="2"/>
-      <c r="H502" s="2"/>
-      <c r="I502" s="2"/>
-      <c r="J502" s="2"/>
-      <c r="K502" s="2"/>
-      <c r="L502" s="2"/>
-      <c r="M502" s="2"/>
-      <c r="N502" s="2"/>
-      <c r="O502" s="2"/>
-      <c r="P502" s="2"/>
+      <c r="A502" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D502" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E502" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F502" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G502" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H502" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I502" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J502" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K502" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L502" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M502" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N502" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O502" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P502" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q502" s="2"/>
       <c r="R502" s="2"/>
       <c r="S502" s="2"/>
@@ -32889,22 +33480,54 @@
       <c r="Z502" s="2"/>
     </row>
     <row r="503" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A503" s="2"/>
-      <c r="B503" s="2"/>
-      <c r="C503" s="2"/>
-      <c r="D503" s="2"/>
-      <c r="E503" s="2"/>
-      <c r="F503" s="2"/>
-      <c r="G503" s="2"/>
-      <c r="H503" s="2"/>
-      <c r="I503" s="2"/>
-      <c r="J503" s="2"/>
-      <c r="K503" s="2"/>
-      <c r="L503" s="2"/>
-      <c r="M503" s="2"/>
-      <c r="N503" s="2"/>
-      <c r="O503" s="2"/>
-      <c r="P503" s="2"/>
+      <c r="A503" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D503" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E503" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F503" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G503" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H503" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I503" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J503" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K503" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L503" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M503" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N503" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O503" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P503" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q503" s="2"/>
       <c r="R503" s="2"/>
       <c r="S503" s="2"/>
@@ -32917,22 +33540,54 @@
       <c r="Z503" s="2"/>
     </row>
     <row r="504" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A504" s="2"/>
-      <c r="B504" s="2"/>
-      <c r="C504" s="2"/>
-      <c r="D504" s="2"/>
-      <c r="E504" s="2"/>
-      <c r="F504" s="2"/>
-      <c r="G504" s="2"/>
-      <c r="H504" s="2"/>
-      <c r="I504" s="2"/>
-      <c r="J504" s="2"/>
-      <c r="K504" s="2"/>
-      <c r="L504" s="2"/>
-      <c r="M504" s="2"/>
-      <c r="N504" s="2"/>
-      <c r="O504" s="2"/>
-      <c r="P504" s="2"/>
+      <c r="A504" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D504" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E504" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F504" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G504" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H504" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I504" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J504" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K504" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L504" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M504" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N504" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O504" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P504" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q504" s="2"/>
       <c r="R504" s="2"/>
       <c r="S504" s="2"/>
@@ -32945,22 +33600,54 @@
       <c r="Z504" s="2"/>
     </row>
     <row r="505" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A505" s="2"/>
-      <c r="B505" s="2"/>
-      <c r="C505" s="2"/>
-      <c r="D505" s="2"/>
-      <c r="E505" s="2"/>
-      <c r="F505" s="2"/>
-      <c r="G505" s="2"/>
-      <c r="H505" s="2"/>
-      <c r="I505" s="2"/>
-      <c r="J505" s="2"/>
-      <c r="K505" s="2"/>
-      <c r="L505" s="2"/>
-      <c r="M505" s="2"/>
-      <c r="N505" s="2"/>
-      <c r="O505" s="2"/>
-      <c r="P505" s="2"/>
+      <c r="A505" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B505" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D505" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E505" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F505" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G505" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H505" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I505" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J505" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K505" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L505" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M505" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N505" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O505" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P505" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q505" s="2"/>
       <c r="R505" s="2"/>
       <c r="S505" s="2"/>
@@ -32973,22 +33660,54 @@
       <c r="Z505" s="2"/>
     </row>
     <row r="506" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A506" s="2"/>
-      <c r="B506" s="2"/>
-      <c r="C506" s="2"/>
-      <c r="D506" s="2"/>
-      <c r="E506" s="2"/>
-      <c r="F506" s="2"/>
-      <c r="G506" s="2"/>
-      <c r="H506" s="2"/>
-      <c r="I506" s="2"/>
-      <c r="J506" s="2"/>
-      <c r="K506" s="2"/>
-      <c r="L506" s="2"/>
-      <c r="M506" s="2"/>
-      <c r="N506" s="2"/>
-      <c r="O506" s="2"/>
-      <c r="P506" s="2"/>
+      <c r="A506" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D506" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E506" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F506" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G506" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H506" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="I506" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J506" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K506" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L506" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M506" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N506" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O506" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P506" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q506" s="2"/>
       <c r="R506" s="2"/>
       <c r="S506" s="2"/>
@@ -33001,22 +33720,54 @@
       <c r="Z506" s="2"/>
     </row>
     <row r="507" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A507" s="2"/>
-      <c r="B507" s="2"/>
-      <c r="C507" s="2"/>
-      <c r="D507" s="2"/>
-      <c r="E507" s="2"/>
-      <c r="F507" s="2"/>
-      <c r="G507" s="2"/>
-      <c r="H507" s="2"/>
-      <c r="I507" s="2"/>
-      <c r="J507" s="2"/>
-      <c r="K507" s="2"/>
-      <c r="L507" s="2"/>
-      <c r="M507" s="2"/>
-      <c r="N507" s="2"/>
-      <c r="O507" s="2"/>
-      <c r="P507" s="2"/>
+      <c r="A507" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D507" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E507" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F507" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G507" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H507" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I507" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J507" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="K507" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L507" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M507" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N507" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O507" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P507" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q507" s="2"/>
       <c r="R507" s="2"/>
       <c r="S507" s="2"/>
@@ -33029,22 +33780,54 @@
       <c r="Z507" s="2"/>
     </row>
     <row r="508" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A508" s="2"/>
-      <c r="B508" s="2"/>
-      <c r="C508" s="2"/>
-      <c r="D508" s="2"/>
-      <c r="E508" s="2"/>
-      <c r="F508" s="2"/>
-      <c r="G508" s="2"/>
-      <c r="H508" s="2"/>
-      <c r="I508" s="2"/>
-      <c r="J508" s="2"/>
-      <c r="K508" s="2"/>
-      <c r="L508" s="2"/>
-      <c r="M508" s="2"/>
-      <c r="N508" s="2"/>
-      <c r="O508" s="2"/>
-      <c r="P508" s="2"/>
+      <c r="A508" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D508" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E508" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F508" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G508" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H508" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I508" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J508" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="K508" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L508" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M508" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N508" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O508" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P508" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q508" s="2"/>
       <c r="R508" s="2"/>
       <c r="S508" s="2"/>
@@ -33057,22 +33840,54 @@
       <c r="Z508" s="2"/>
     </row>
     <row r="509" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A509" s="2"/>
-      <c r="B509" s="2"/>
-      <c r="C509" s="2"/>
-      <c r="D509" s="2"/>
-      <c r="E509" s="2"/>
-      <c r="F509" s="2"/>
-      <c r="G509" s="2"/>
-      <c r="H509" s="2"/>
-      <c r="I509" s="2"/>
-      <c r="J509" s="2"/>
-      <c r="K509" s="2"/>
-      <c r="L509" s="2"/>
-      <c r="M509" s="2"/>
-      <c r="N509" s="2"/>
-      <c r="O509" s="2"/>
-      <c r="P509" s="2"/>
+      <c r="A509" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D509" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E509" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F509" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G509" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H509" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="I509" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J509" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="K509" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L509" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M509" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N509" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O509" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P509" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q509" s="2"/>
       <c r="R509" s="2"/>
       <c r="S509" s="2"/>
@@ -33085,22 +33900,54 @@
       <c r="Z509" s="2"/>
     </row>
     <row r="510" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A510" s="2"/>
-      <c r="B510" s="2"/>
-      <c r="C510" s="2"/>
-      <c r="D510" s="2"/>
-      <c r="E510" s="2"/>
-      <c r="F510" s="2"/>
-      <c r="G510" s="2"/>
-      <c r="H510" s="2"/>
-      <c r="I510" s="2"/>
-      <c r="J510" s="2"/>
-      <c r="K510" s="2"/>
-      <c r="L510" s="2"/>
-      <c r="M510" s="2"/>
-      <c r="N510" s="2"/>
-      <c r="O510" s="2"/>
-      <c r="P510" s="2"/>
+      <c r="A510" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B510" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C510" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D510" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E510" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F510" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G510" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H510" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I510" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J510" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K510" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L510" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M510" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N510" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O510" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P510" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q510" s="2"/>
       <c r="R510" s="2"/>
       <c r="S510" s="2"/>
@@ -33113,22 +33960,54 @@
       <c r="Z510" s="2"/>
     </row>
     <row r="511" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A511" s="2"/>
-      <c r="B511" s="2"/>
-      <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
-      <c r="E511" s="2"/>
-      <c r="F511" s="2"/>
-      <c r="G511" s="2"/>
-      <c r="H511" s="2"/>
-      <c r="I511" s="2"/>
-      <c r="J511" s="2"/>
-      <c r="K511" s="2"/>
-      <c r="L511" s="2"/>
-      <c r="M511" s="2"/>
-      <c r="N511" s="2"/>
-      <c r="O511" s="2"/>
-      <c r="P511" s="2"/>
+      <c r="A511" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D511" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E511" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F511" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G511" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H511" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I511" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J511" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="K511" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L511" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M511" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N511" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O511" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P511" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q511" s="2"/>
       <c r="R511" s="2"/>
       <c r="S511" s="2"/>
@@ -33141,22 +34020,54 @@
       <c r="Z511" s="2"/>
     </row>
     <row r="512" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A512" s="2"/>
-      <c r="B512" s="2"/>
-      <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
-      <c r="E512" s="2"/>
-      <c r="F512" s="2"/>
-      <c r="G512" s="2"/>
-      <c r="H512" s="2"/>
-      <c r="I512" s="2"/>
-      <c r="J512" s="2"/>
-      <c r="K512" s="2"/>
-      <c r="L512" s="2"/>
-      <c r="M512" s="2"/>
-      <c r="N512" s="2"/>
-      <c r="O512" s="2"/>
-      <c r="P512" s="2"/>
+      <c r="A512" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B512" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D512" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E512" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F512" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G512" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H512" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I512" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J512" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="K512" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L512" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M512" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N512" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O512" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P512" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q512" s="2"/>
       <c r="R512" s="2"/>
       <c r="S512" s="2"/>
@@ -33169,22 +34080,54 @@
       <c r="Z512" s="2"/>
     </row>
     <row r="513" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A513" s="2"/>
-      <c r="B513" s="2"/>
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
-      <c r="E513" s="2"/>
-      <c r="F513" s="2"/>
-      <c r="G513" s="2"/>
-      <c r="H513" s="2"/>
-      <c r="I513" s="2"/>
-      <c r="J513" s="2"/>
-      <c r="K513" s="2"/>
-      <c r="L513" s="2"/>
-      <c r="M513" s="2"/>
-      <c r="N513" s="2"/>
-      <c r="O513" s="2"/>
-      <c r="P513" s="2"/>
+      <c r="A513" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D513" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E513" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F513" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G513" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H513" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I513" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J513" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K513" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L513" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M513" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N513" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O513" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P513" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q513" s="2"/>
       <c r="R513" s="2"/>
       <c r="S513" s="2"/>
@@ -33197,22 +34140,54 @@
       <c r="Z513" s="2"/>
     </row>
     <row r="514" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A514" s="2"/>
-      <c r="B514" s="2"/>
-      <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
-      <c r="E514" s="2"/>
-      <c r="F514" s="2"/>
-      <c r="G514" s="2"/>
-      <c r="H514" s="2"/>
-      <c r="I514" s="2"/>
-      <c r="J514" s="2"/>
-      <c r="K514" s="2"/>
-      <c r="L514" s="2"/>
-      <c r="M514" s="2"/>
-      <c r="N514" s="2"/>
-      <c r="O514" s="2"/>
-      <c r="P514" s="2"/>
+      <c r="A514" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B514" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D514" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F514" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G514" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H514" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I514" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J514" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K514" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L514" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M514" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N514" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O514" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P514" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q514" s="2"/>
       <c r="R514" s="2"/>
       <c r="S514" s="2"/>
@@ -33225,22 +34200,54 @@
       <c r="Z514" s="2"/>
     </row>
     <row r="515" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A515" s="2"/>
-      <c r="B515" s="2"/>
-      <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
-      <c r="E515" s="2"/>
-      <c r="F515" s="2"/>
-      <c r="G515" s="2"/>
-      <c r="H515" s="2"/>
-      <c r="I515" s="2"/>
-      <c r="J515" s="2"/>
-      <c r="K515" s="2"/>
-      <c r="L515" s="2"/>
-      <c r="M515" s="2"/>
-      <c r="N515" s="2"/>
-      <c r="O515" s="2"/>
-      <c r="P515" s="2"/>
+      <c r="A515" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B515" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D515" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F515" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G515" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H515" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I515" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J515" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="K515" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L515" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M515" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N515" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O515" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P515" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q515" s="2"/>
       <c r="R515" s="2"/>
       <c r="S515" s="2"/>
@@ -33252,51 +34259,115 @@
       <c r="Y515" s="2"/>
       <c r="Z515" s="2"/>
     </row>
-    <row r="516" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A516" s="2"/>
-      <c r="B516" s="2"/>
-      <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
-      <c r="E516" s="2"/>
-      <c r="F516" s="2"/>
-      <c r="G516" s="2"/>
-      <c r="H516" s="2"/>
-      <c r="I516" s="2"/>
-      <c r="J516" s="2"/>
-      <c r="K516" s="2"/>
-      <c r="L516" s="2"/>
-      <c r="M516" s="2"/>
-      <c r="N516" s="2"/>
-      <c r="O516" s="2"/>
-      <c r="P516" s="2"/>
-      <c r="Q516" s="2"/>
-      <c r="R516" s="2"/>
-      <c r="S516" s="2"/>
-      <c r="T516" s="2"/>
-      <c r="U516" s="2"/>
-      <c r="V516" s="2"/>
-      <c r="W516" s="2"/>
-      <c r="X516" s="2"/>
-      <c r="Y516" s="2"/>
-      <c r="Z516" s="2"/>
+    <row r="516" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A516" s="10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B516" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C516" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D516" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E516" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F516" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G516" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="H516" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I516" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J516" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K516" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L516" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M516" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N516" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O516" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P516" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q516" s="8"/>
+      <c r="R516" s="8"/>
+      <c r="S516" s="8"/>
+      <c r="T516" s="8"/>
+      <c r="U516" s="8"/>
+      <c r="V516" s="8"/>
+      <c r="W516" s="8"/>
+      <c r="X516" s="8"/>
+      <c r="Y516" s="8"/>
+      <c r="Z516" s="8"/>
     </row>
     <row r="517" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A517" s="2"/>
-      <c r="B517" s="2"/>
-      <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
-      <c r="E517" s="2"/>
-      <c r="F517" s="2"/>
-      <c r="G517" s="2"/>
-      <c r="H517" s="2"/>
-      <c r="I517" s="2"/>
-      <c r="J517" s="2"/>
-      <c r="K517" s="2"/>
-      <c r="L517" s="2"/>
-      <c r="M517" s="2"/>
-      <c r="N517" s="2"/>
-      <c r="O517" s="2"/>
-      <c r="P517" s="2"/>
+      <c r="A517" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="B517" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D517" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F517" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H517" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I517" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K517" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L517" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M517" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="N517" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O517" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P517" s="5" t="s">
+        <v>474</v>
+      </c>
       <c r="Q517" s="2"/>
       <c r="R517" s="2"/>
       <c r="S517" s="2"/>
@@ -33309,22 +34380,54 @@
       <c r="Z517" s="2"/>
     </row>
     <row r="518" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A518" s="2"/>
-      <c r="B518" s="2"/>
-      <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
-      <c r="E518" s="2"/>
-      <c r="F518" s="2"/>
-      <c r="G518" s="2"/>
-      <c r="H518" s="2"/>
-      <c r="I518" s="2"/>
-      <c r="J518" s="2"/>
-      <c r="K518" s="2"/>
-      <c r="L518" s="2"/>
-      <c r="M518" s="2"/>
-      <c r="N518" s="2"/>
-      <c r="O518" s="2"/>
-      <c r="P518" s="2"/>
+      <c r="A518" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B518" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D518" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F518" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H518" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I518" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J518" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L518" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M518" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="N518" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O518" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P518" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q518" s="2"/>
       <c r="R518" s="2"/>
       <c r="S518" s="2"/>
@@ -33337,22 +34440,54 @@
       <c r="Z518" s="2"/>
     </row>
     <row r="519" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A519" s="2"/>
-      <c r="B519" s="2"/>
-      <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
-      <c r="E519" s="2"/>
-      <c r="F519" s="2"/>
-      <c r="G519" s="2"/>
-      <c r="H519" s="2"/>
-      <c r="I519" s="2"/>
-      <c r="J519" s="2"/>
-      <c r="K519" s="2"/>
-      <c r="L519" s="2"/>
-      <c r="M519" s="2"/>
-      <c r="N519" s="2"/>
-      <c r="O519" s="2"/>
-      <c r="P519" s="2"/>
+      <c r="A519" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D519" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H519" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I519" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L519" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M519" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="N519" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O519" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P519" s="5" t="s">
+        <v>1036</v>
+      </c>
       <c r="Q519" s="2"/>
       <c r="R519" s="2"/>
       <c r="S519" s="2"/>
@@ -33365,22 +34500,52 @@
       <c r="Z519" s="2"/>
     </row>
     <row r="520" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A520" s="2"/>
-      <c r="B520" s="2"/>
-      <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
-      <c r="E520" s="2"/>
-      <c r="F520" s="2"/>
-      <c r="G520" s="2"/>
-      <c r="H520" s="2"/>
-      <c r="I520" s="2"/>
-      <c r="J520" s="2"/>
-      <c r="K520" s="2"/>
-      <c r="L520" s="2"/>
-      <c r="M520" s="2"/>
-      <c r="N520" s="2"/>
-      <c r="O520" s="2"/>
-      <c r="P520" s="2"/>
+      <c r="A520" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D520" s="6"/>
+      <c r="E520" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F520" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H520" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I520" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K520" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L520" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M520" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="N520" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O520" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P520" s="5" t="s">
+        <v>1036</v>
+      </c>
       <c r="Q520" s="2"/>
       <c r="R520" s="2"/>
       <c r="S520" s="2"/>
@@ -33393,22 +34558,54 @@
       <c r="Z520" s="2"/>
     </row>
     <row r="521" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A521" s="2"/>
-      <c r="B521" s="2"/>
-      <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
-      <c r="E521" s="2"/>
-      <c r="F521" s="2"/>
-      <c r="G521" s="2"/>
-      <c r="H521" s="2"/>
-      <c r="I521" s="2"/>
-      <c r="J521" s="2"/>
-      <c r="K521" s="2"/>
-      <c r="L521" s="2"/>
-      <c r="M521" s="2"/>
-      <c r="N521" s="2"/>
-      <c r="O521" s="2"/>
-      <c r="P521" s="2"/>
+      <c r="A521" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D521" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F521" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H521" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I521" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K521" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L521" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M521" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="N521" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O521" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P521" s="5" t="s">
+        <v>309</v>
+      </c>
       <c r="Q521" s="2"/>
       <c r="R521" s="2"/>
       <c r="S521" s="2"/>
@@ -33420,23 +34617,55 @@
       <c r="Y521" s="2"/>
       <c r="Z521" s="2"/>
     </row>
-    <row r="522" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A522" s="2"/>
-      <c r="B522" s="2"/>
-      <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
-      <c r="E522" s="2"/>
-      <c r="F522" s="2"/>
-      <c r="G522" s="2"/>
-      <c r="H522" s="2"/>
-      <c r="I522" s="2"/>
-      <c r="J522" s="2"/>
-      <c r="K522" s="2"/>
-      <c r="L522" s="2"/>
-      <c r="M522" s="2"/>
-      <c r="N522" s="2"/>
-      <c r="O522" s="2"/>
-      <c r="P522" s="2"/>
+    <row r="522" spans="1:26" ht="14" x14ac:dyDescent="0.2">
+      <c r="A522" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D522" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F522" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I522" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K522" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L522" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="M522" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="N522" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O522" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P522" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q522" s="2"/>
       <c r="R522" s="2"/>
       <c r="S522" s="2"/>
@@ -33449,22 +34678,54 @@
       <c r="Z522" s="2"/>
     </row>
     <row r="523" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A523" s="2"/>
-      <c r="B523" s="2"/>
-      <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
-      <c r="E523" s="2"/>
-      <c r="F523" s="2"/>
-      <c r="G523" s="2"/>
-      <c r="H523" s="2"/>
-      <c r="I523" s="2"/>
-      <c r="J523" s="2"/>
-      <c r="K523" s="2"/>
-      <c r="L523" s="2"/>
-      <c r="M523" s="2"/>
-      <c r="N523" s="2"/>
-      <c r="O523" s="2"/>
-      <c r="P523" s="2"/>
+      <c r="A523" s="5" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D523" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F523" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I523" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J523" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L523" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M523" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N523" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O523" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P523" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q523" s="2"/>
       <c r="R523" s="2"/>
       <c r="S523" s="2"/>
@@ -33477,22 +34738,54 @@
       <c r="Z523" s="2"/>
     </row>
     <row r="524" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A524" s="2"/>
-      <c r="B524" s="2"/>
-      <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
-      <c r="E524" s="2"/>
-      <c r="F524" s="2"/>
-      <c r="G524" s="2"/>
-      <c r="H524" s="2"/>
-      <c r="I524" s="2"/>
-      <c r="J524" s="2"/>
-      <c r="K524" s="2"/>
-      <c r="L524" s="2"/>
-      <c r="M524" s="2"/>
-      <c r="N524" s="2"/>
-      <c r="O524" s="2"/>
-      <c r="P524" s="2"/>
+      <c r="A524" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D524" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F524" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L524" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M524" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N524" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O524" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P524" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q524" s="2"/>
       <c r="R524" s="2"/>
       <c r="S524" s="2"/>
@@ -33504,41 +34797,73 @@
       <c r="Y524" s="2"/>
       <c r="Z524" s="2"/>
     </row>
-    <row r="525" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A525" s="2"/>
-      <c r="B525" s="2"/>
-      <c r="C525" s="2"/>
-      <c r="D525" s="2"/>
-      <c r="E525" s="2"/>
-      <c r="F525" s="2"/>
-      <c r="G525" s="2"/>
-      <c r="H525" s="2"/>
-      <c r="I525" s="2"/>
-      <c r="J525" s="2"/>
-      <c r="K525" s="2"/>
-      <c r="L525" s="2"/>
-      <c r="M525" s="2"/>
-      <c r="N525" s="2"/>
-      <c r="O525" s="2"/>
-      <c r="P525" s="2"/>
-      <c r="Q525" s="2"/>
-      <c r="R525" s="2"/>
-      <c r="S525" s="2"/>
-      <c r="T525" s="2"/>
-      <c r="U525" s="2"/>
-      <c r="V525" s="2"/>
-      <c r="W525" s="2"/>
-      <c r="X525" s="2"/>
-      <c r="Y525" s="2"/>
-      <c r="Z525" s="2"/>
+    <row r="525" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A525" s="10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B525" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C525" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D525" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E525" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F525" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G525" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H525" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I525" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J525" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K525" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L525" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M525" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N525" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O525" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P525" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q525" s="8"/>
+      <c r="R525" s="8"/>
+      <c r="S525" s="8"/>
+      <c r="T525" s="8"/>
+      <c r="U525" s="8"/>
+      <c r="V525" s="8"/>
+      <c r="W525" s="8"/>
+      <c r="X525" s="8"/>
+      <c r="Y525" s="8"/>
+      <c r="Z525" s="8"/>
     </row>
     <row r="526" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A526" s="2"/>
-      <c r="B526" s="2"/>
-      <c r="C526" s="2"/>
-      <c r="D526" s="2"/>
+      <c r="A526" s="5"/>
+      <c r="B526" s="5"/>
+      <c r="C526" s="5"/>
+      <c r="D526" s="5"/>
       <c r="E526" s="2"/>
-      <c r="F526" s="2"/>
+      <c r="F526" s="5"/>
       <c r="G526" s="2"/>
       <c r="H526" s="2"/>
       <c r="I526" s="2"/>
@@ -33547,8 +34872,8 @@
       <c r="L526" s="2"/>
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
-      <c r="O526" s="2"/>
-      <c r="P526" s="2"/>
+      <c r="O526" s="5"/>
+      <c r="P526" s="5"/>
       <c r="Q526" s="2"/>
       <c r="R526" s="2"/>
       <c r="S526" s="2"/>
@@ -33561,12 +34886,12 @@
       <c r="Z526" s="2"/>
     </row>
     <row r="527" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A527" s="2"/>
-      <c r="B527" s="2"/>
-      <c r="C527" s="2"/>
-      <c r="D527" s="2"/>
+      <c r="A527" s="5"/>
+      <c r="B527" s="5"/>
+      <c r="C527" s="5"/>
+      <c r="D527" s="5"/>
       <c r="E527" s="2"/>
-      <c r="F527" s="2"/>
+      <c r="F527" s="5"/>
       <c r="G527" s="2"/>
       <c r="H527" s="2"/>
       <c r="I527" s="2"/>
@@ -33575,8 +34900,8 @@
       <c r="L527" s="2"/>
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
-      <c r="O527" s="2"/>
-      <c r="P527" s="2"/>
+      <c r="O527" s="5"/>
+      <c r="P527" s="5"/>
       <c r="Q527" s="2"/>
       <c r="R527" s="2"/>
       <c r="S527" s="2"/>
@@ -33589,12 +34914,12 @@
       <c r="Z527" s="2"/>
     </row>
     <row r="528" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A528" s="2"/>
-      <c r="B528" s="2"/>
-      <c r="C528" s="2"/>
-      <c r="D528" s="2"/>
+      <c r="A528" s="5"/>
+      <c r="B528" s="5"/>
+      <c r="C528" s="5"/>
+      <c r="D528" s="5"/>
       <c r="E528" s="2"/>
-      <c r="F528" s="2"/>
+      <c r="F528" s="5"/>
       <c r="G528" s="2"/>
       <c r="H528" s="2"/>
       <c r="I528" s="2"/>
@@ -33603,8 +34928,8 @@
       <c r="L528" s="2"/>
       <c r="M528" s="2"/>
       <c r="N528" s="2"/>
-      <c r="O528" s="2"/>
-      <c r="P528" s="2"/>
+      <c r="O528" s="5"/>
+      <c r="P528" s="5"/>
       <c r="Q528" s="2"/>
       <c r="R528" s="2"/>
       <c r="S528" s="2"/>
@@ -33617,12 +34942,12 @@
       <c r="Z528" s="2"/>
     </row>
     <row r="529" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A529" s="2"/>
-      <c r="B529" s="2"/>
-      <c r="C529" s="2"/>
-      <c r="D529" s="2"/>
+      <c r="A529" s="5"/>
+      <c r="B529" s="5"/>
+      <c r="C529" s="5"/>
+      <c r="D529" s="5"/>
       <c r="E529" s="2"/>
-      <c r="F529" s="2"/>
+      <c r="F529" s="5"/>
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
       <c r="I529" s="2"/>
@@ -33631,8 +34956,8 @@
       <c r="L529" s="2"/>
       <c r="M529" s="2"/>
       <c r="N529" s="2"/>
-      <c r="O529" s="2"/>
-      <c r="P529" s="2"/>
+      <c r="O529" s="5"/>
+      <c r="P529" s="5"/>
       <c r="Q529" s="2"/>
       <c r="R529" s="2"/>
       <c r="S529" s="2"/>
@@ -33645,12 +34970,12 @@
       <c r="Z529" s="2"/>
     </row>
     <row r="530" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A530" s="2"/>
-      <c r="B530" s="2"/>
-      <c r="C530" s="2"/>
-      <c r="D530" s="2"/>
+      <c r="A530" s="5"/>
+      <c r="B530" s="5"/>
+      <c r="C530" s="5"/>
+      <c r="D530" s="5"/>
       <c r="E530" s="2"/>
-      <c r="F530" s="2"/>
+      <c r="F530" s="5"/>
       <c r="G530" s="2"/>
       <c r="H530" s="2"/>
       <c r="I530" s="2"/>
@@ -33659,8 +34984,8 @@
       <c r="L530" s="2"/>
       <c r="M530" s="2"/>
       <c r="N530" s="2"/>
-      <c r="O530" s="2"/>
-      <c r="P530" s="2"/>
+      <c r="O530" s="5"/>
+      <c r="P530" s="5"/>
       <c r="Q530" s="2"/>
       <c r="R530" s="2"/>
       <c r="S530" s="2"/>
@@ -33673,12 +34998,12 @@
       <c r="Z530" s="2"/>
     </row>
     <row r="531" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A531" s="2"/>
-      <c r="B531" s="2"/>
-      <c r="C531" s="2"/>
-      <c r="D531" s="2"/>
+      <c r="A531" s="5"/>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
+      <c r="D531" s="5"/>
       <c r="E531" s="2"/>
-      <c r="F531" s="2"/>
+      <c r="F531" s="5"/>
       <c r="G531" s="2"/>
       <c r="H531" s="2"/>
       <c r="I531" s="2"/>
@@ -33687,8 +35012,8 @@
       <c r="L531" s="2"/>
       <c r="M531" s="2"/>
       <c r="N531" s="2"/>
-      <c r="O531" s="2"/>
-      <c r="P531" s="2"/>
+      <c r="O531" s="5"/>
+      <c r="P531" s="5"/>
       <c r="Q531" s="2"/>
       <c r="R531" s="2"/>
       <c r="S531" s="2"/>
@@ -33701,12 +35026,12 @@
       <c r="Z531" s="2"/>
     </row>
     <row r="532" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A532" s="2"/>
-      <c r="B532" s="2"/>
-      <c r="C532" s="2"/>
-      <c r="D532" s="2"/>
+      <c r="A532" s="5"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="5"/>
+      <c r="D532" s="6"/>
       <c r="E532" s="2"/>
-      <c r="F532" s="2"/>
+      <c r="F532" s="5"/>
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
       <c r="I532" s="2"/>
@@ -33715,8 +35040,8 @@
       <c r="L532" s="2"/>
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
-      <c r="O532" s="2"/>
-      <c r="P532" s="2"/>
+      <c r="O532" s="5"/>
+      <c r="P532" s="5"/>
       <c r="Q532" s="2"/>
       <c r="R532" s="2"/>
       <c r="S532" s="2"/>
@@ -33729,12 +35054,12 @@
       <c r="Z532" s="2"/>
     </row>
     <row r="533" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A533" s="2"/>
-      <c r="B533" s="2"/>
-      <c r="C533" s="2"/>
-      <c r="D533" s="2"/>
+      <c r="A533" s="5"/>
+      <c r="B533" s="5"/>
+      <c r="C533" s="5"/>
+      <c r="D533" s="5"/>
       <c r="E533" s="2"/>
-      <c r="F533" s="2"/>
+      <c r="F533" s="5"/>
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
       <c r="I533" s="2"/>
@@ -33743,8 +35068,8 @@
       <c r="L533" s="2"/>
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
-      <c r="O533" s="2"/>
-      <c r="P533" s="2"/>
+      <c r="O533" s="5"/>
+      <c r="P533" s="5"/>
       <c r="Q533" s="2"/>
       <c r="R533" s="2"/>
       <c r="S533" s="2"/>
@@ -33756,13 +35081,13 @@
       <c r="Y533" s="2"/>
       <c r="Z533" s="2"/>
     </row>
-    <row r="534" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A534" s="2"/>
-      <c r="B534" s="2"/>
-      <c r="C534" s="2"/>
-      <c r="D534" s="2"/>
+    <row r="534" spans="1:26" ht="14" x14ac:dyDescent="0.2">
+      <c r="A534" s="5"/>
+      <c r="B534" s="5"/>
+      <c r="C534" s="5"/>
+      <c r="D534" s="5"/>
       <c r="E534" s="2"/>
-      <c r="F534" s="2"/>
+      <c r="F534" s="13"/>
       <c r="G534" s="2"/>
       <c r="H534" s="2"/>
       <c r="I534" s="2"/>
@@ -33771,8 +35096,8 @@
       <c r="L534" s="2"/>
       <c r="M534" s="2"/>
       <c r="N534" s="2"/>
-      <c r="O534" s="2"/>
-      <c r="P534" s="2"/>
+      <c r="O534" s="5"/>
+      <c r="P534" s="5"/>
       <c r="Q534" s="2"/>
       <c r="R534" s="2"/>
       <c r="S534" s="2"/>
@@ -33785,12 +35110,12 @@
       <c r="Z534" s="2"/>
     </row>
     <row r="535" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A535" s="2"/>
-      <c r="B535" s="2"/>
-      <c r="C535" s="2"/>
-      <c r="D535" s="2"/>
+      <c r="A535" s="5"/>
+      <c r="B535" s="5"/>
+      <c r="C535" s="5"/>
+      <c r="D535" s="5"/>
       <c r="E535" s="2"/>
-      <c r="F535" s="2"/>
+      <c r="F535" s="5"/>
       <c r="G535" s="2"/>
       <c r="H535" s="2"/>
       <c r="I535" s="2"/>
@@ -33799,8 +35124,8 @@
       <c r="L535" s="2"/>
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
-      <c r="O535" s="2"/>
-      <c r="P535" s="2"/>
+      <c r="O535" s="5"/>
+      <c r="P535" s="5"/>
       <c r="Q535" s="2"/>
       <c r="R535" s="2"/>
       <c r="S535" s="2"/>
@@ -33813,12 +35138,12 @@
       <c r="Z535" s="2"/>
     </row>
     <row r="536" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A536" s="2"/>
-      <c r="B536" s="2"/>
-      <c r="C536" s="2"/>
-      <c r="D536" s="2"/>
+      <c r="A536" s="5"/>
+      <c r="B536" s="5"/>
+      <c r="C536" s="5"/>
+      <c r="D536" s="5"/>
       <c r="E536" s="2"/>
-      <c r="F536" s="2"/>
+      <c r="F536" s="5"/>
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
       <c r="I536" s="2"/>
@@ -33827,8 +35152,8 @@
       <c r="L536" s="2"/>
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
-      <c r="O536" s="2"/>
-      <c r="P536" s="2"/>
+      <c r="O536" s="5"/>
+      <c r="P536" s="5"/>
       <c r="Q536" s="2"/>
       <c r="R536" s="2"/>
       <c r="S536" s="2"/>
@@ -33841,12 +35166,12 @@
       <c r="Z536" s="2"/>
     </row>
     <row r="537" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A537" s="2"/>
-      <c r="B537" s="2"/>
-      <c r="C537" s="2"/>
-      <c r="D537" s="2"/>
+      <c r="A537" s="5"/>
+      <c r="B537" s="5"/>
+      <c r="C537" s="5"/>
+      <c r="D537" s="5"/>
       <c r="E537" s="2"/>
-      <c r="F537" s="2"/>
+      <c r="F537" s="5"/>
       <c r="G537" s="2"/>
       <c r="H537" s="2"/>
       <c r="I537" s="2"/>
@@ -33855,8 +35180,8 @@
       <c r="L537" s="2"/>
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
-      <c r="O537" s="2"/>
-      <c r="P537" s="2"/>
+      <c r="O537" s="5"/>
+      <c r="P537" s="5"/>
       <c r="Q537" s="2"/>
       <c r="R537" s="2"/>
       <c r="S537" s="2"/>
@@ -46749,7 +48074,7 @@
       <c r="Z997" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P468" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P486" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/insightsgraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26ADAEA-E6D5-2A4E-A8DA-DC25201B4735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848AF7E0-B51A-A54B-BEA4-29384A871892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9407" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9914" uniqueCount="1087">
   <si>
     <t>Customer Name</t>
   </si>
@@ -3164,6 +3164,141 @@
   </si>
   <si>
     <t>Oh My Millets</t>
+  </si>
+  <si>
+    <t>Gautam Das</t>
+  </si>
+  <si>
+    <t>Riyaz Nagori</t>
+  </si>
+  <si>
+    <t>Chandan saha</t>
+  </si>
+  <si>
+    <t>Kamal ladwani</t>
+  </si>
+  <si>
+    <t>Muskan shabar</t>
+  </si>
+  <si>
+    <t>Sailakshmi mandavelli</t>
+  </si>
+  <si>
+    <t>Debkanya banerjee</t>
+  </si>
+  <si>
+    <t>Sunny bajaj</t>
+  </si>
+  <si>
+    <t>Tenzin Namdol</t>
+  </si>
+  <si>
+    <t>During work/study breaks, While watching content(Netflix, tv, amazon prime, sports), When I'm bored, While traveling</t>
+  </si>
+  <si>
+    <t>Big Mishra Peda</t>
+  </si>
+  <si>
+    <t>Prefers whatever's convenient, Most of the times its home made sweets</t>
+  </si>
+  <si>
+    <t>Haldiram's, Dadi, Almond house</t>
+  </si>
+  <si>
+    <t>She does not usually prefer any specific brand as most items are prepared at home but occasionally she prefers GODESi.</t>
+  </si>
+  <si>
+    <t>Dont prefer any brands usually</t>
+  </si>
+  <si>
+    <t>Bikanervala, Haldiram's, Lal</t>
+  </si>
+  <si>
+    <t>Tahseen Raza Sayyad</t>
+  </si>
+  <si>
+    <t>Achala Arvind Pewekar</t>
+  </si>
+  <si>
+    <t>Jatinder Bansal</t>
+  </si>
+  <si>
+    <t>Anubhav sharma</t>
+  </si>
+  <si>
+    <t>Dhanraj Chakravarti</t>
+  </si>
+  <si>
+    <t>Divya Salunke</t>
+  </si>
+  <si>
+    <t>Mn automobiles</t>
+  </si>
+  <si>
+    <t>Shivani agrawal</t>
+  </si>
+  <si>
+    <t>Amrita pani</t>
+  </si>
+  <si>
+    <t>Abdul ashik</t>
+  </si>
+  <si>
+    <t>Dhananjay </t>
+  </si>
+  <si>
+    <t>Manish Kumar Beck</t>
+  </si>
+  <si>
+    <t>Parth Patel</t>
+  </si>
+  <si>
+    <t>Atharva Dube</t>
+  </si>
+  <si>
+    <t>Kabilesh b</t>
+  </si>
+  <si>
+    <t>Nadeem Shaikh</t>
+  </si>
+  <si>
+    <t>Reshu jha</t>
+  </si>
+  <si>
+    <t>Abhishek MAHANTA</t>
+  </si>
+  <si>
+    <t>Ankita Sarvaiya</t>
+  </si>
+  <si>
+    <t>Arjun </t>
+  </si>
+  <si>
+    <t>Deepshikha Sharma</t>
+  </si>
+  <si>
+    <t>Unique format, Just wanted to try</t>
+  </si>
+  <si>
+    <t>After meals, While watching content, When I'm bored, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>Unique format, Better Ingredients, Just wanted to try</t>
+  </si>
+  <si>
+    <t>While watching content, When I'm bored, To curb my chatpata cravings, While traveling, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>Chapati cravings, Unique format, Better Ingredients, Fun to eat</t>
+  </si>
+  <si>
+    <t>Unique format, Better Ingredients, Marketing is good , trustworthy</t>
+  </si>
+  <si>
+    <t>After meals, When I'm bored</t>
+  </si>
+  <si>
+    <t>Chapati cravings, Better Ingredients, Nostalgic vibes</t>
   </si>
 </sst>
 </file>
@@ -34858,22 +34993,54 @@
       <c r="Z525" s="8"/>
     </row>
     <row r="526" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A526" s="5"/>
-      <c r="B526" s="5"/>
-      <c r="C526" s="5"/>
-      <c r="D526" s="5"/>
-      <c r="E526" s="2"/>
-      <c r="F526" s="5"/>
-      <c r="G526" s="2"/>
-      <c r="H526" s="2"/>
-      <c r="I526" s="2"/>
-      <c r="J526" s="2"/>
-      <c r="K526" s="2"/>
-      <c r="L526" s="2"/>
-      <c r="M526" s="2"/>
-      <c r="N526" s="2"/>
-      <c r="O526" s="5"/>
-      <c r="P526" s="5"/>
+      <c r="A526" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D526" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F526" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="G526" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H526" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I526" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J526" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K526" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L526" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M526" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N526" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O526" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P526" s="5" t="s">
+        <v>314</v>
+      </c>
       <c r="Q526" s="2"/>
       <c r="R526" s="2"/>
       <c r="S526" s="2"/>
@@ -34886,22 +35053,54 @@
       <c r="Z526" s="2"/>
     </row>
     <row r="527" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A527" s="5"/>
-      <c r="B527" s="5"/>
-      <c r="C527" s="5"/>
-      <c r="D527" s="5"/>
-      <c r="E527" s="2"/>
-      <c r="F527" s="5"/>
-      <c r="G527" s="2"/>
-      <c r="H527" s="2"/>
-      <c r="I527" s="2"/>
-      <c r="J527" s="2"/>
-      <c r="K527" s="2"/>
-      <c r="L527" s="2"/>
-      <c r="M527" s="2"/>
-      <c r="N527" s="2"/>
-      <c r="O527" s="5"/>
-      <c r="P527" s="5"/>
+      <c r="A527" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F527" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G527" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H527" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I527" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J527" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K527" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L527" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="M527" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="N527" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O527" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P527" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q527" s="2"/>
       <c r="R527" s="2"/>
       <c r="S527" s="2"/>
@@ -34914,22 +35113,54 @@
       <c r="Z527" s="2"/>
     </row>
     <row r="528" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A528" s="5"/>
-      <c r="B528" s="5"/>
-      <c r="C528" s="5"/>
-      <c r="D528" s="5"/>
-      <c r="E528" s="2"/>
-      <c r="F528" s="5"/>
-      <c r="G528" s="2"/>
-      <c r="H528" s="2"/>
-      <c r="I528" s="2"/>
-      <c r="J528" s="2"/>
-      <c r="K528" s="2"/>
-      <c r="L528" s="2"/>
-      <c r="M528" s="2"/>
-      <c r="N528" s="2"/>
-      <c r="O528" s="5"/>
-      <c r="P528" s="5"/>
+      <c r="A528" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D528" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E528" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F528" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G528" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H528" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I528" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J528" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K528" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L528" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M528" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N528" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O528" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P528" s="5" t="s">
+        <v>1051</v>
+      </c>
       <c r="Q528" s="2"/>
       <c r="R528" s="2"/>
       <c r="S528" s="2"/>
@@ -34942,22 +35173,52 @@
       <c r="Z528" s="2"/>
     </row>
     <row r="529" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A529" s="5"/>
-      <c r="B529" s="5"/>
-      <c r="C529" s="5"/>
-      <c r="D529" s="5"/>
-      <c r="E529" s="2"/>
-      <c r="F529" s="5"/>
-      <c r="G529" s="2"/>
-      <c r="H529" s="2"/>
-      <c r="I529" s="2"/>
-      <c r="J529" s="2"/>
-      <c r="K529" s="2"/>
-      <c r="L529" s="2"/>
-      <c r="M529" s="2"/>
-      <c r="N529" s="2"/>
-      <c r="O529" s="5"/>
-      <c r="P529" s="5"/>
+      <c r="A529" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D529" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F529" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G529" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H529" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I529" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J529" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K529" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L529" s="6"/>
+      <c r="M529" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N529" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O529" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P529" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q529" s="2"/>
       <c r="R529" s="2"/>
       <c r="S529" s="2"/>
@@ -34970,22 +35231,54 @@
       <c r="Z529" s="2"/>
     </row>
     <row r="530" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A530" s="5"/>
-      <c r="B530" s="5"/>
-      <c r="C530" s="5"/>
-      <c r="D530" s="5"/>
-      <c r="E530" s="2"/>
-      <c r="F530" s="5"/>
-      <c r="G530" s="2"/>
-      <c r="H530" s="2"/>
-      <c r="I530" s="2"/>
-      <c r="J530" s="2"/>
-      <c r="K530" s="2"/>
-      <c r="L530" s="2"/>
-      <c r="M530" s="2"/>
-      <c r="N530" s="2"/>
-      <c r="O530" s="5"/>
-      <c r="P530" s="5"/>
+      <c r="A530" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D530" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E530" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F530" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G530" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H530" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I530" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J530" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K530" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L530" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M530" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N530" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O530" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P530" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q530" s="2"/>
       <c r="R530" s="2"/>
       <c r="S530" s="2"/>
@@ -34998,22 +35291,52 @@
       <c r="Z530" s="2"/>
     </row>
     <row r="531" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A531" s="5"/>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
-      <c r="D531" s="5"/>
-      <c r="E531" s="2"/>
-      <c r="F531" s="5"/>
-      <c r="G531" s="2"/>
-      <c r="H531" s="2"/>
-      <c r="I531" s="2"/>
-      <c r="J531" s="2"/>
-      <c r="K531" s="2"/>
-      <c r="L531" s="2"/>
-      <c r="M531" s="2"/>
-      <c r="N531" s="2"/>
-      <c r="O531" s="5"/>
-      <c r="P531" s="5"/>
+      <c r="A531" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F531" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="G531" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H531" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I531" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J531" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K531" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L531" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M531" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="N531" s="6"/>
+      <c r="O531" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P531" s="5" t="s">
+        <v>955</v>
+      </c>
       <c r="Q531" s="2"/>
       <c r="R531" s="2"/>
       <c r="S531" s="2"/>
@@ -35026,22 +35349,54 @@
       <c r="Z531" s="2"/>
     </row>
     <row r="532" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A532" s="5"/>
-      <c r="B532" s="5"/>
-      <c r="C532" s="5"/>
-      <c r="D532" s="6"/>
-      <c r="E532" s="2"/>
-      <c r="F532" s="5"/>
-      <c r="G532" s="2"/>
-      <c r="H532" s="2"/>
-      <c r="I532" s="2"/>
-      <c r="J532" s="2"/>
-      <c r="K532" s="2"/>
-      <c r="L532" s="2"/>
-      <c r="M532" s="2"/>
-      <c r="N532" s="2"/>
-      <c r="O532" s="5"/>
-      <c r="P532" s="5"/>
+      <c r="A532" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D532" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E532" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G532" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H532" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I532" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J532" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K532" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L532" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M532" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N532" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O532" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P532" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="Q532" s="2"/>
       <c r="R532" s="2"/>
       <c r="S532" s="2"/>
@@ -35054,22 +35409,54 @@
       <c r="Z532" s="2"/>
     </row>
     <row r="533" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A533" s="5"/>
-      <c r="B533" s="5"/>
-      <c r="C533" s="5"/>
-      <c r="D533" s="5"/>
-      <c r="E533" s="2"/>
-      <c r="F533" s="5"/>
-      <c r="G533" s="2"/>
-      <c r="H533" s="2"/>
-      <c r="I533" s="2"/>
-      <c r="J533" s="2"/>
-      <c r="K533" s="2"/>
-      <c r="L533" s="2"/>
-      <c r="M533" s="2"/>
-      <c r="N533" s="2"/>
-      <c r="O533" s="5"/>
-      <c r="P533" s="5"/>
+      <c r="A533" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E533" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F533" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="G533" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H533" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I533" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J533" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K533" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L533" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M533" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="N533" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O533" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P533" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q533" s="2"/>
       <c r="R533" s="2"/>
       <c r="S533" s="2"/>
@@ -35081,23 +35468,55 @@
       <c r="Y533" s="2"/>
       <c r="Z533" s="2"/>
     </row>
-    <row r="534" spans="1:26" ht="14" x14ac:dyDescent="0.2">
-      <c r="A534" s="5"/>
-      <c r="B534" s="5"/>
-      <c r="C534" s="5"/>
-      <c r="D534" s="5"/>
-      <c r="E534" s="2"/>
-      <c r="F534" s="13"/>
-      <c r="G534" s="2"/>
-      <c r="H534" s="2"/>
-      <c r="I534" s="2"/>
-      <c r="J534" s="2"/>
-      <c r="K534" s="2"/>
-      <c r="L534" s="2"/>
-      <c r="M534" s="2"/>
-      <c r="N534" s="2"/>
-      <c r="O534" s="5"/>
-      <c r="P534" s="5"/>
+    <row r="534" spans="1:26" ht="13" x14ac:dyDescent="0.15">
+      <c r="A534" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D534" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E534" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F534" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G534" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H534" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I534" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J534" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K534" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L534" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M534" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="N534" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O534" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P534" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q534" s="2"/>
       <c r="R534" s="2"/>
       <c r="S534" s="2"/>
@@ -35109,51 +35528,115 @@
       <c r="Y534" s="2"/>
       <c r="Z534" s="2"/>
     </row>
-    <row r="535" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A535" s="5"/>
-      <c r="B535" s="5"/>
-      <c r="C535" s="5"/>
-      <c r="D535" s="5"/>
-      <c r="E535" s="2"/>
-      <c r="F535" s="5"/>
-      <c r="G535" s="2"/>
-      <c r="H535" s="2"/>
-      <c r="I535" s="2"/>
-      <c r="J535" s="2"/>
-      <c r="K535" s="2"/>
-      <c r="L535" s="2"/>
-      <c r="M535" s="2"/>
-      <c r="N535" s="2"/>
-      <c r="O535" s="5"/>
-      <c r="P535" s="5"/>
-      <c r="Q535" s="2"/>
-      <c r="R535" s="2"/>
-      <c r="S535" s="2"/>
-      <c r="T535" s="2"/>
-      <c r="U535" s="2"/>
-      <c r="V535" s="2"/>
-      <c r="W535" s="2"/>
-      <c r="X535" s="2"/>
-      <c r="Y535" s="2"/>
-      <c r="Z535" s="2"/>
+    <row r="535" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A535" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B535" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C535" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D535" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E535" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F535" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G535" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H535" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I535" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J535" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K535" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L535" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="M535" s="10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N535" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="O535" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P535" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q535" s="8"/>
+      <c r="R535" s="8"/>
+      <c r="S535" s="8"/>
+      <c r="T535" s="8"/>
+      <c r="U535" s="8"/>
+      <c r="V535" s="8"/>
+      <c r="W535" s="8"/>
+      <c r="X535" s="8"/>
+      <c r="Y535" s="8"/>
+      <c r="Z535" s="8"/>
     </row>
     <row r="536" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A536" s="5"/>
-      <c r="B536" s="5"/>
-      <c r="C536" s="5"/>
-      <c r="D536" s="5"/>
-      <c r="E536" s="2"/>
-      <c r="F536" s="5"/>
-      <c r="G536" s="2"/>
-      <c r="H536" s="2"/>
-      <c r="I536" s="2"/>
-      <c r="J536" s="2"/>
-      <c r="K536" s="2"/>
-      <c r="L536" s="2"/>
-      <c r="M536" s="2"/>
-      <c r="N536" s="2"/>
-      <c r="O536" s="5"/>
-      <c r="P536" s="5"/>
+      <c r="A536" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D536" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E536" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F536" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G536" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H536" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I536" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J536" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K536" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L536" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M536" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N536" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O536" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P536" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q536" s="2"/>
       <c r="R536" s="2"/>
       <c r="S536" s="2"/>
@@ -35166,22 +35649,54 @@
       <c r="Z536" s="2"/>
     </row>
     <row r="537" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A537" s="5"/>
-      <c r="B537" s="5"/>
-      <c r="C537" s="5"/>
-      <c r="D537" s="5"/>
-      <c r="E537" s="2"/>
-      <c r="F537" s="5"/>
-      <c r="G537" s="2"/>
-      <c r="H537" s="2"/>
-      <c r="I537" s="2"/>
-      <c r="J537" s="2"/>
-      <c r="K537" s="2"/>
-      <c r="L537" s="2"/>
-      <c r="M537" s="2"/>
-      <c r="N537" s="2"/>
-      <c r="O537" s="5"/>
-      <c r="P537" s="5"/>
+      <c r="A537" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E537" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F537" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G537" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H537" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I537" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J537" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K537" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L537" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M537" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N537" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O537" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P537" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q537" s="2"/>
       <c r="R537" s="2"/>
       <c r="S537" s="2"/>
@@ -35194,22 +35709,54 @@
       <c r="Z537" s="2"/>
     </row>
     <row r="538" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A538" s="2"/>
-      <c r="B538" s="2"/>
-      <c r="C538" s="2"/>
-      <c r="D538" s="2"/>
-      <c r="E538" s="2"/>
-      <c r="F538" s="2"/>
-      <c r="G538" s="2"/>
-      <c r="H538" s="2"/>
-      <c r="I538" s="2"/>
-      <c r="J538" s="2"/>
-      <c r="K538" s="2"/>
-      <c r="L538" s="2"/>
-      <c r="M538" s="2"/>
-      <c r="N538" s="2"/>
-      <c r="O538" s="2"/>
-      <c r="P538" s="2"/>
+      <c r="A538" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E538" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F538" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G538" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H538" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I538" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J538" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K538" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L538" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M538" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N538" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O538" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P538" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q538" s="2"/>
       <c r="R538" s="2"/>
       <c r="S538" s="2"/>
@@ -35222,22 +35769,52 @@
       <c r="Z538" s="2"/>
     </row>
     <row r="539" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A539" s="2"/>
-      <c r="B539" s="2"/>
-      <c r="C539" s="2"/>
-      <c r="D539" s="2"/>
-      <c r="E539" s="2"/>
-      <c r="F539" s="2"/>
-      <c r="G539" s="2"/>
-      <c r="H539" s="2"/>
-      <c r="I539" s="2"/>
-      <c r="J539" s="2"/>
-      <c r="K539" s="2"/>
-      <c r="L539" s="2"/>
-      <c r="M539" s="2"/>
-      <c r="N539" s="2"/>
-      <c r="O539" s="2"/>
-      <c r="P539" s="2"/>
+      <c r="A539" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D539" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E539" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F539" s="6"/>
+      <c r="G539" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H539" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I539" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J539" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K539" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L539" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M539" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N539" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O539" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P539" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q539" s="2"/>
       <c r="R539" s="2"/>
       <c r="S539" s="2"/>
@@ -35250,22 +35827,52 @@
       <c r="Z539" s="2"/>
     </row>
     <row r="540" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A540" s="2"/>
-      <c r="B540" s="2"/>
-      <c r="C540" s="2"/>
-      <c r="D540" s="2"/>
-      <c r="E540" s="2"/>
-      <c r="F540" s="2"/>
-      <c r="G540" s="2"/>
-      <c r="H540" s="2"/>
-      <c r="I540" s="2"/>
-      <c r="J540" s="2"/>
-      <c r="K540" s="2"/>
-      <c r="L540" s="2"/>
-      <c r="M540" s="2"/>
-      <c r="N540" s="2"/>
-      <c r="O540" s="2"/>
-      <c r="P540" s="2"/>
+      <c r="A540" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D540" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E540" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F540" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G540" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H540" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I540" s="6"/>
+      <c r="J540" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K540" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L540" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M540" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N540" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O540" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P540" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q540" s="2"/>
       <c r="R540" s="2"/>
       <c r="S540" s="2"/>
@@ -35278,22 +35885,54 @@
       <c r="Z540" s="2"/>
     </row>
     <row r="541" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A541" s="2"/>
-      <c r="B541" s="2"/>
-      <c r="C541" s="2"/>
-      <c r="D541" s="2"/>
-      <c r="E541" s="2"/>
-      <c r="F541" s="2"/>
-      <c r="G541" s="2"/>
-      <c r="H541" s="2"/>
-      <c r="I541" s="2"/>
-      <c r="J541" s="2"/>
-      <c r="K541" s="2"/>
-      <c r="L541" s="2"/>
-      <c r="M541" s="2"/>
-      <c r="N541" s="2"/>
-      <c r="O541" s="2"/>
-      <c r="P541" s="2"/>
+      <c r="A541" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E541" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F541" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G541" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H541" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I541" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J541" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K541" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L541" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M541" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N541" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O541" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P541" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q541" s="2"/>
       <c r="R541" s="2"/>
       <c r="S541" s="2"/>
@@ -35306,22 +35945,54 @@
       <c r="Z541" s="2"/>
     </row>
     <row r="542" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A542" s="2"/>
-      <c r="B542" s="2"/>
-      <c r="C542" s="2"/>
-      <c r="D542" s="2"/>
-      <c r="E542" s="2"/>
-      <c r="F542" s="2"/>
-      <c r="G542" s="2"/>
-      <c r="H542" s="2"/>
-      <c r="I542" s="2"/>
-      <c r="J542" s="2"/>
-      <c r="K542" s="2"/>
-      <c r="L542" s="2"/>
-      <c r="M542" s="2"/>
-      <c r="N542" s="2"/>
-      <c r="O542" s="2"/>
-      <c r="P542" s="2"/>
+      <c r="A542" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D542" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F542" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G542" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H542" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I542" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J542" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K542" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L542" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M542" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N542" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O542" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P542" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q542" s="2"/>
       <c r="R542" s="2"/>
       <c r="S542" s="2"/>
@@ -35334,22 +36005,54 @@
       <c r="Z542" s="2"/>
     </row>
     <row r="543" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A543" s="2"/>
-      <c r="B543" s="2"/>
-      <c r="C543" s="2"/>
-      <c r="D543" s="2"/>
-      <c r="E543" s="2"/>
-      <c r="F543" s="2"/>
-      <c r="G543" s="2"/>
-      <c r="H543" s="2"/>
-      <c r="I543" s="2"/>
-      <c r="J543" s="2"/>
-      <c r="K543" s="2"/>
-      <c r="L543" s="2"/>
-      <c r="M543" s="2"/>
-      <c r="N543" s="2"/>
-      <c r="O543" s="2"/>
-      <c r="P543" s="2"/>
+      <c r="A543" s="5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D543" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E543" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F543" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G543" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H543" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I543" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J543" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K543" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L543" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M543" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N543" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O543" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P543" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q543" s="2"/>
       <c r="R543" s="2"/>
       <c r="S543" s="2"/>
@@ -35362,22 +36065,54 @@
       <c r="Z543" s="2"/>
     </row>
     <row r="544" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A544" s="2"/>
-      <c r="B544" s="2"/>
-      <c r="C544" s="2"/>
-      <c r="D544" s="2"/>
-      <c r="E544" s="2"/>
-      <c r="F544" s="2"/>
-      <c r="G544" s="2"/>
-      <c r="H544" s="2"/>
-      <c r="I544" s="2"/>
-      <c r="J544" s="2"/>
-      <c r="K544" s="2"/>
-      <c r="L544" s="2"/>
-      <c r="M544" s="2"/>
-      <c r="N544" s="2"/>
-      <c r="O544" s="2"/>
-      <c r="P544" s="2"/>
+      <c r="A544" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D544" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E544" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F544" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G544" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H544" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I544" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J544" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K544" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L544" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M544" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N544" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O544" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P544" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q544" s="2"/>
       <c r="R544" s="2"/>
       <c r="S544" s="2"/>
@@ -35390,22 +36125,54 @@
       <c r="Z544" s="2"/>
     </row>
     <row r="545" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A545" s="2"/>
-      <c r="B545" s="2"/>
-      <c r="C545" s="2"/>
-      <c r="D545" s="2"/>
-      <c r="E545" s="2"/>
-      <c r="F545" s="2"/>
-      <c r="G545" s="2"/>
-      <c r="H545" s="2"/>
-      <c r="I545" s="2"/>
-      <c r="J545" s="2"/>
-      <c r="K545" s="2"/>
-      <c r="L545" s="2"/>
-      <c r="M545" s="2"/>
-      <c r="N545" s="2"/>
-      <c r="O545" s="2"/>
-      <c r="P545" s="2"/>
+      <c r="A545" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D545" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E545" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F545" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G545" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H545" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I545" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J545" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K545" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L545" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M545" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N545" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O545" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P545" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q545" s="2"/>
       <c r="R545" s="2"/>
       <c r="S545" s="2"/>
@@ -35418,22 +36185,54 @@
       <c r="Z545" s="2"/>
     </row>
     <row r="546" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A546" s="2"/>
-      <c r="B546" s="2"/>
-      <c r="C546" s="2"/>
-      <c r="D546" s="2"/>
-      <c r="E546" s="2"/>
-      <c r="F546" s="2"/>
-      <c r="G546" s="2"/>
-      <c r="H546" s="2"/>
-      <c r="I546" s="2"/>
-      <c r="J546" s="2"/>
-      <c r="K546" s="2"/>
-      <c r="L546" s="2"/>
-      <c r="M546" s="2"/>
-      <c r="N546" s="2"/>
-      <c r="O546" s="2"/>
-      <c r="P546" s="2"/>
+      <c r="A546" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D546" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E546" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F546" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G546" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H546" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I546" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J546" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K546" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L546" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M546" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N546" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O546" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P546" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q546" s="2"/>
       <c r="R546" s="2"/>
       <c r="S546" s="2"/>
@@ -35446,22 +36245,52 @@
       <c r="Z546" s="2"/>
     </row>
     <row r="547" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A547" s="2"/>
-      <c r="B547" s="2"/>
-      <c r="C547" s="2"/>
-      <c r="D547" s="2"/>
-      <c r="E547" s="2"/>
-      <c r="F547" s="2"/>
-      <c r="G547" s="2"/>
-      <c r="H547" s="2"/>
-      <c r="I547" s="2"/>
-      <c r="J547" s="2"/>
-      <c r="K547" s="2"/>
-      <c r="L547" s="2"/>
-      <c r="M547" s="2"/>
-      <c r="N547" s="2"/>
-      <c r="O547" s="2"/>
-      <c r="P547" s="2"/>
+      <c r="A547" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D547" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E547" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F547" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G547" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H547" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I547" s="6"/>
+      <c r="J547" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K547" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L547" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M547" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N547" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O547" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P547" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q547" s="2"/>
       <c r="R547" s="2"/>
       <c r="S547" s="2"/>
@@ -35474,22 +36303,54 @@
       <c r="Z547" s="2"/>
     </row>
     <row r="548" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A548" s="2"/>
-      <c r="B548" s="2"/>
-      <c r="C548" s="2"/>
-      <c r="D548" s="2"/>
-      <c r="E548" s="2"/>
-      <c r="F548" s="2"/>
-      <c r="G548" s="2"/>
-      <c r="H548" s="2"/>
-      <c r="I548" s="2"/>
-      <c r="J548" s="2"/>
-      <c r="K548" s="2"/>
-      <c r="L548" s="2"/>
-      <c r="M548" s="2"/>
-      <c r="N548" s="2"/>
-      <c r="O548" s="2"/>
-      <c r="P548" s="2"/>
+      <c r="A548" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B548" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D548" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E548" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F548" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G548" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H548" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I548" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J548" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K548" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L548" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M548" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N548" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O548" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P548" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q548" s="2"/>
       <c r="R548" s="2"/>
       <c r="S548" s="2"/>
@@ -35502,22 +36363,54 @@
       <c r="Z548" s="2"/>
     </row>
     <row r="549" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A549" s="2"/>
-      <c r="B549" s="2"/>
-      <c r="C549" s="2"/>
-      <c r="D549" s="2"/>
-      <c r="E549" s="2"/>
-      <c r="F549" s="2"/>
-      <c r="G549" s="2"/>
-      <c r="H549" s="2"/>
-      <c r="I549" s="2"/>
-      <c r="J549" s="2"/>
-      <c r="K549" s="2"/>
-      <c r="L549" s="2"/>
-      <c r="M549" s="2"/>
-      <c r="N549" s="2"/>
-      <c r="O549" s="2"/>
-      <c r="P549" s="2"/>
+      <c r="A549" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D549" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E549" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F549" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G549" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H549" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I549" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J549" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K549" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L549" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M549" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N549" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O549" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P549" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q549" s="2"/>
       <c r="R549" s="2"/>
       <c r="S549" s="2"/>
@@ -35530,22 +36423,54 @@
       <c r="Z549" s="2"/>
     </row>
     <row r="550" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A550" s="2"/>
-      <c r="B550" s="2"/>
-      <c r="C550" s="2"/>
-      <c r="D550" s="2"/>
-      <c r="E550" s="2"/>
-      <c r="F550" s="2"/>
-      <c r="G550" s="2"/>
-      <c r="H550" s="2"/>
-      <c r="I550" s="2"/>
-      <c r="J550" s="2"/>
-      <c r="K550" s="2"/>
-      <c r="L550" s="2"/>
-      <c r="M550" s="2"/>
-      <c r="N550" s="2"/>
-      <c r="O550" s="2"/>
-      <c r="P550" s="2"/>
+      <c r="A550" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D550" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E550" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F550" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G550" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H550" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I550" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J550" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K550" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L550" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M550" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N550" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O550" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P550" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q550" s="2"/>
       <c r="R550" s="2"/>
       <c r="S550" s="2"/>
@@ -35558,22 +36483,54 @@
       <c r="Z550" s="2"/>
     </row>
     <row r="551" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A551" s="2"/>
-      <c r="B551" s="2"/>
-      <c r="C551" s="2"/>
-      <c r="D551" s="2"/>
-      <c r="E551" s="2"/>
-      <c r="F551" s="2"/>
-      <c r="G551" s="2"/>
-      <c r="H551" s="2"/>
-      <c r="I551" s="2"/>
-      <c r="J551" s="2"/>
-      <c r="K551" s="2"/>
-      <c r="L551" s="2"/>
-      <c r="M551" s="2"/>
-      <c r="N551" s="2"/>
-      <c r="O551" s="2"/>
-      <c r="P551" s="2"/>
+      <c r="A551" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D551" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E551" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F551" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G551" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H551" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I551" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J551" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K551" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L551" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M551" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N551" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O551" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P551" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q551" s="2"/>
       <c r="R551" s="2"/>
       <c r="S551" s="2"/>
@@ -35586,22 +36543,54 @@
       <c r="Z551" s="2"/>
     </row>
     <row r="552" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A552" s="2"/>
-      <c r="B552" s="2"/>
-      <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
-      <c r="E552" s="2"/>
-      <c r="F552" s="2"/>
-      <c r="G552" s="2"/>
-      <c r="H552" s="2"/>
-      <c r="I552" s="2"/>
-      <c r="J552" s="2"/>
-      <c r="K552" s="2"/>
-      <c r="L552" s="2"/>
-      <c r="M552" s="2"/>
-      <c r="N552" s="2"/>
-      <c r="O552" s="2"/>
-      <c r="P552" s="2"/>
+      <c r="A552" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D552" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E552" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F552" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G552" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H552" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I552" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J552" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K552" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L552" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M552" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N552" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O552" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P552" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q552" s="2"/>
       <c r="R552" s="2"/>
       <c r="S552" s="2"/>
@@ -35614,22 +36603,54 @@
       <c r="Z552" s="2"/>
     </row>
     <row r="553" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A553" s="2"/>
-      <c r="B553" s="2"/>
-      <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
-      <c r="E553" s="2"/>
-      <c r="F553" s="2"/>
-      <c r="G553" s="2"/>
-      <c r="H553" s="2"/>
-      <c r="I553" s="2"/>
-      <c r="J553" s="2"/>
-      <c r="K553" s="2"/>
-      <c r="L553" s="2"/>
-      <c r="M553" s="2"/>
-      <c r="N553" s="2"/>
-      <c r="O553" s="2"/>
-      <c r="P553" s="2"/>
+      <c r="A553" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B553" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D553" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E553" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F553" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G553" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H553" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I553" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J553" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K553" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L553" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M553" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N553" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O553" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P553" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q553" s="2"/>
       <c r="R553" s="2"/>
       <c r="S553" s="2"/>
@@ -35642,22 +36663,54 @@
       <c r="Z553" s="2"/>
     </row>
     <row r="554" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A554" s="2"/>
-      <c r="B554" s="2"/>
-      <c r="C554" s="2"/>
-      <c r="D554" s="2"/>
-      <c r="E554" s="2"/>
-      <c r="F554" s="2"/>
-      <c r="G554" s="2"/>
-      <c r="H554" s="2"/>
-      <c r="I554" s="2"/>
-      <c r="J554" s="2"/>
-      <c r="K554" s="2"/>
-      <c r="L554" s="2"/>
-      <c r="M554" s="2"/>
-      <c r="N554" s="2"/>
-      <c r="O554" s="2"/>
-      <c r="P554" s="2"/>
+      <c r="A554" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D554" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E554" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F554" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G554" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H554" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I554" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J554" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K554" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L554" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M554" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N554" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O554" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P554" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q554" s="2"/>
       <c r="R554" s="2"/>
       <c r="S554" s="2"/>
@@ -35670,22 +36723,54 @@
       <c r="Z554" s="2"/>
     </row>
     <row r="555" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A555" s="2"/>
-      <c r="B555" s="2"/>
-      <c r="C555" s="2"/>
-      <c r="D555" s="2"/>
-      <c r="E555" s="2"/>
-      <c r="F555" s="2"/>
-      <c r="G555" s="2"/>
-      <c r="H555" s="2"/>
-      <c r="I555" s="2"/>
-      <c r="J555" s="2"/>
-      <c r="K555" s="2"/>
-      <c r="L555" s="2"/>
-      <c r="M555" s="2"/>
-      <c r="N555" s="2"/>
-      <c r="O555" s="2"/>
-      <c r="P555" s="2"/>
+      <c r="A555" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D555" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E555" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F555" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G555" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H555" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I555" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J555" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K555" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L555" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M555" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N555" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O555" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P555" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q555" s="2"/>
       <c r="R555" s="2"/>
       <c r="S555" s="2"/>
@@ -35698,22 +36783,54 @@
       <c r="Z555" s="2"/>
     </row>
     <row r="556" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A556" s="2"/>
-      <c r="B556" s="2"/>
-      <c r="C556" s="2"/>
-      <c r="D556" s="2"/>
-      <c r="E556" s="2"/>
-      <c r="F556" s="2"/>
-      <c r="G556" s="2"/>
-      <c r="H556" s="2"/>
-      <c r="I556" s="2"/>
-      <c r="J556" s="2"/>
-      <c r="K556" s="2"/>
-      <c r="L556" s="2"/>
-      <c r="M556" s="2"/>
-      <c r="N556" s="2"/>
-      <c r="O556" s="2"/>
-      <c r="P556" s="2"/>
+      <c r="A556" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D556" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E556" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F556" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G556" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H556" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I556" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J556" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K556" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L556" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M556" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N556" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O556" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P556" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q556" s="2"/>
       <c r="R556" s="2"/>
       <c r="S556" s="2"/>
@@ -35725,33 +36842,65 @@
       <c r="Y556" s="2"/>
       <c r="Z556" s="2"/>
     </row>
-    <row r="557" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A557" s="2"/>
-      <c r="B557" s="2"/>
-      <c r="C557" s="2"/>
-      <c r="D557" s="2"/>
-      <c r="E557" s="2"/>
-      <c r="F557" s="2"/>
-      <c r="G557" s="2"/>
-      <c r="H557" s="2"/>
-      <c r="I557" s="2"/>
-      <c r="J557" s="2"/>
-      <c r="K557" s="2"/>
-      <c r="L557" s="2"/>
-      <c r="M557" s="2"/>
-      <c r="N557" s="2"/>
-      <c r="O557" s="2"/>
-      <c r="P557" s="2"/>
-      <c r="Q557" s="2"/>
-      <c r="R557" s="2"/>
-      <c r="S557" s="2"/>
-      <c r="T557" s="2"/>
-      <c r="U557" s="2"/>
-      <c r="V557" s="2"/>
-      <c r="W557" s="2"/>
-      <c r="X557" s="2"/>
-      <c r="Y557" s="2"/>
-      <c r="Z557" s="2"/>
+    <row r="557" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A557" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B557" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C557" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D557" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E557" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F557" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G557" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H557" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="I557" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="J557" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K557" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L557" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M557" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N557" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O557" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P557" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q557" s="8"/>
+      <c r="R557" s="8"/>
+      <c r="S557" s="8"/>
+      <c r="T557" s="8"/>
+      <c r="U557" s="8"/>
+      <c r="V557" s="8"/>
+      <c r="W557" s="8"/>
+      <c r="X557" s="8"/>
+      <c r="Y557" s="8"/>
+      <c r="Z557" s="8"/>
     </row>
     <row r="558" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A558" s="2"/>

--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/insightsgraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848AF7E0-B51A-A54B-BEA4-29384A871892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F0D365-B697-0942-8001-1C00CE8C8FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9914" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10620" uniqueCount="1143">
   <si>
     <t>Customer Name</t>
   </si>
@@ -3299,6 +3299,174 @@
   </si>
   <si>
     <t>Chapati cravings, Better Ingredients, Nostalgic vibes</t>
+  </si>
+  <si>
+    <t>Renu b</t>
+  </si>
+  <si>
+    <t>Gopal </t>
+  </si>
+  <si>
+    <t>ravindranath bellana</t>
+  </si>
+  <si>
+    <t>Ashmi </t>
+  </si>
+  <si>
+    <t>Zeeshan alikhan</t>
+  </si>
+  <si>
+    <t>vaishnavi Vishnu zombade</t>
+  </si>
+  <si>
+    <t>Siddharth kushwaha</t>
+  </si>
+  <si>
+    <t>Mushtaq ahmad khan</t>
+  </si>
+  <si>
+    <t>Vipul kumar prem</t>
+  </si>
+  <si>
+    <t>Hinal Tailor</t>
+  </si>
+  <si>
+    <t>Palak patra</t>
+  </si>
+  <si>
+    <t>Dharmaji Jyotshna</t>
+  </si>
+  <si>
+    <t>Nikita khatri</t>
+  </si>
+  <si>
+    <t>Ashwani Kr Singh</t>
+  </si>
+  <si>
+    <t>Abid akhtar</t>
+  </si>
+  <si>
+    <t>saratha </t>
+  </si>
+  <si>
+    <t>K MANJUNATHAREDDY</t>
+  </si>
+  <si>
+    <t>shashwat Jain</t>
+  </si>
+  <si>
+    <t>V Bhagya Lakshmi</t>
+  </si>
+  <si>
+    <t>RACHIT Chauhan</t>
+  </si>
+  <si>
+    <t>Ratnesh Shukla</t>
+  </si>
+  <si>
+    <t>Supritha </t>
+  </si>
+  <si>
+    <t>kaviprasath </t>
+  </si>
+  <si>
+    <t>Shailendra kumar verma</t>
+  </si>
+  <si>
+    <t>Ratandeep Arunkumar</t>
+  </si>
+  <si>
+    <t>Monika kanagala</t>
+  </si>
+  <si>
+    <t>Tikam singh rajput</t>
+  </si>
+  <si>
+    <t>Imran khan s</t>
+  </si>
+  <si>
+    <t>Gourav kumar gurnani</t>
+  </si>
+  <si>
+    <t>Munibanaaz </t>
+  </si>
+  <si>
+    <t>Rupal Pardeshi</t>
+  </si>
+  <si>
+    <t>Akash ghildiyal</t>
+  </si>
+  <si>
+    <t>Evening snacks</t>
+  </si>
+  <si>
+    <t>Better Ingredients, Hygiene</t>
+  </si>
+  <si>
+    <t>liked it </t>
+  </si>
+  <si>
+    <t>Candy, Lollipop, Churan, Tamrind Pop, Chocolate</t>
+  </si>
+  <si>
+    <t>Mohammad Waseem Akki</t>
+  </si>
+  <si>
+    <t>Namrata manglik</t>
+  </si>
+  <si>
+    <t>Sandeesh babu</t>
+  </si>
+  <si>
+    <t>Girijesh Gupta</t>
+  </si>
+  <si>
+    <t>Namrata Angadi</t>
+  </si>
+  <si>
+    <t>saroj gupta</t>
+  </si>
+  <si>
+    <t>uttam sundesha</t>
+  </si>
+  <si>
+    <t>Hari bagavandhan</t>
+  </si>
+  <si>
+    <t>Kritika suman</t>
+  </si>
+  <si>
+    <t>Manas Ranjan Parida</t>
+  </si>
+  <si>
+    <t>Svk </t>
+  </si>
+  <si>
+    <t>While watching content(Netflix, tv, amazon prime, sports)</t>
+  </si>
+  <si>
+    <t>Diconnected in middle of the call</t>
+  </si>
+  <si>
+    <t>Amul, Haldiram's, Novelty</t>
+  </si>
+  <si>
+    <t>local shops</t>
+  </si>
+  <si>
+    <t>Nandini Sweets, Haldiram's</t>
+  </si>
+  <si>
+    <t>Prefers whatever's convenient, </t>
+  </si>
+  <si>
+    <t>Amul, </t>
+  </si>
+  <si>
+    <t>Amul, Haldiram's, Bikaji Sweets</t>
+  </si>
+  <si>
+    <t>Haldiram's, </t>
   </si>
 </sst>
 </file>
@@ -3382,7 +3550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3407,6 +3575,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -36903,22 +37072,54 @@
       <c r="Z557" s="8"/>
     </row>
     <row r="558" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A558" s="2"/>
-      <c r="B558" s="2"/>
-      <c r="C558" s="2"/>
-      <c r="D558" s="2"/>
-      <c r="E558" s="2"/>
-      <c r="F558" s="2"/>
-      <c r="G558" s="2"/>
-      <c r="H558" s="2"/>
-      <c r="I558" s="2"/>
-      <c r="J558" s="2"/>
-      <c r="K558" s="2"/>
-      <c r="L558" s="2"/>
-      <c r="M558" s="2"/>
-      <c r="N558" s="2"/>
-      <c r="O558" s="2"/>
-      <c r="P558" s="2"/>
+      <c r="A558" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D558" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E558" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F558" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G558" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H558" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I558" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J558" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K558" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L558" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M558" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N558" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O558" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P558" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q558" s="2"/>
       <c r="R558" s="2"/>
       <c r="S558" s="2"/>
@@ -36931,22 +37132,52 @@
       <c r="Z558" s="2"/>
     </row>
     <row r="559" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A559" s="2"/>
-      <c r="B559" s="2"/>
-      <c r="C559" s="2"/>
-      <c r="D559" s="2"/>
-      <c r="E559" s="2"/>
-      <c r="F559" s="2"/>
-      <c r="G559" s="2"/>
-      <c r="H559" s="2"/>
-      <c r="I559" s="2"/>
-      <c r="J559" s="2"/>
-      <c r="K559" s="2"/>
-      <c r="L559" s="2"/>
-      <c r="M559" s="2"/>
-      <c r="N559" s="2"/>
-      <c r="O559" s="2"/>
-      <c r="P559" s="2"/>
+      <c r="A559" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D559" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E559" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F559" s="6"/>
+      <c r="G559" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H559" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I559" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J559" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K559" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L559" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M559" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N559" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O559" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P559" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q559" s="2"/>
       <c r="R559" s="2"/>
       <c r="S559" s="2"/>
@@ -36959,22 +37190,54 @@
       <c r="Z559" s="2"/>
     </row>
     <row r="560" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A560" s="2"/>
-      <c r="B560" s="2"/>
-      <c r="C560" s="2"/>
-      <c r="D560" s="2"/>
-      <c r="E560" s="2"/>
-      <c r="F560" s="2"/>
-      <c r="G560" s="2"/>
-      <c r="H560" s="2"/>
-      <c r="I560" s="2"/>
-      <c r="J560" s="2"/>
-      <c r="K560" s="2"/>
-      <c r="L560" s="2"/>
-      <c r="M560" s="2"/>
-      <c r="N560" s="2"/>
-      <c r="O560" s="2"/>
-      <c r="P560" s="2"/>
+      <c r="A560" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D560" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E560" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F560" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G560" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H560" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I560" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J560" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K560" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L560" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M560" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N560" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O560" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P560" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q560" s="2"/>
       <c r="R560" s="2"/>
       <c r="S560" s="2"/>
@@ -36987,22 +37250,54 @@
       <c r="Z560" s="2"/>
     </row>
     <row r="561" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A561" s="2"/>
-      <c r="B561" s="2"/>
-      <c r="C561" s="2"/>
-      <c r="D561" s="2"/>
-      <c r="E561" s="2"/>
-      <c r="F561" s="2"/>
-      <c r="G561" s="2"/>
-      <c r="H561" s="2"/>
-      <c r="I561" s="2"/>
-      <c r="J561" s="2"/>
-      <c r="K561" s="2"/>
-      <c r="L561" s="2"/>
-      <c r="M561" s="2"/>
-      <c r="N561" s="2"/>
-      <c r="O561" s="2"/>
-      <c r="P561" s="2"/>
+      <c r="A561" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D561" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E561" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F561" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G561" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H561" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I561" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J561" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K561" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L561" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M561" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N561" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O561" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P561" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q561" s="2"/>
       <c r="R561" s="2"/>
       <c r="S561" s="2"/>
@@ -37015,22 +37310,54 @@
       <c r="Z561" s="2"/>
     </row>
     <row r="562" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A562" s="2"/>
-      <c r="B562" s="2"/>
-      <c r="C562" s="2"/>
-      <c r="D562" s="2"/>
-      <c r="E562" s="2"/>
-      <c r="F562" s="2"/>
-      <c r="G562" s="2"/>
-      <c r="H562" s="2"/>
-      <c r="I562" s="2"/>
-      <c r="J562" s="2"/>
-      <c r="K562" s="2"/>
-      <c r="L562" s="2"/>
-      <c r="M562" s="2"/>
-      <c r="N562" s="2"/>
-      <c r="O562" s="2"/>
-      <c r="P562" s="2"/>
+      <c r="A562" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D562" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E562" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F562" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G562" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H562" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I562" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J562" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K562" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P562" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q562" s="2"/>
       <c r="R562" s="2"/>
       <c r="S562" s="2"/>
@@ -37043,22 +37370,54 @@
       <c r="Z562" s="2"/>
     </row>
     <row r="563" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A563" s="2"/>
-      <c r="B563" s="2"/>
-      <c r="C563" s="2"/>
-      <c r="D563" s="2"/>
-      <c r="E563" s="2"/>
-      <c r="F563" s="2"/>
-      <c r="G563" s="2"/>
-      <c r="H563" s="2"/>
-      <c r="I563" s="2"/>
-      <c r="J563" s="2"/>
-      <c r="K563" s="2"/>
-      <c r="L563" s="2"/>
-      <c r="M563" s="2"/>
-      <c r="N563" s="2"/>
-      <c r="O563" s="2"/>
-      <c r="P563" s="2"/>
+      <c r="A563" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E563" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F563" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G563" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H563" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I563" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J563" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="K563" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L563" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M563" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N563" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O563" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P563" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q563" s="2"/>
       <c r="R563" s="2"/>
       <c r="S563" s="2"/>
@@ -37071,22 +37430,50 @@
       <c r="Z563" s="2"/>
     </row>
     <row r="564" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A564" s="2"/>
-      <c r="B564" s="2"/>
-      <c r="C564" s="2"/>
-      <c r="D564" s="2"/>
-      <c r="E564" s="2"/>
-      <c r="F564" s="2"/>
-      <c r="G564" s="2"/>
-      <c r="H564" s="2"/>
-      <c r="I564" s="2"/>
-      <c r="J564" s="2"/>
-      <c r="K564" s="2"/>
-      <c r="L564" s="2"/>
-      <c r="M564" s="2"/>
-      <c r="N564" s="2"/>
-      <c r="O564" s="2"/>
-      <c r="P564" s="2"/>
+      <c r="A564" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D564" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E564" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F564" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G564" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H564" s="6"/>
+      <c r="I564" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J564" s="6"/>
+      <c r="K564" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L564" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M564" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N564" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O564" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P564" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q564" s="2"/>
       <c r="R564" s="2"/>
       <c r="S564" s="2"/>
@@ -37099,22 +37486,52 @@
       <c r="Z564" s="2"/>
     </row>
     <row r="565" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A565" s="2"/>
-      <c r="B565" s="2"/>
-      <c r="C565" s="2"/>
-      <c r="D565" s="2"/>
-      <c r="E565" s="2"/>
-      <c r="F565" s="2"/>
-      <c r="G565" s="2"/>
-      <c r="H565" s="2"/>
-      <c r="I565" s="2"/>
-      <c r="J565" s="2"/>
-      <c r="K565" s="2"/>
-      <c r="L565" s="2"/>
-      <c r="M565" s="2"/>
-      <c r="N565" s="2"/>
-      <c r="O565" s="2"/>
-      <c r="P565" s="2"/>
+      <c r="A565" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E565" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F565" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G565" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H565" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I565" s="6"/>
+      <c r="J565" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K565" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L565" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M565" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N565" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O565" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P565" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q565" s="2"/>
       <c r="R565" s="2"/>
       <c r="S565" s="2"/>
@@ -37127,22 +37544,54 @@
       <c r="Z565" s="2"/>
     </row>
     <row r="566" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A566" s="2"/>
-      <c r="B566" s="2"/>
-      <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
-      <c r="E566" s="2"/>
-      <c r="F566" s="2"/>
-      <c r="G566" s="2"/>
-      <c r="H566" s="2"/>
-      <c r="I566" s="2"/>
-      <c r="J566" s="2"/>
-      <c r="K566" s="2"/>
-      <c r="L566" s="2"/>
-      <c r="M566" s="2"/>
-      <c r="N566" s="2"/>
-      <c r="O566" s="2"/>
-      <c r="P566" s="2"/>
+      <c r="A566" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D566" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E566" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F566" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G566" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H566" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I566" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J566" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K566" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L566" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M566" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N566" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O566" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P566" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q566" s="2"/>
       <c r="R566" s="2"/>
       <c r="S566" s="2"/>
@@ -37155,22 +37604,54 @@
       <c r="Z566" s="2"/>
     </row>
     <row r="567" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A567" s="2"/>
-      <c r="B567" s="2"/>
-      <c r="C567" s="2"/>
-      <c r="D567" s="2"/>
-      <c r="E567" s="2"/>
-      <c r="F567" s="2"/>
-      <c r="G567" s="2"/>
-      <c r="H567" s="2"/>
-      <c r="I567" s="2"/>
-      <c r="J567" s="2"/>
-      <c r="K567" s="2"/>
-      <c r="L567" s="2"/>
-      <c r="M567" s="2"/>
-      <c r="N567" s="2"/>
-      <c r="O567" s="2"/>
-      <c r="P567" s="2"/>
+      <c r="A567" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B567" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D567" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E567" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F567" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G567" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H567" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I567" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J567" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K567" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L567" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M567" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N567" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O567" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P567" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q567" s="2"/>
       <c r="R567" s="2"/>
       <c r="S567" s="2"/>
@@ -37183,22 +37664,54 @@
       <c r="Z567" s="2"/>
     </row>
     <row r="568" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A568" s="2"/>
-      <c r="B568" s="2"/>
-      <c r="C568" s="2"/>
-      <c r="D568" s="2"/>
-      <c r="E568" s="2"/>
-      <c r="F568" s="2"/>
-      <c r="G568" s="2"/>
-      <c r="H568" s="2"/>
-      <c r="I568" s="2"/>
-      <c r="J568" s="2"/>
-      <c r="K568" s="2"/>
-      <c r="L568" s="2"/>
-      <c r="M568" s="2"/>
-      <c r="N568" s="2"/>
-      <c r="O568" s="2"/>
-      <c r="P568" s="2"/>
+      <c r="A568" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D568" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E568" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F568" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G568" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H568" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I568" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J568" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K568" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L568" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M568" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N568" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O568" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P568" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q568" s="2"/>
       <c r="R568" s="2"/>
       <c r="S568" s="2"/>
@@ -37211,22 +37724,54 @@
       <c r="Z568" s="2"/>
     </row>
     <row r="569" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A569" s="2"/>
-      <c r="B569" s="2"/>
-      <c r="C569" s="2"/>
-      <c r="D569" s="2"/>
-      <c r="E569" s="2"/>
-      <c r="F569" s="2"/>
-      <c r="G569" s="2"/>
-      <c r="H569" s="2"/>
-      <c r="I569" s="2"/>
-      <c r="J569" s="2"/>
-      <c r="K569" s="2"/>
-      <c r="L569" s="2"/>
-      <c r="M569" s="2"/>
-      <c r="N569" s="2"/>
-      <c r="O569" s="2"/>
-      <c r="P569" s="2"/>
+      <c r="A569" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B569" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D569" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E569" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F569" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G569" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H569" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I569" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J569" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K569" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L569" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M569" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N569" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O569" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P569" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q569" s="2"/>
       <c r="R569" s="2"/>
       <c r="S569" s="2"/>
@@ -37239,22 +37784,54 @@
       <c r="Z569" s="2"/>
     </row>
     <row r="570" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A570" s="2"/>
-      <c r="B570" s="2"/>
-      <c r="C570" s="2"/>
-      <c r="D570" s="2"/>
-      <c r="E570" s="2"/>
-      <c r="F570" s="2"/>
-      <c r="G570" s="2"/>
-      <c r="H570" s="2"/>
-      <c r="I570" s="2"/>
-      <c r="J570" s="2"/>
-      <c r="K570" s="2"/>
-      <c r="L570" s="2"/>
-      <c r="M570" s="2"/>
-      <c r="N570" s="2"/>
-      <c r="O570" s="2"/>
-      <c r="P570" s="2"/>
+      <c r="A570" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B570" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D570" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E570" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F570" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G570" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H570" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I570" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J570" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K570" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L570" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M570" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N570" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O570" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P570" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q570" s="2"/>
       <c r="R570" s="2"/>
       <c r="S570" s="2"/>
@@ -37267,22 +37844,52 @@
       <c r="Z570" s="2"/>
     </row>
     <row r="571" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A571" s="2"/>
-      <c r="B571" s="2"/>
-      <c r="C571" s="2"/>
-      <c r="D571" s="2"/>
-      <c r="E571" s="2"/>
-      <c r="F571" s="2"/>
-      <c r="G571" s="2"/>
-      <c r="H571" s="2"/>
-      <c r="I571" s="2"/>
-      <c r="J571" s="2"/>
-      <c r="K571" s="2"/>
-      <c r="L571" s="2"/>
-      <c r="M571" s="2"/>
-      <c r="N571" s="2"/>
-      <c r="O571" s="2"/>
-      <c r="P571" s="2"/>
+      <c r="A571" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B571" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D571" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E571" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F571" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G571" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H571" s="6"/>
+      <c r="I571" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J571" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K571" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L571" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M571" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N571" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O571" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P571" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q571" s="2"/>
       <c r="R571" s="2"/>
       <c r="S571" s="2"/>
@@ -37295,22 +37902,54 @@
       <c r="Z571" s="2"/>
     </row>
     <row r="572" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A572" s="2"/>
-      <c r="B572" s="2"/>
-      <c r="C572" s="2"/>
-      <c r="D572" s="2"/>
-      <c r="E572" s="2"/>
-      <c r="F572" s="2"/>
-      <c r="G572" s="2"/>
-      <c r="H572" s="2"/>
-      <c r="I572" s="2"/>
-      <c r="J572" s="2"/>
-      <c r="K572" s="2"/>
-      <c r="L572" s="2"/>
-      <c r="M572" s="2"/>
-      <c r="N572" s="2"/>
-      <c r="O572" s="2"/>
-      <c r="P572" s="2"/>
+      <c r="A572" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D572" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E572" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F572" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G572" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H572" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I572" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J572" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K572" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L572" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M572" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N572" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O572" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P572" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q572" s="2"/>
       <c r="R572" s="2"/>
       <c r="S572" s="2"/>
@@ -37323,22 +37962,54 @@
       <c r="Z572" s="2"/>
     </row>
     <row r="573" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A573" s="2"/>
-      <c r="B573" s="2"/>
-      <c r="C573" s="2"/>
-      <c r="D573" s="2"/>
-      <c r="E573" s="2"/>
-      <c r="F573" s="2"/>
-      <c r="G573" s="2"/>
-      <c r="H573" s="2"/>
-      <c r="I573" s="2"/>
-      <c r="J573" s="2"/>
-      <c r="K573" s="2"/>
-      <c r="L573" s="2"/>
-      <c r="M573" s="2"/>
-      <c r="N573" s="2"/>
-      <c r="O573" s="2"/>
-      <c r="P573" s="2"/>
+      <c r="A573" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B573" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E573" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G573" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H573" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I573" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J573" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K573" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L573" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M573" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N573" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O573" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P573" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q573" s="2"/>
       <c r="R573" s="2"/>
       <c r="S573" s="2"/>
@@ -37351,22 +38022,54 @@
       <c r="Z573" s="2"/>
     </row>
     <row r="574" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A574" s="2"/>
-      <c r="B574" s="2"/>
-      <c r="C574" s="2"/>
-      <c r="D574" s="2"/>
-      <c r="E574" s="2"/>
-      <c r="F574" s="2"/>
-      <c r="G574" s="2"/>
-      <c r="H574" s="2"/>
-      <c r="I574" s="2"/>
-      <c r="J574" s="2"/>
-      <c r="K574" s="2"/>
-      <c r="L574" s="2"/>
-      <c r="M574" s="2"/>
-      <c r="N574" s="2"/>
-      <c r="O574" s="2"/>
-      <c r="P574" s="2"/>
+      <c r="A574" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B574" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D574" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E574" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F574" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G574" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H574" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I574" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J574" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="K574" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L574" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M574" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N574" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O574" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P574" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q574" s="2"/>
       <c r="R574" s="2"/>
       <c r="S574" s="2"/>
@@ -37379,22 +38082,50 @@
       <c r="Z574" s="2"/>
     </row>
     <row r="575" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A575" s="2"/>
-      <c r="B575" s="2"/>
-      <c r="C575" s="2"/>
-      <c r="D575" s="2"/>
-      <c r="E575" s="2"/>
-      <c r="F575" s="2"/>
-      <c r="G575" s="2"/>
-      <c r="H575" s="2"/>
-      <c r="I575" s="2"/>
-      <c r="J575" s="2"/>
-      <c r="K575" s="2"/>
-      <c r="L575" s="2"/>
-      <c r="M575" s="2"/>
-      <c r="N575" s="2"/>
-      <c r="O575" s="2"/>
-      <c r="P575" s="2"/>
+      <c r="A575" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B575" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D575" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E575" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F575" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G575" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H575" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I575" s="6"/>
+      <c r="J575" s="6"/>
+      <c r="K575" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L575" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M575" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N575" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O575" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P575" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q575" s="2"/>
       <c r="R575" s="2"/>
       <c r="S575" s="2"/>
@@ -37407,22 +38138,54 @@
       <c r="Z575" s="2"/>
     </row>
     <row r="576" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A576" s="2"/>
-      <c r="B576" s="2"/>
-      <c r="C576" s="2"/>
-      <c r="D576" s="2"/>
-      <c r="E576" s="2"/>
-      <c r="F576" s="2"/>
-      <c r="G576" s="2"/>
-      <c r="H576" s="2"/>
-      <c r="I576" s="2"/>
-      <c r="J576" s="2"/>
-      <c r="K576" s="2"/>
-      <c r="L576" s="2"/>
-      <c r="M576" s="2"/>
-      <c r="N576" s="2"/>
-      <c r="O576" s="2"/>
-      <c r="P576" s="2"/>
+      <c r="A576" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B576" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D576" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E576" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F576" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G576" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H576" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I576" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J576" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K576" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L576" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M576" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N576" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O576" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P576" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q576" s="2"/>
       <c r="R576" s="2"/>
       <c r="S576" s="2"/>
@@ -37435,22 +38198,54 @@
       <c r="Z576" s="2"/>
     </row>
     <row r="577" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A577" s="2"/>
-      <c r="B577" s="2"/>
-      <c r="C577" s="2"/>
-      <c r="D577" s="2"/>
-      <c r="E577" s="2"/>
-      <c r="F577" s="2"/>
-      <c r="G577" s="2"/>
-      <c r="H577" s="2"/>
-      <c r="I577" s="2"/>
-      <c r="J577" s="2"/>
-      <c r="K577" s="2"/>
-      <c r="L577" s="2"/>
-      <c r="M577" s="2"/>
-      <c r="N577" s="2"/>
-      <c r="O577" s="2"/>
-      <c r="P577" s="2"/>
+      <c r="A577" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B577" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D577" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E577" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F577" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G577" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H577" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I577" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J577" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K577" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L577" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M577" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N577" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O577" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P577" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q577" s="2"/>
       <c r="R577" s="2"/>
       <c r="S577" s="2"/>
@@ -37463,22 +38258,54 @@
       <c r="Z577" s="2"/>
     </row>
     <row r="578" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A578" s="2"/>
-      <c r="B578" s="2"/>
-      <c r="C578" s="2"/>
-      <c r="D578" s="2"/>
-      <c r="E578" s="2"/>
-      <c r="F578" s="2"/>
-      <c r="G578" s="2"/>
-      <c r="H578" s="2"/>
-      <c r="I578" s="2"/>
-      <c r="J578" s="2"/>
-      <c r="K578" s="2"/>
-      <c r="L578" s="2"/>
-      <c r="M578" s="2"/>
-      <c r="N578" s="2"/>
-      <c r="O578" s="2"/>
-      <c r="P578" s="2"/>
+      <c r="A578" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B578" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D578" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E578" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F578" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G578" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H578" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I578" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J578" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="K578" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L578" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M578" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N578" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O578" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P578" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q578" s="2"/>
       <c r="R578" s="2"/>
       <c r="S578" s="2"/>
@@ -37491,22 +38318,54 @@
       <c r="Z578" s="2"/>
     </row>
     <row r="579" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A579" s="2"/>
-      <c r="B579" s="2"/>
-      <c r="C579" s="2"/>
-      <c r="D579" s="2"/>
-      <c r="E579" s="2"/>
-      <c r="F579" s="2"/>
-      <c r="G579" s="2"/>
-      <c r="H579" s="2"/>
-      <c r="I579" s="2"/>
-      <c r="J579" s="2"/>
-      <c r="K579" s="2"/>
-      <c r="L579" s="2"/>
-      <c r="M579" s="2"/>
-      <c r="N579" s="2"/>
-      <c r="O579" s="2"/>
-      <c r="P579" s="2"/>
+      <c r="A579" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B579" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D579" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E579" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F579" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G579" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H579" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I579" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J579" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="K579" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L579" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M579" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N579" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O579" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P579" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q579" s="2"/>
       <c r="R579" s="2"/>
       <c r="S579" s="2"/>
@@ -37519,22 +38378,54 @@
       <c r="Z579" s="2"/>
     </row>
     <row r="580" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A580" s="2"/>
-      <c r="B580" s="2"/>
-      <c r="C580" s="2"/>
-      <c r="D580" s="2"/>
-      <c r="E580" s="2"/>
-      <c r="F580" s="2"/>
-      <c r="G580" s="2"/>
-      <c r="H580" s="2"/>
-      <c r="I580" s="2"/>
-      <c r="J580" s="2"/>
-      <c r="K580" s="2"/>
-      <c r="L580" s="2"/>
-      <c r="M580" s="2"/>
-      <c r="N580" s="2"/>
-      <c r="O580" s="2"/>
-      <c r="P580" s="2"/>
+      <c r="A580" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B580" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C580" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D580" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E580" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F580" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G580" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H580" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I580" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J580" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K580" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L580" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M580" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N580" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O580" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P580" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q580" s="2"/>
       <c r="R580" s="2"/>
       <c r="S580" s="2"/>
@@ -37547,22 +38438,54 @@
       <c r="Z580" s="2"/>
     </row>
     <row r="581" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A581" s="2"/>
-      <c r="B581" s="2"/>
-      <c r="C581" s="2"/>
-      <c r="D581" s="2"/>
-      <c r="E581" s="2"/>
-      <c r="F581" s="2"/>
-      <c r="G581" s="2"/>
-      <c r="H581" s="2"/>
-      <c r="I581" s="2"/>
-      <c r="J581" s="2"/>
-      <c r="K581" s="2"/>
-      <c r="L581" s="2"/>
-      <c r="M581" s="2"/>
-      <c r="N581" s="2"/>
-      <c r="O581" s="2"/>
-      <c r="P581" s="2"/>
+      <c r="A581" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B581" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D581" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E581" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F581" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G581" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H581" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I581" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J581" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K581" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L581" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N581" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O581" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P581" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q581" s="2"/>
       <c r="R581" s="2"/>
       <c r="S581" s="2"/>
@@ -37575,22 +38498,52 @@
       <c r="Z581" s="2"/>
     </row>
     <row r="582" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A582" s="2"/>
-      <c r="B582" s="2"/>
-      <c r="C582" s="2"/>
-      <c r="D582" s="2"/>
-      <c r="E582" s="2"/>
-      <c r="F582" s="2"/>
-      <c r="G582" s="2"/>
-      <c r="H582" s="2"/>
-      <c r="I582" s="2"/>
-      <c r="J582" s="2"/>
-      <c r="K582" s="2"/>
-      <c r="L582" s="2"/>
-      <c r="M582" s="2"/>
-      <c r="N582" s="2"/>
-      <c r="O582" s="2"/>
-      <c r="P582" s="2"/>
+      <c r="A582" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B582" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D582" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E582" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F582" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G582" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H582" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I582" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J582" s="6"/>
+      <c r="K582" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L582" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M582" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N582" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O582" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P582" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q582" s="2"/>
       <c r="R582" s="2"/>
       <c r="S582" s="2"/>
@@ -37603,22 +38556,54 @@
       <c r="Z582" s="2"/>
     </row>
     <row r="583" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A583" s="2"/>
-      <c r="B583" s="2"/>
-      <c r="C583" s="2"/>
-      <c r="D583" s="2"/>
-      <c r="E583" s="2"/>
-      <c r="F583" s="2"/>
-      <c r="G583" s="2"/>
-      <c r="H583" s="2"/>
-      <c r="I583" s="2"/>
-      <c r="J583" s="2"/>
-      <c r="K583" s="2"/>
-      <c r="L583" s="2"/>
-      <c r="M583" s="2"/>
-      <c r="N583" s="2"/>
-      <c r="O583" s="2"/>
-      <c r="P583" s="2"/>
+      <c r="A583" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B583" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D583" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E583" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F583" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G583" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H583" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I583" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J583" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K583" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L583" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M583" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N583" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O583" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P583" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q583" s="2"/>
       <c r="R583" s="2"/>
       <c r="S583" s="2"/>
@@ -37631,22 +38616,54 @@
       <c r="Z583" s="2"/>
     </row>
     <row r="584" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A584" s="2"/>
-      <c r="B584" s="2"/>
-      <c r="C584" s="2"/>
-      <c r="D584" s="2"/>
-      <c r="E584" s="2"/>
-      <c r="F584" s="2"/>
-      <c r="G584" s="2"/>
-      <c r="H584" s="2"/>
-      <c r="I584" s="2"/>
-      <c r="J584" s="2"/>
-      <c r="K584" s="2"/>
-      <c r="L584" s="2"/>
-      <c r="M584" s="2"/>
-      <c r="N584" s="2"/>
-      <c r="O584" s="2"/>
-      <c r="P584" s="2"/>
+      <c r="A584" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B584" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C584" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D584" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E584" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F584" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G584" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H584" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I584" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J584" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K584" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L584" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M584" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N584" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O584" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P584" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q584" s="2"/>
       <c r="R584" s="2"/>
       <c r="S584" s="2"/>
@@ -37659,22 +38676,54 @@
       <c r="Z584" s="2"/>
     </row>
     <row r="585" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A585" s="2"/>
-      <c r="B585" s="2"/>
-      <c r="C585" s="2"/>
-      <c r="D585" s="2"/>
-      <c r="E585" s="2"/>
-      <c r="F585" s="2"/>
-      <c r="G585" s="2"/>
-      <c r="H585" s="2"/>
-      <c r="I585" s="2"/>
-      <c r="J585" s="2"/>
-      <c r="K585" s="2"/>
-      <c r="L585" s="2"/>
-      <c r="M585" s="2"/>
-      <c r="N585" s="2"/>
-      <c r="O585" s="2"/>
-      <c r="P585" s="2"/>
+      <c r="A585" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B585" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D585" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E585" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F585" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G585" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H585" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I585" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J585" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K585" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L585" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M585" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N585" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O585" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P585" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q585" s="2"/>
       <c r="R585" s="2"/>
       <c r="S585" s="2"/>
@@ -37687,22 +38736,54 @@
       <c r="Z585" s="2"/>
     </row>
     <row r="586" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A586" s="2"/>
-      <c r="B586" s="2"/>
-      <c r="C586" s="2"/>
-      <c r="D586" s="2"/>
-      <c r="E586" s="2"/>
-      <c r="F586" s="2"/>
-      <c r="G586" s="2"/>
-      <c r="H586" s="2"/>
-      <c r="I586" s="2"/>
-      <c r="J586" s="2"/>
-      <c r="K586" s="2"/>
-      <c r="L586" s="2"/>
-      <c r="M586" s="2"/>
-      <c r="N586" s="2"/>
-      <c r="O586" s="2"/>
-      <c r="P586" s="2"/>
+      <c r="A586" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="B586" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C586" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D586" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E586" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F586" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G586" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H586" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I586" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J586" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K586" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L586" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M586" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N586" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O586" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P586" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q586" s="2"/>
       <c r="R586" s="2"/>
       <c r="S586" s="2"/>
@@ -37715,22 +38796,54 @@
       <c r="Z586" s="2"/>
     </row>
     <row r="587" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A587" s="2"/>
-      <c r="B587" s="2"/>
-      <c r="C587" s="2"/>
-      <c r="D587" s="2"/>
-      <c r="E587" s="2"/>
-      <c r="F587" s="2"/>
-      <c r="G587" s="2"/>
-      <c r="H587" s="2"/>
-      <c r="I587" s="2"/>
-      <c r="J587" s="2"/>
-      <c r="K587" s="2"/>
-      <c r="L587" s="2"/>
-      <c r="M587" s="2"/>
-      <c r="N587" s="2"/>
-      <c r="O587" s="2"/>
-      <c r="P587" s="2"/>
+      <c r="A587" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B587" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D587" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E587" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F587" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G587" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H587" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I587" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J587" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K587" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L587" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M587" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N587" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O587" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P587" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q587" s="2"/>
       <c r="R587" s="2"/>
       <c r="S587" s="2"/>
@@ -37743,22 +38856,54 @@
       <c r="Z587" s="2"/>
     </row>
     <row r="588" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A588" s="2"/>
-      <c r="B588" s="2"/>
-      <c r="C588" s="2"/>
-      <c r="D588" s="2"/>
-      <c r="E588" s="2"/>
-      <c r="F588" s="2"/>
-      <c r="G588" s="2"/>
-      <c r="H588" s="2"/>
-      <c r="I588" s="2"/>
-      <c r="J588" s="2"/>
-      <c r="K588" s="2"/>
-      <c r="L588" s="2"/>
-      <c r="M588" s="2"/>
-      <c r="N588" s="2"/>
-      <c r="O588" s="2"/>
-      <c r="P588" s="2"/>
+      <c r="A588" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B588" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C588" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D588" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E588" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F588" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G588" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H588" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I588" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J588" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K588" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L588" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M588" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N588" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O588" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P588" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q588" s="2"/>
       <c r="R588" s="2"/>
       <c r="S588" s="2"/>
@@ -37771,22 +38916,54 @@
       <c r="Z588" s="2"/>
     </row>
     <row r="589" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A589" s="2"/>
-      <c r="B589" s="2"/>
-      <c r="C589" s="2"/>
-      <c r="D589" s="2"/>
-      <c r="E589" s="2"/>
-      <c r="F589" s="2"/>
-      <c r="G589" s="2"/>
-      <c r="H589" s="2"/>
-      <c r="I589" s="2"/>
-      <c r="J589" s="2"/>
-      <c r="K589" s="2"/>
-      <c r="L589" s="2"/>
-      <c r="M589" s="2"/>
-      <c r="N589" s="2"/>
-      <c r="O589" s="2"/>
-      <c r="P589" s="2"/>
+      <c r="A589" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B589" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D589" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E589" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F589" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G589" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="H589" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I589" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J589" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K589" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L589" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M589" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N589" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O589" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P589" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q589" s="2"/>
       <c r="R589" s="2"/>
       <c r="S589" s="2"/>
@@ -37798,51 +38975,113 @@
       <c r="Y589" s="2"/>
       <c r="Z589" s="2"/>
     </row>
-    <row r="590" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A590" s="2"/>
-      <c r="B590" s="2"/>
-      <c r="C590" s="2"/>
-      <c r="D590" s="2"/>
-      <c r="E590" s="2"/>
-      <c r="F590" s="2"/>
-      <c r="G590" s="2"/>
-      <c r="H590" s="2"/>
-      <c r="I590" s="2"/>
-      <c r="J590" s="2"/>
-      <c r="K590" s="2"/>
-      <c r="L590" s="2"/>
-      <c r="M590" s="2"/>
-      <c r="N590" s="2"/>
-      <c r="O590" s="2"/>
-      <c r="P590" s="2"/>
-      <c r="Q590" s="2"/>
-      <c r="R590" s="2"/>
-      <c r="S590" s="2"/>
-      <c r="T590" s="2"/>
-      <c r="U590" s="2"/>
-      <c r="V590" s="2"/>
-      <c r="W590" s="2"/>
-      <c r="X590" s="2"/>
-      <c r="Y590" s="2"/>
-      <c r="Z590" s="2"/>
+    <row r="590" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A590" s="10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B590" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C590" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D590" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E590" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F590" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G590" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H590" s="10" t="s">
+        <v>909</v>
+      </c>
+      <c r="I590" s="14"/>
+      <c r="J590" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="K590" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L590" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M590" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N590" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O590" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P590" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q590" s="8"/>
+      <c r="R590" s="8"/>
+      <c r="S590" s="8"/>
+      <c r="T590" s="8"/>
+      <c r="U590" s="8"/>
+      <c r="V590" s="8"/>
+      <c r="W590" s="8"/>
+      <c r="X590" s="8"/>
+      <c r="Y590" s="8"/>
+      <c r="Z590" s="8"/>
     </row>
     <row r="591" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A591" s="2"/>
-      <c r="B591" s="2"/>
-      <c r="C591" s="2"/>
-      <c r="D591" s="2"/>
-      <c r="E591" s="2"/>
-      <c r="F591" s="2"/>
-      <c r="G591" s="2"/>
-      <c r="H591" s="2"/>
-      <c r="I591" s="2"/>
-      <c r="J591" s="2"/>
-      <c r="K591" s="2"/>
-      <c r="L591" s="2"/>
-      <c r="M591" s="2"/>
-      <c r="N591" s="2"/>
-      <c r="O591" s="2"/>
-      <c r="P591" s="2"/>
+      <c r="A591" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B591" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D591" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E591" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F591" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G591" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H591" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I591" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J591" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K591" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L591" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M591" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N591" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O591" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P591" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q591" s="2"/>
       <c r="R591" s="2"/>
       <c r="S591" s="2"/>
@@ -37855,22 +39094,54 @@
       <c r="Z591" s="2"/>
     </row>
     <row r="592" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A592" s="2"/>
-      <c r="B592" s="2"/>
-      <c r="C592" s="2"/>
-      <c r="D592" s="2"/>
-      <c r="E592" s="2"/>
-      <c r="F592" s="2"/>
-      <c r="G592" s="2"/>
-      <c r="H592" s="2"/>
-      <c r="I592" s="2"/>
-      <c r="J592" s="2"/>
-      <c r="K592" s="2"/>
-      <c r="L592" s="2"/>
-      <c r="M592" s="2"/>
-      <c r="N592" s="2"/>
-      <c r="O592" s="2"/>
-      <c r="P592" s="2"/>
+      <c r="A592" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B592" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C592" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D592" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E592" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F592" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G592" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H592" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I592" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J592" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K592" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L592" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M592" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N592" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O592" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P592" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q592" s="2"/>
       <c r="R592" s="2"/>
       <c r="S592" s="2"/>
@@ -37883,22 +39154,54 @@
       <c r="Z592" s="2"/>
     </row>
     <row r="593" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A593" s="2"/>
-      <c r="B593" s="2"/>
-      <c r="C593" s="2"/>
-      <c r="D593" s="2"/>
-      <c r="E593" s="2"/>
-      <c r="F593" s="2"/>
-      <c r="G593" s="2"/>
-      <c r="H593" s="2"/>
-      <c r="I593" s="2"/>
-      <c r="J593" s="2"/>
-      <c r="K593" s="2"/>
-      <c r="L593" s="2"/>
-      <c r="M593" s="2"/>
-      <c r="N593" s="2"/>
-      <c r="O593" s="2"/>
-      <c r="P593" s="2"/>
+      <c r="A593" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B593" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D593" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E593" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F593" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G593" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I593" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J593" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K593" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L593" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M593" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N593" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O593" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P593" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="Q593" s="2"/>
       <c r="R593" s="2"/>
       <c r="S593" s="2"/>
@@ -37911,22 +39214,54 @@
       <c r="Z593" s="2"/>
     </row>
     <row r="594" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A594" s="2"/>
-      <c r="B594" s="2"/>
-      <c r="C594" s="2"/>
-      <c r="D594" s="2"/>
-      <c r="E594" s="2"/>
-      <c r="F594" s="2"/>
-      <c r="G594" s="2"/>
-      <c r="H594" s="2"/>
-      <c r="I594" s="2"/>
-      <c r="J594" s="2"/>
-      <c r="K594" s="2"/>
-      <c r="L594" s="2"/>
-      <c r="M594" s="2"/>
-      <c r="N594" s="2"/>
-      <c r="O594" s="2"/>
-      <c r="P594" s="2"/>
+      <c r="A594" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B594" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C594" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D594" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E594" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F594" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G594" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H594" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I594" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J594" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K594" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L594" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="M594" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="N594" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O594" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P594" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q594" s="2"/>
       <c r="R594" s="2"/>
       <c r="S594" s="2"/>
@@ -37939,22 +39274,54 @@
       <c r="Z594" s="2"/>
     </row>
     <row r="595" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A595" s="2"/>
-      <c r="B595" s="2"/>
-      <c r="C595" s="2"/>
-      <c r="D595" s="2"/>
-      <c r="E595" s="2"/>
-      <c r="F595" s="2"/>
-      <c r="G595" s="2"/>
-      <c r="H595" s="2"/>
-      <c r="I595" s="2"/>
-      <c r="J595" s="2"/>
-      <c r="K595" s="2"/>
-      <c r="L595" s="2"/>
-      <c r="M595" s="2"/>
-      <c r="N595" s="2"/>
-      <c r="O595" s="2"/>
-      <c r="P595" s="2"/>
+      <c r="A595" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D595" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E595" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F595" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G595" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H595" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I595" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J595" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K595" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L595" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M595" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N595" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="O595" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P595" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="Q595" s="2"/>
       <c r="R595" s="2"/>
       <c r="S595" s="2"/>
@@ -37967,22 +39334,52 @@
       <c r="Z595" s="2"/>
     </row>
     <row r="596" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A596" s="2"/>
-      <c r="B596" s="2"/>
-      <c r="C596" s="2"/>
-      <c r="D596" s="2"/>
-      <c r="E596" s="2"/>
-      <c r="F596" s="2"/>
-      <c r="G596" s="2"/>
-      <c r="H596" s="2"/>
-      <c r="I596" s="2"/>
-      <c r="J596" s="2"/>
-      <c r="K596" s="2"/>
-      <c r="L596" s="2"/>
-      <c r="M596" s="2"/>
-      <c r="N596" s="2"/>
-      <c r="O596" s="2"/>
-      <c r="P596" s="2"/>
+      <c r="A596" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B596" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C596" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D596" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E596" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F596" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G596" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H596" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I596" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J596" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K596" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L596" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="M596" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="N596" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O596" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P596" s="6"/>
       <c r="Q596" s="2"/>
       <c r="R596" s="2"/>
       <c r="S596" s="2"/>
@@ -37995,22 +39392,52 @@
       <c r="Z596" s="2"/>
     </row>
     <row r="597" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A597" s="2"/>
-      <c r="B597" s="2"/>
-      <c r="C597" s="2"/>
-      <c r="D597" s="2"/>
-      <c r="E597" s="2"/>
-      <c r="F597" s="2"/>
-      <c r="G597" s="2"/>
-      <c r="H597" s="2"/>
-      <c r="I597" s="2"/>
-      <c r="J597" s="2"/>
-      <c r="K597" s="2"/>
-      <c r="L597" s="2"/>
-      <c r="M597" s="2"/>
-      <c r="N597" s="2"/>
-      <c r="O597" s="2"/>
-      <c r="P597" s="2"/>
+      <c r="A597" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B597" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D597" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E597" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F597" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G597" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H597" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I597" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J597" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K597" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L597" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="M597" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="N597" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O597" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P597" s="6"/>
       <c r="Q597" s="2"/>
       <c r="R597" s="2"/>
       <c r="S597" s="2"/>
@@ -38023,22 +39450,54 @@
       <c r="Z597" s="2"/>
     </row>
     <row r="598" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A598" s="2"/>
-      <c r="B598" s="2"/>
-      <c r="C598" s="2"/>
-      <c r="D598" s="2"/>
-      <c r="E598" s="2"/>
-      <c r="F598" s="2"/>
-      <c r="G598" s="2"/>
-      <c r="H598" s="2"/>
-      <c r="I598" s="2"/>
-      <c r="J598" s="2"/>
-      <c r="K598" s="2"/>
-      <c r="L598" s="2"/>
-      <c r="M598" s="2"/>
-      <c r="N598" s="2"/>
-      <c r="O598" s="2"/>
-      <c r="P598" s="2"/>
+      <c r="A598" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B598" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C598" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D598" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E598" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F598" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G598" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H598" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I598" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J598" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K598" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L598" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M598" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N598" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O598" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P598" s="5" t="s">
+        <v>1134</v>
+      </c>
       <c r="Q598" s="2"/>
       <c r="R598" s="2"/>
       <c r="S598" s="2"/>
@@ -38051,22 +39510,52 @@
       <c r="Z598" s="2"/>
     </row>
     <row r="599" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A599" s="2"/>
-      <c r="B599" s="2"/>
-      <c r="C599" s="2"/>
-      <c r="D599" s="2"/>
-      <c r="E599" s="2"/>
-      <c r="F599" s="2"/>
-      <c r="G599" s="2"/>
-      <c r="H599" s="2"/>
-      <c r="I599" s="2"/>
-      <c r="J599" s="2"/>
-      <c r="K599" s="2"/>
-      <c r="L599" s="2"/>
-      <c r="M599" s="2"/>
-      <c r="N599" s="2"/>
-      <c r="O599" s="2"/>
-      <c r="P599" s="2"/>
+      <c r="A599" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B599" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D599" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E599" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F599" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G599" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H599" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I599" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J599" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K599" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L599" s="6"/>
+      <c r="M599" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="N599" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O599" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P599" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="Q599" s="2"/>
       <c r="R599" s="2"/>
       <c r="S599" s="2"/>
@@ -38079,22 +39568,54 @@
       <c r="Z599" s="2"/>
     </row>
     <row r="600" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A600" s="2"/>
-      <c r="B600" s="2"/>
-      <c r="C600" s="2"/>
-      <c r="D600" s="2"/>
-      <c r="E600" s="2"/>
-      <c r="F600" s="2"/>
-      <c r="G600" s="2"/>
-      <c r="H600" s="2"/>
-      <c r="I600" s="2"/>
-      <c r="J600" s="2"/>
-      <c r="K600" s="2"/>
-      <c r="L600" s="2"/>
-      <c r="M600" s="2"/>
-      <c r="N600" s="2"/>
-      <c r="O600" s="2"/>
-      <c r="P600" s="2"/>
+      <c r="A600" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B600" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D600" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E600" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F600" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G600" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H600" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I600" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J600" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K600" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L600" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="M600" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N600" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O600" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P600" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="Q600" s="2"/>
       <c r="R600" s="2"/>
       <c r="S600" s="2"/>
@@ -38107,22 +39628,52 @@
       <c r="Z600" s="2"/>
     </row>
     <row r="601" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A601" s="2"/>
-      <c r="B601" s="2"/>
-      <c r="C601" s="2"/>
-      <c r="D601" s="2"/>
-      <c r="E601" s="2"/>
-      <c r="F601" s="2"/>
-      <c r="G601" s="2"/>
-      <c r="H601" s="2"/>
-      <c r="I601" s="2"/>
-      <c r="J601" s="2"/>
-      <c r="K601" s="2"/>
-      <c r="L601" s="2"/>
-      <c r="M601" s="2"/>
-      <c r="N601" s="2"/>
-      <c r="O601" s="2"/>
-      <c r="P601" s="2"/>
+      <c r="A601" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B601" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D601" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E601" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F601" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G601" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H601" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I601" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J601" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K601" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L601" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="M601" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="N601" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="O601" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="P601" s="6"/>
       <c r="Q601" s="2"/>
       <c r="R601" s="2"/>
       <c r="S601" s="2"/>
@@ -38134,33 +39685,62 @@
       <c r="Y601" s="2"/>
       <c r="Z601" s="2"/>
     </row>
-    <row r="602" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A602" s="2"/>
-      <c r="B602" s="2"/>
-      <c r="C602" s="2"/>
-      <c r="D602" s="2"/>
-      <c r="E602" s="2"/>
-      <c r="F602" s="2"/>
-      <c r="G602" s="2"/>
-      <c r="H602" s="2"/>
-      <c r="I602" s="2"/>
-      <c r="J602" s="2"/>
-      <c r="K602" s="2"/>
-      <c r="L602" s="2"/>
-      <c r="M602" s="2"/>
-      <c r="N602" s="2"/>
-      <c r="O602" s="2"/>
-      <c r="P602" s="2"/>
-      <c r="Q602" s="2"/>
-      <c r="R602" s="2"/>
-      <c r="S602" s="2"/>
-      <c r="T602" s="2"/>
-      <c r="U602" s="2"/>
-      <c r="V602" s="2"/>
-      <c r="W602" s="2"/>
-      <c r="X602" s="2"/>
-      <c r="Y602" s="2"/>
-      <c r="Z602" s="2"/>
+    <row r="602" spans="1:26" s="12" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+      <c r="A602" s="10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B602" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C602" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D602" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E602" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F602" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G602" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H602" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I602" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J602" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K602" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L602" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="M602" s="10" t="s">
+        <v>1142</v>
+      </c>
+      <c r="N602" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="O602" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q602" s="8"/>
+      <c r="R602" s="8"/>
+      <c r="S602" s="8"/>
+      <c r="T602" s="8"/>
+      <c r="U602" s="8"/>
+      <c r="V602" s="8"/>
+      <c r="W602" s="8"/>
+      <c r="X602" s="8"/>
+      <c r="Y602" s="8"/>
+      <c r="Z602" s="8"/>
     </row>
     <row r="603" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A603" s="2"/>

--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/insightsgraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F0D365-B697-0942-8001-1C00CE8C8FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3FEDC3-7946-CA40-88E0-D258C2E7F907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sweets" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Master!$A$1:$P$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Master!$A$1:$P$602</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10620" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10622" uniqueCount="1143">
   <si>
     <t>Customer Name</t>
   </si>
@@ -28752,7 +28752,9 @@
       <c r="B418" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C418" s="6"/>
+      <c r="C418" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D418" s="5" t="s">
         <v>97</v>
       </c>
@@ -29348,7 +29350,9 @@
       <c r="B428" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C428" s="6"/>
+      <c r="C428" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D428" s="5" t="s">
         <v>237</v>
       </c>
@@ -50803,7 +50807,7 @@
       <c r="Z997" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P486" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P602" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/insightsgraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3FEDC3-7946-CA40-88E0-D258C2E7F907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF562B5-50B8-9A40-8894-21F5F51B7F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10622" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11922" uniqueCount="1247">
   <si>
     <t>Customer Name</t>
   </si>
@@ -3467,6 +3467,318 @@
   </si>
   <si>
     <t>Haldiram's, </t>
+  </si>
+  <si>
+    <t>Mohammed Tanveer</t>
+  </si>
+  <si>
+    <t>SACHINKUMAR DEVAIYA</t>
+  </si>
+  <si>
+    <t>Simranjit kaur</t>
+  </si>
+  <si>
+    <t>Pooja khadgi</t>
+  </si>
+  <si>
+    <t>Varun </t>
+  </si>
+  <si>
+    <t>Shilajit Mondal</t>
+  </si>
+  <si>
+    <t>Ravula vijayendra</t>
+  </si>
+  <si>
+    <t>Aryan jaiswal</t>
+  </si>
+  <si>
+    <t>Sudatta Kar</t>
+  </si>
+  <si>
+    <t>Hanif divekar</t>
+  </si>
+  <si>
+    <t>Shivam Kumar</t>
+  </si>
+  <si>
+    <t>Joan rosario</t>
+  </si>
+  <si>
+    <t>Vandana sukhwal</t>
+  </si>
+  <si>
+    <t>muhasin salam</t>
+  </si>
+  <si>
+    <t>Rachit Singh</t>
+  </si>
+  <si>
+    <t>Rakesh sahoo</t>
+  </si>
+  <si>
+    <t>Akshay kumar</t>
+  </si>
+  <si>
+    <t>Vinayak Dubey</t>
+  </si>
+  <si>
+    <t>Subodh waghmare</t>
+  </si>
+  <si>
+    <t>Hiren oza</t>
+  </si>
+  <si>
+    <t>Sagnika chowdhury</t>
+  </si>
+  <si>
+    <t>honey </t>
+  </si>
+  <si>
+    <t>GURNOOR CHOPRA</t>
+  </si>
+  <si>
+    <t>Avinash singh</t>
+  </si>
+  <si>
+    <t>Amir Baig</t>
+  </si>
+  <si>
+    <t>Jonsi Dalal</t>
+  </si>
+  <si>
+    <t>Anubhuti Mittal</t>
+  </si>
+  <si>
+    <t>Vishesh Tripathi</t>
+  </si>
+  <si>
+    <t>R geethanjali</t>
+  </si>
+  <si>
+    <t>Rohan k</t>
+  </si>
+  <si>
+    <t>Taniya ghosh</t>
+  </si>
+  <si>
+    <t>Suraksha Srikanth Poojary</t>
+  </si>
+  <si>
+    <t>Prema pradeep</t>
+  </si>
+  <si>
+    <t>Lotus agro projects</t>
+  </si>
+  <si>
+    <t>Sumit mondal</t>
+  </si>
+  <si>
+    <t>Chiku sahoo</t>
+  </si>
+  <si>
+    <t>Mayank yadav</t>
+  </si>
+  <si>
+    <t>Gouthami cherry</t>
+  </si>
+  <si>
+    <t>Nityam soni</t>
+  </si>
+  <si>
+    <t>Vitthal tukaram phalke</t>
+  </si>
+  <si>
+    <t>Gohil Vinayak jigneshbhai</t>
+  </si>
+  <si>
+    <t>Apoorvi gupta</t>
+  </si>
+  <si>
+    <t>Bappa nandi</t>
+  </si>
+  <si>
+    <t>Ghazal mittal</t>
+  </si>
+  <si>
+    <t>Rani Khatun</t>
+  </si>
+  <si>
+    <t>Hemal Sanghvi</t>
+  </si>
+  <si>
+    <t>Sk Asifuddin</t>
+  </si>
+  <si>
+    <t>Astha Singh</t>
+  </si>
+  <si>
+    <t>Pragya wadhawan</t>
+  </si>
+  <si>
+    <t>Kedar mahajan</t>
+  </si>
+  <si>
+    <t>Monashree Hitesh Borikar</t>
+  </si>
+  <si>
+    <t>Barkha arlekar</t>
+  </si>
+  <si>
+    <t>Sangram keshari podhiary</t>
+  </si>
+  <si>
+    <t>Akshata J</t>
+  </si>
+  <si>
+    <t>Garima goyal</t>
+  </si>
+  <si>
+    <t>harshvardhan Chaudhary</t>
+  </si>
+  <si>
+    <t>subrata maity</t>
+  </si>
+  <si>
+    <t>Aniket kumar</t>
+  </si>
+  <si>
+    <t>Renuka Pandey</t>
+  </si>
+  <si>
+    <t>Vishal </t>
+  </si>
+  <si>
+    <t>Suchitra </t>
+  </si>
+  <si>
+    <t>Parul Kisor Shah</t>
+  </si>
+  <si>
+    <t>Saranyaprakash saranyaprakash</t>
+  </si>
+  <si>
+    <t>Chaitali Chanda</t>
+  </si>
+  <si>
+    <t>Shreya koppallar</t>
+  </si>
+  <si>
+    <t>PawanJit singh</t>
+  </si>
+  <si>
+    <t>Nachiket Vyawahare</t>
+  </si>
+  <si>
+    <t>Muskan chauhan</t>
+  </si>
+  <si>
+    <t>Shivam Gupta</t>
+  </si>
+  <si>
+    <t>Kruti shah</t>
+  </si>
+  <si>
+    <t>Saicharan </t>
+  </si>
+  <si>
+    <t>Ronit walecha</t>
+  </si>
+  <si>
+    <t>B Gokulnaath</t>
+  </si>
+  <si>
+    <t>komal khatri</t>
+  </si>
+  <si>
+    <t>Anushka Prajapat</t>
+  </si>
+  <si>
+    <t>Varsha Jain</t>
+  </si>
+  <si>
+    <t>Got it as a gift hamper</t>
+  </si>
+  <si>
+    <t>collaboration</t>
+  </si>
+  <si>
+    <t>While watching content, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>While traveling, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>To curb my chatpata cravings, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>While watching content, When I'm bored, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>Cx bought it for someone else</t>
+  </si>
+  <si>
+    <t>After meals, When I'm bored, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>During work/study breaks, When I'm bored, To curb my chatpata cravings, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>After meals, When I'm bored, While traveling</t>
+  </si>
+  <si>
+    <t>During work/study breaks, While watching content, While traveling</t>
+  </si>
+  <si>
+    <t>During work/study breaks, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>During work/study breaks, When I'm bored, To curb my chatpata cravings, While traveling, Whenever the customer feels like</t>
+  </si>
+  <si>
+    <t>Gifting purpose</t>
+  </si>
+  <si>
+    <t>Candy, Churan</t>
+  </si>
+  <si>
+    <t>Candy, Chocolate</t>
+  </si>
+  <si>
+    <t>Chapati cravings, Just wanted to try</t>
+  </si>
+  <si>
+    <t>Unique format, Better Ingredients, Fun to eat</t>
+  </si>
+  <si>
+    <t>Unique format, Better Ingredients, Nostalgic vibes, Guilt free snacking, Fun to eat</t>
+  </si>
+  <si>
+    <t>Fun to eat, Just wanted to try</t>
+  </si>
+  <si>
+    <t>Call got disconnected in the middle</t>
+  </si>
+  <si>
+    <t>Tamrind Pop, Chocolate</t>
+  </si>
+  <si>
+    <t>Better Ingredients, Guilt free snacking, Fun to eat</t>
+  </si>
+  <si>
+    <t>A healthy snack</t>
+  </si>
+  <si>
+    <t>Better Ingredients, Guilt free snacking, Just wanted to try</t>
+  </si>
+  <si>
+    <t>Better Ingredients, Good packaging</t>
+  </si>
+  <si>
+    <t>Good packing</t>
+  </si>
+  <si>
+    <t>Healthy snack</t>
   </si>
 </sst>
 </file>
@@ -39747,22 +40059,54 @@
       <c r="Z602" s="8"/>
     </row>
     <row r="603" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A603" s="2"/>
-      <c r="B603" s="2"/>
-      <c r="C603" s="2"/>
-      <c r="D603" s="2"/>
-      <c r="E603" s="2"/>
-      <c r="F603" s="2"/>
-      <c r="G603" s="2"/>
-      <c r="H603" s="2"/>
-      <c r="I603" s="2"/>
-      <c r="J603" s="2"/>
-      <c r="K603" s="2"/>
-      <c r="L603" s="2"/>
-      <c r="M603" s="2"/>
-      <c r="N603" s="2"/>
-      <c r="O603" s="2"/>
-      <c r="P603" s="2"/>
+      <c r="A603" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B603" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D603" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E603" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F603" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G603" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H603" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I603" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J603" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K603" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L603" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M603" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N603" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O603" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P603" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q603" s="2"/>
       <c r="R603" s="2"/>
       <c r="S603" s="2"/>
@@ -39775,22 +40119,54 @@
       <c r="Z603" s="2"/>
     </row>
     <row r="604" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A604" s="2"/>
-      <c r="B604" s="2"/>
-      <c r="C604" s="2"/>
-      <c r="D604" s="2"/>
-      <c r="E604" s="2"/>
-      <c r="F604" s="2"/>
-      <c r="G604" s="2"/>
-      <c r="H604" s="2"/>
-      <c r="I604" s="2"/>
-      <c r="J604" s="2"/>
-      <c r="K604" s="2"/>
-      <c r="L604" s="2"/>
-      <c r="M604" s="2"/>
-      <c r="N604" s="2"/>
-      <c r="O604" s="2"/>
-      <c r="P604" s="2"/>
+      <c r="A604" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B604" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D604" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E604" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F604" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G604" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H604" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I604" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J604" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K604" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L604" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M604" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N604" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O604" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P604" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q604" s="2"/>
       <c r="R604" s="2"/>
       <c r="S604" s="2"/>
@@ -39803,22 +40179,54 @@
       <c r="Z604" s="2"/>
     </row>
     <row r="605" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A605" s="2"/>
-      <c r="B605" s="2"/>
-      <c r="C605" s="2"/>
-      <c r="D605" s="2"/>
-      <c r="E605" s="2"/>
-      <c r="F605" s="2"/>
-      <c r="G605" s="2"/>
-      <c r="H605" s="2"/>
-      <c r="I605" s="2"/>
-      <c r="J605" s="2"/>
-      <c r="K605" s="2"/>
-      <c r="L605" s="2"/>
-      <c r="M605" s="2"/>
-      <c r="N605" s="2"/>
-      <c r="O605" s="2"/>
-      <c r="P605" s="2"/>
+      <c r="A605" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B605" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D605" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E605" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F605" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G605" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H605" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I605" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J605" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K605" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L605" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M605" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N605" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O605" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P605" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q605" s="2"/>
       <c r="R605" s="2"/>
       <c r="S605" s="2"/>
@@ -39831,22 +40239,48 @@
       <c r="Z605" s="2"/>
     </row>
     <row r="606" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A606" s="2"/>
-      <c r="B606" s="2"/>
-      <c r="C606" s="2"/>
-      <c r="D606" s="2"/>
-      <c r="E606" s="2"/>
-      <c r="F606" s="2"/>
-      <c r="G606" s="2"/>
-      <c r="H606" s="2"/>
-      <c r="I606" s="2"/>
-      <c r="J606" s="2"/>
-      <c r="K606" s="2"/>
-      <c r="L606" s="2"/>
-      <c r="M606" s="2"/>
-      <c r="N606" s="2"/>
-      <c r="O606" s="2"/>
-      <c r="P606" s="2"/>
+      <c r="A606" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B606" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D606" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E606" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F606" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G606" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H606" s="6"/>
+      <c r="I606" s="6"/>
+      <c r="J606" s="6"/>
+      <c r="K606" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L606" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M606" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N606" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O606" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P606" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q606" s="2"/>
       <c r="R606" s="2"/>
       <c r="S606" s="2"/>
@@ -39859,22 +40293,54 @@
       <c r="Z606" s="2"/>
     </row>
     <row r="607" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A607" s="2"/>
-      <c r="B607" s="2"/>
-      <c r="C607" s="2"/>
-      <c r="D607" s="2"/>
-      <c r="E607" s="2"/>
-      <c r="F607" s="2"/>
-      <c r="G607" s="2"/>
-      <c r="H607" s="2"/>
-      <c r="I607" s="2"/>
-      <c r="J607" s="2"/>
-      <c r="K607" s="2"/>
-      <c r="L607" s="2"/>
-      <c r="M607" s="2"/>
-      <c r="N607" s="2"/>
-      <c r="O607" s="2"/>
-      <c r="P607" s="2"/>
+      <c r="A607" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B607" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D607" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E607" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F607" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G607" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H607" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I607" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J607" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K607" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L607" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M607" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N607" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O607" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P607" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q607" s="2"/>
       <c r="R607" s="2"/>
       <c r="S607" s="2"/>
@@ -39887,22 +40353,52 @@
       <c r="Z607" s="2"/>
     </row>
     <row r="608" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A608" s="2"/>
-      <c r="B608" s="2"/>
-      <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
-      <c r="E608" s="2"/>
-      <c r="F608" s="2"/>
-      <c r="G608" s="2"/>
-      <c r="H608" s="2"/>
-      <c r="I608" s="2"/>
-      <c r="J608" s="2"/>
-      <c r="K608" s="2"/>
-      <c r="L608" s="2"/>
-      <c r="M608" s="2"/>
-      <c r="N608" s="2"/>
-      <c r="O608" s="2"/>
-      <c r="P608" s="2"/>
+      <c r="A608" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B608" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D608" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E608" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F608" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G608" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H608" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I608" s="6"/>
+      <c r="J608" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K608" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L608" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M608" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N608" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O608" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P608" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q608" s="2"/>
       <c r="R608" s="2"/>
       <c r="S608" s="2"/>
@@ -39915,22 +40411,52 @@
       <c r="Z608" s="2"/>
     </row>
     <row r="609" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A609" s="2"/>
-      <c r="B609" s="2"/>
-      <c r="C609" s="2"/>
-      <c r="D609" s="2"/>
-      <c r="E609" s="2"/>
-      <c r="F609" s="2"/>
-      <c r="G609" s="2"/>
-      <c r="H609" s="2"/>
-      <c r="I609" s="2"/>
-      <c r="J609" s="2"/>
-      <c r="K609" s="2"/>
-      <c r="L609" s="2"/>
-      <c r="M609" s="2"/>
-      <c r="N609" s="2"/>
-      <c r="O609" s="2"/>
-      <c r="P609" s="2"/>
+      <c r="A609" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B609" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D609" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E609" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F609" s="6"/>
+      <c r="G609" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H609" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I609" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J609" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K609" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L609" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M609" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N609" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O609" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P609" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q609" s="2"/>
       <c r="R609" s="2"/>
       <c r="S609" s="2"/>
@@ -39943,22 +40469,54 @@
       <c r="Z609" s="2"/>
     </row>
     <row r="610" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A610" s="2"/>
-      <c r="B610" s="2"/>
-      <c r="C610" s="2"/>
-      <c r="D610" s="2"/>
-      <c r="E610" s="2"/>
-      <c r="F610" s="2"/>
-      <c r="G610" s="2"/>
-      <c r="H610" s="2"/>
-      <c r="I610" s="2"/>
-      <c r="J610" s="2"/>
-      <c r="K610" s="2"/>
-      <c r="L610" s="2"/>
-      <c r="M610" s="2"/>
-      <c r="N610" s="2"/>
-      <c r="O610" s="2"/>
-      <c r="P610" s="2"/>
+      <c r="A610" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B610" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D610" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E610" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F610" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G610" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H610" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I610" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J610" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K610" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L610" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M610" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N610" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O610" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P610" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q610" s="2"/>
       <c r="R610" s="2"/>
       <c r="S610" s="2"/>
@@ -39971,22 +40529,52 @@
       <c r="Z610" s="2"/>
     </row>
     <row r="611" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A611" s="2"/>
-      <c r="B611" s="2"/>
-      <c r="C611" s="2"/>
-      <c r="D611" s="2"/>
-      <c r="E611" s="2"/>
-      <c r="F611" s="2"/>
-      <c r="G611" s="2"/>
-      <c r="H611" s="2"/>
-      <c r="I611" s="2"/>
-      <c r="J611" s="2"/>
-      <c r="K611" s="2"/>
-      <c r="L611" s="2"/>
-      <c r="M611" s="2"/>
-      <c r="N611" s="2"/>
-      <c r="O611" s="2"/>
-      <c r="P611" s="2"/>
+      <c r="A611" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B611" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D611" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E611" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F611" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G611" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H611" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I611" s="6"/>
+      <c r="J611" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K611" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L611" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M611" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N611" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O611" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P611" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q611" s="2"/>
       <c r="R611" s="2"/>
       <c r="S611" s="2"/>
@@ -39999,22 +40587,54 @@
       <c r="Z611" s="2"/>
     </row>
     <row r="612" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A612" s="2"/>
-      <c r="B612" s="2"/>
-      <c r="C612" s="2"/>
-      <c r="D612" s="2"/>
-      <c r="E612" s="2"/>
-      <c r="F612" s="2"/>
-      <c r="G612" s="2"/>
-      <c r="H612" s="2"/>
-      <c r="I612" s="2"/>
-      <c r="J612" s="2"/>
-      <c r="K612" s="2"/>
-      <c r="L612" s="2"/>
-      <c r="M612" s="2"/>
-      <c r="N612" s="2"/>
-      <c r="O612" s="2"/>
-      <c r="P612" s="2"/>
+      <c r="A612" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B612" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D612" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E612" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F612" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G612" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H612" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I612" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J612" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K612" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L612" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M612" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N612" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O612" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P612" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q612" s="2"/>
       <c r="R612" s="2"/>
       <c r="S612" s="2"/>
@@ -40027,22 +40647,54 @@
       <c r="Z612" s="2"/>
     </row>
     <row r="613" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A613" s="2"/>
-      <c r="B613" s="2"/>
-      <c r="C613" s="2"/>
-      <c r="D613" s="2"/>
-      <c r="E613" s="2"/>
-      <c r="F613" s="2"/>
-      <c r="G613" s="2"/>
-      <c r="H613" s="2"/>
-      <c r="I613" s="2"/>
-      <c r="J613" s="2"/>
-      <c r="K613" s="2"/>
-      <c r="L613" s="2"/>
-      <c r="M613" s="2"/>
-      <c r="N613" s="2"/>
-      <c r="O613" s="2"/>
-      <c r="P613" s="2"/>
+      <c r="A613" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B613" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D613" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E613" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F613" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G613" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H613" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I613" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J613" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="K613" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L613" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M613" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N613" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O613" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P613" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q613" s="2"/>
       <c r="R613" s="2"/>
       <c r="S613" s="2"/>
@@ -40055,22 +40707,52 @@
       <c r="Z613" s="2"/>
     </row>
     <row r="614" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A614" s="2"/>
-      <c r="B614" s="2"/>
-      <c r="C614" s="2"/>
-      <c r="D614" s="2"/>
-      <c r="E614" s="2"/>
-      <c r="F614" s="2"/>
-      <c r="G614" s="2"/>
-      <c r="H614" s="2"/>
-      <c r="I614" s="2"/>
-      <c r="J614" s="2"/>
-      <c r="K614" s="2"/>
-      <c r="L614" s="2"/>
-      <c r="M614" s="2"/>
-      <c r="N614" s="2"/>
-      <c r="O614" s="2"/>
-      <c r="P614" s="2"/>
+      <c r="A614" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B614" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D614" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E614" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F614" s="6"/>
+      <c r="G614" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H614" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I614" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J614" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K614" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L614" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M614" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N614" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O614" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P614" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q614" s="2"/>
       <c r="R614" s="2"/>
       <c r="S614" s="2"/>
@@ -40083,22 +40765,54 @@
       <c r="Z614" s="2"/>
     </row>
     <row r="615" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A615" s="2"/>
-      <c r="B615" s="2"/>
-      <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
-      <c r="E615" s="2"/>
-      <c r="F615" s="2"/>
-      <c r="G615" s="2"/>
-      <c r="H615" s="2"/>
-      <c r="I615" s="2"/>
-      <c r="J615" s="2"/>
-      <c r="K615" s="2"/>
-      <c r="L615" s="2"/>
-      <c r="M615" s="2"/>
-      <c r="N615" s="2"/>
-      <c r="O615" s="2"/>
-      <c r="P615" s="2"/>
+      <c r="A615" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B615" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D615" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E615" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F615" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G615" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H615" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I615" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J615" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="K615" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L615" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M615" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N615" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O615" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P615" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q615" s="2"/>
       <c r="R615" s="2"/>
       <c r="S615" s="2"/>
@@ -40111,22 +40825,54 @@
       <c r="Z615" s="2"/>
     </row>
     <row r="616" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A616" s="2"/>
-      <c r="B616" s="2"/>
-      <c r="C616" s="2"/>
-      <c r="D616" s="2"/>
-      <c r="E616" s="2"/>
-      <c r="F616" s="2"/>
-      <c r="G616" s="2"/>
-      <c r="H616" s="2"/>
-      <c r="I616" s="2"/>
-      <c r="J616" s="2"/>
-      <c r="K616" s="2"/>
-      <c r="L616" s="2"/>
-      <c r="M616" s="2"/>
-      <c r="N616" s="2"/>
-      <c r="O616" s="2"/>
-      <c r="P616" s="2"/>
+      <c r="A616" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B616" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D616" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E616" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F616" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G616" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H616" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I616" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J616" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K616" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L616" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M616" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N616" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O616" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P616" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q616" s="2"/>
       <c r="R616" s="2"/>
       <c r="S616" s="2"/>
@@ -40139,22 +40885,54 @@
       <c r="Z616" s="2"/>
     </row>
     <row r="617" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A617" s="2"/>
-      <c r="B617" s="2"/>
-      <c r="C617" s="2"/>
-      <c r="D617" s="2"/>
-      <c r="E617" s="2"/>
-      <c r="F617" s="2"/>
-      <c r="G617" s="2"/>
-      <c r="H617" s="2"/>
-      <c r="I617" s="2"/>
-      <c r="J617" s="2"/>
-      <c r="K617" s="2"/>
-      <c r="L617" s="2"/>
-      <c r="M617" s="2"/>
-      <c r="N617" s="2"/>
-      <c r="O617" s="2"/>
-      <c r="P617" s="2"/>
+      <c r="A617" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B617" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D617" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F617" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G617" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H617" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I617" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J617" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K617" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L617" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M617" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N617" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O617" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P617" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q617" s="2"/>
       <c r="R617" s="2"/>
       <c r="S617" s="2"/>
@@ -40167,22 +40945,54 @@
       <c r="Z617" s="2"/>
     </row>
     <row r="618" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A618" s="2"/>
-      <c r="B618" s="2"/>
-      <c r="C618" s="2"/>
-      <c r="D618" s="2"/>
-      <c r="E618" s="2"/>
-      <c r="F618" s="2"/>
-      <c r="G618" s="2"/>
-      <c r="H618" s="2"/>
-      <c r="I618" s="2"/>
-      <c r="J618" s="2"/>
-      <c r="K618" s="2"/>
-      <c r="L618" s="2"/>
-      <c r="M618" s="2"/>
-      <c r="N618" s="2"/>
-      <c r="O618" s="2"/>
-      <c r="P618" s="2"/>
+      <c r="A618" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B618" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D618" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E618" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F618" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G618" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H618" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I618" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J618" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K618" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L618" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M618" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N618" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O618" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P618" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q618" s="2"/>
       <c r="R618" s="2"/>
       <c r="S618" s="2"/>
@@ -40195,22 +41005,54 @@
       <c r="Z618" s="2"/>
     </row>
     <row r="619" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A619" s="2"/>
-      <c r="B619" s="2"/>
-      <c r="C619" s="2"/>
-      <c r="D619" s="2"/>
-      <c r="E619" s="2"/>
-      <c r="F619" s="2"/>
-      <c r="G619" s="2"/>
-      <c r="H619" s="2"/>
-      <c r="I619" s="2"/>
-      <c r="J619" s="2"/>
-      <c r="K619" s="2"/>
-      <c r="L619" s="2"/>
-      <c r="M619" s="2"/>
-      <c r="N619" s="2"/>
-      <c r="O619" s="2"/>
-      <c r="P619" s="2"/>
+      <c r="A619" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B619" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D619" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E619" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F619" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G619" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H619" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I619" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J619" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K619" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P619" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q619" s="2"/>
       <c r="R619" s="2"/>
       <c r="S619" s="2"/>
@@ -40223,22 +41065,54 @@
       <c r="Z619" s="2"/>
     </row>
     <row r="620" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A620" s="2"/>
-      <c r="B620" s="2"/>
-      <c r="C620" s="2"/>
-      <c r="D620" s="2"/>
-      <c r="E620" s="2"/>
-      <c r="F620" s="2"/>
-      <c r="G620" s="2"/>
-      <c r="H620" s="2"/>
-      <c r="I620" s="2"/>
-      <c r="J620" s="2"/>
-      <c r="K620" s="2"/>
-      <c r="L620" s="2"/>
-      <c r="M620" s="2"/>
-      <c r="N620" s="2"/>
-      <c r="O620" s="2"/>
-      <c r="P620" s="2"/>
+      <c r="A620" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B620" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D620" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E620" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F620" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G620" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H620" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I620" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J620" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="K620" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L620" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M620" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N620" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O620" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P620" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q620" s="2"/>
       <c r="R620" s="2"/>
       <c r="S620" s="2"/>
@@ -40251,22 +41125,54 @@
       <c r="Z620" s="2"/>
     </row>
     <row r="621" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A621" s="2"/>
-      <c r="B621" s="2"/>
-      <c r="C621" s="2"/>
-      <c r="D621" s="2"/>
-      <c r="E621" s="2"/>
-      <c r="F621" s="2"/>
-      <c r="G621" s="2"/>
-      <c r="H621" s="2"/>
-      <c r="I621" s="2"/>
-      <c r="J621" s="2"/>
-      <c r="K621" s="2"/>
-      <c r="L621" s="2"/>
-      <c r="M621" s="2"/>
-      <c r="N621" s="2"/>
-      <c r="O621" s="2"/>
-      <c r="P621" s="2"/>
+      <c r="A621" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B621" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D621" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E621" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F621" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G621" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H621" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I621" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J621" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="K621" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L621" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M621" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N621" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O621" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P621" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q621" s="2"/>
       <c r="R621" s="2"/>
       <c r="S621" s="2"/>
@@ -40279,22 +41185,54 @@
       <c r="Z621" s="2"/>
     </row>
     <row r="622" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A622" s="2"/>
-      <c r="B622" s="2"/>
-      <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
-      <c r="E622" s="2"/>
-      <c r="F622" s="2"/>
-      <c r="G622" s="2"/>
-      <c r="H622" s="2"/>
-      <c r="I622" s="2"/>
-      <c r="J622" s="2"/>
-      <c r="K622" s="2"/>
-      <c r="L622" s="2"/>
-      <c r="M622" s="2"/>
-      <c r="N622" s="2"/>
-      <c r="O622" s="2"/>
-      <c r="P622" s="2"/>
+      <c r="A622" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B622" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D622" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E622" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F622" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G622" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H622" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I622" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J622" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K622" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L622" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M622" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N622" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O622" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P622" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q622" s="2"/>
       <c r="R622" s="2"/>
       <c r="S622" s="2"/>
@@ -40307,22 +41245,54 @@
       <c r="Z622" s="2"/>
     </row>
     <row r="623" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A623" s="2"/>
-      <c r="B623" s="2"/>
-      <c r="C623" s="2"/>
-      <c r="D623" s="2"/>
-      <c r="E623" s="2"/>
-      <c r="F623" s="2"/>
-      <c r="G623" s="2"/>
-      <c r="H623" s="2"/>
-      <c r="I623" s="2"/>
-      <c r="J623" s="2"/>
-      <c r="K623" s="2"/>
-      <c r="L623" s="2"/>
-      <c r="M623" s="2"/>
-      <c r="N623" s="2"/>
-      <c r="O623" s="2"/>
-      <c r="P623" s="2"/>
+      <c r="A623" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B623" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D623" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E623" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F623" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G623" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H623" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I623" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J623" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K623" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L623" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M623" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N623" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O623" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P623" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q623" s="2"/>
       <c r="R623" s="2"/>
       <c r="S623" s="2"/>
@@ -40335,22 +41305,54 @@
       <c r="Z623" s="2"/>
     </row>
     <row r="624" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A624" s="2"/>
-      <c r="B624" s="2"/>
-      <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
-      <c r="E624" s="2"/>
-      <c r="F624" s="2"/>
-      <c r="G624" s="2"/>
-      <c r="H624" s="2"/>
-      <c r="I624" s="2"/>
-      <c r="J624" s="2"/>
-      <c r="K624" s="2"/>
-      <c r="L624" s="2"/>
-      <c r="M624" s="2"/>
-      <c r="N624" s="2"/>
-      <c r="O624" s="2"/>
-      <c r="P624" s="2"/>
+      <c r="A624" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B624" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D624" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E624" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F624" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G624" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H624" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I624" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J624" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K624" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L624" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M624" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N624" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O624" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P624" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q624" s="2"/>
       <c r="R624" s="2"/>
       <c r="S624" s="2"/>
@@ -40363,22 +41365,54 @@
       <c r="Z624" s="2"/>
     </row>
     <row r="625" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A625" s="2"/>
-      <c r="B625" s="2"/>
-      <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
-      <c r="E625" s="2"/>
-      <c r="F625" s="2"/>
-      <c r="G625" s="2"/>
-      <c r="H625" s="2"/>
-      <c r="I625" s="2"/>
-      <c r="J625" s="2"/>
-      <c r="K625" s="2"/>
-      <c r="L625" s="2"/>
-      <c r="M625" s="2"/>
-      <c r="N625" s="2"/>
-      <c r="O625" s="2"/>
-      <c r="P625" s="2"/>
+      <c r="A625" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B625" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D625" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F625" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G625" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H625" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I625" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J625" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K625" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L625" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M625" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N625" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O625" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P625" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q625" s="2"/>
       <c r="R625" s="2"/>
       <c r="S625" s="2"/>
@@ -40391,22 +41425,54 @@
       <c r="Z625" s="2"/>
     </row>
     <row r="626" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A626" s="2"/>
-      <c r="B626" s="2"/>
-      <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
-      <c r="E626" s="2"/>
-      <c r="F626" s="2"/>
-      <c r="G626" s="2"/>
-      <c r="H626" s="2"/>
-      <c r="I626" s="2"/>
-      <c r="J626" s="2"/>
-      <c r="K626" s="2"/>
-      <c r="L626" s="2"/>
-      <c r="M626" s="2"/>
-      <c r="N626" s="2"/>
-      <c r="O626" s="2"/>
-      <c r="P626" s="2"/>
+      <c r="A626" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B626" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D626" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E626" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F626" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G626" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H626" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I626" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J626" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K626" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L626" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M626" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N626" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O626" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P626" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q626" s="2"/>
       <c r="R626" s="2"/>
       <c r="S626" s="2"/>
@@ -40419,22 +41485,54 @@
       <c r="Z626" s="2"/>
     </row>
     <row r="627" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A627" s="2"/>
-      <c r="B627" s="2"/>
-      <c r="C627" s="2"/>
-      <c r="D627" s="2"/>
-      <c r="E627" s="2"/>
-      <c r="F627" s="2"/>
-      <c r="G627" s="2"/>
-      <c r="H627" s="2"/>
-      <c r="I627" s="2"/>
-      <c r="J627" s="2"/>
-      <c r="K627" s="2"/>
-      <c r="L627" s="2"/>
-      <c r="M627" s="2"/>
-      <c r="N627" s="2"/>
-      <c r="O627" s="2"/>
-      <c r="P627" s="2"/>
+      <c r="A627" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B627" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D627" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F627" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G627" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H627" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I627" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J627" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K627" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L627" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M627" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N627" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O627" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P627" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q627" s="2"/>
       <c r="R627" s="2"/>
       <c r="S627" s="2"/>
@@ -40447,22 +41545,54 @@
       <c r="Z627" s="2"/>
     </row>
     <row r="628" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A628" s="2"/>
-      <c r="B628" s="2"/>
-      <c r="C628" s="2"/>
-      <c r="D628" s="2"/>
-      <c r="E628" s="2"/>
-      <c r="F628" s="2"/>
-      <c r="G628" s="2"/>
-      <c r="H628" s="2"/>
-      <c r="I628" s="2"/>
-      <c r="J628" s="2"/>
-      <c r="K628" s="2"/>
-      <c r="L628" s="2"/>
-      <c r="M628" s="2"/>
-      <c r="N628" s="2"/>
-      <c r="O628" s="2"/>
-      <c r="P628" s="2"/>
+      <c r="A628" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B628" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C628" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D628" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E628" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F628" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G628" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H628" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I628" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J628" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K628" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L628" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M628" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N628" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O628" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P628" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q628" s="2"/>
       <c r="R628" s="2"/>
       <c r="S628" s="2"/>
@@ -40475,22 +41605,54 @@
       <c r="Z628" s="2"/>
     </row>
     <row r="629" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A629" s="2"/>
-      <c r="B629" s="2"/>
-      <c r="C629" s="2"/>
-      <c r="D629" s="2"/>
-      <c r="E629" s="2"/>
-      <c r="F629" s="2"/>
-      <c r="G629" s="2"/>
-      <c r="H629" s="2"/>
-      <c r="I629" s="2"/>
-      <c r="J629" s="2"/>
-      <c r="K629" s="2"/>
-      <c r="L629" s="2"/>
-      <c r="M629" s="2"/>
-      <c r="N629" s="2"/>
-      <c r="O629" s="2"/>
-      <c r="P629" s="2"/>
+      <c r="A629" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B629" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D629" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E629" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F629" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G629" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H629" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I629" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J629" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K629" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L629" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M629" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N629" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O629" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P629" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q629" s="2"/>
       <c r="R629" s="2"/>
       <c r="S629" s="2"/>
@@ -40503,22 +41665,52 @@
       <c r="Z629" s="2"/>
     </row>
     <row r="630" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A630" s="2"/>
-      <c r="B630" s="2"/>
-      <c r="C630" s="2"/>
-      <c r="D630" s="2"/>
-      <c r="E630" s="2"/>
-      <c r="F630" s="2"/>
-      <c r="G630" s="2"/>
-      <c r="H630" s="2"/>
-      <c r="I630" s="2"/>
-      <c r="J630" s="2"/>
-      <c r="K630" s="2"/>
-      <c r="L630" s="2"/>
-      <c r="M630" s="2"/>
-      <c r="N630" s="2"/>
-      <c r="O630" s="2"/>
-      <c r="P630" s="2"/>
+      <c r="A630" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B630" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C630" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D630" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F630" s="6"/>
+      <c r="G630" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H630" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I630" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J630" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K630" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L630" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M630" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N630" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O630" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P630" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q630" s="2"/>
       <c r="R630" s="2"/>
       <c r="S630" s="2"/>
@@ -40531,22 +41723,54 @@
       <c r="Z630" s="2"/>
     </row>
     <row r="631" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A631" s="2"/>
-      <c r="B631" s="2"/>
-      <c r="C631" s="2"/>
-      <c r="D631" s="2"/>
-      <c r="E631" s="2"/>
-      <c r="F631" s="2"/>
-      <c r="G631" s="2"/>
-      <c r="H631" s="2"/>
-      <c r="I631" s="2"/>
-      <c r="J631" s="2"/>
-      <c r="K631" s="2"/>
-      <c r="L631" s="2"/>
-      <c r="M631" s="2"/>
-      <c r="N631" s="2"/>
-      <c r="O631" s="2"/>
-      <c r="P631" s="2"/>
+      <c r="A631" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B631" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D631" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H631" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I631" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J631" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K631" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L631" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M631" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N631" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O631" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P631" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q631" s="2"/>
       <c r="R631" s="2"/>
       <c r="S631" s="2"/>
@@ -40559,22 +41783,54 @@
       <c r="Z631" s="2"/>
     </row>
     <row r="632" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A632" s="2"/>
-      <c r="B632" s="2"/>
-      <c r="C632" s="2"/>
-      <c r="D632" s="2"/>
-      <c r="E632" s="2"/>
-      <c r="F632" s="2"/>
-      <c r="G632" s="2"/>
-      <c r="H632" s="2"/>
-      <c r="I632" s="2"/>
-      <c r="J632" s="2"/>
-      <c r="K632" s="2"/>
-      <c r="L632" s="2"/>
-      <c r="M632" s="2"/>
-      <c r="N632" s="2"/>
-      <c r="O632" s="2"/>
-      <c r="P632" s="2"/>
+      <c r="A632" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B632" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C632" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D632" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H632" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I632" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J632" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K632" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L632" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M632" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N632" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O632" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P632" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q632" s="2"/>
       <c r="R632" s="2"/>
       <c r="S632" s="2"/>
@@ -40587,22 +41843,52 @@
       <c r="Z632" s="2"/>
     </row>
     <row r="633" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A633" s="2"/>
-      <c r="B633" s="2"/>
-      <c r="C633" s="2"/>
-      <c r="D633" s="2"/>
-      <c r="E633" s="2"/>
-      <c r="F633" s="2"/>
-      <c r="G633" s="2"/>
-      <c r="H633" s="2"/>
-      <c r="I633" s="2"/>
-      <c r="J633" s="2"/>
-      <c r="K633" s="2"/>
-      <c r="L633" s="2"/>
-      <c r="M633" s="2"/>
-      <c r="N633" s="2"/>
-      <c r="O633" s="2"/>
-      <c r="P633" s="2"/>
+      <c r="A633" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B633" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D633" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E633" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F633" s="6"/>
+      <c r="G633" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H633" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I633" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J633" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K633" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L633" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M633" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N633" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O633" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P633" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q633" s="2"/>
       <c r="R633" s="2"/>
       <c r="S633" s="2"/>
@@ -40615,22 +41901,54 @@
       <c r="Z633" s="2"/>
     </row>
     <row r="634" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A634" s="2"/>
-      <c r="B634" s="2"/>
-      <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
-      <c r="E634" s="2"/>
-      <c r="F634" s="2"/>
-      <c r="G634" s="2"/>
-      <c r="H634" s="2"/>
-      <c r="I634" s="2"/>
-      <c r="J634" s="2"/>
-      <c r="K634" s="2"/>
-      <c r="L634" s="2"/>
-      <c r="M634" s="2"/>
-      <c r="N634" s="2"/>
-      <c r="O634" s="2"/>
-      <c r="P634" s="2"/>
+      <c r="A634" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B634" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C634" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D634" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F634" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G634" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H634" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I634" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J634" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K634" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L634" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M634" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N634" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O634" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P634" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q634" s="2"/>
       <c r="R634" s="2"/>
       <c r="S634" s="2"/>
@@ -40643,22 +41961,54 @@
       <c r="Z634" s="2"/>
     </row>
     <row r="635" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A635" s="2"/>
-      <c r="B635" s="2"/>
-      <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
-      <c r="E635" s="2"/>
-      <c r="F635" s="2"/>
-      <c r="G635" s="2"/>
-      <c r="H635" s="2"/>
-      <c r="I635" s="2"/>
-      <c r="J635" s="2"/>
-      <c r="K635" s="2"/>
-      <c r="L635" s="2"/>
-      <c r="M635" s="2"/>
-      <c r="N635" s="2"/>
-      <c r="O635" s="2"/>
-      <c r="P635" s="2"/>
+      <c r="A635" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B635" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D635" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E635" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F635" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G635" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H635" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I635" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J635" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K635" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L635" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M635" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N635" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O635" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P635" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q635" s="2"/>
       <c r="R635" s="2"/>
       <c r="S635" s="2"/>
@@ -40671,22 +42021,54 @@
       <c r="Z635" s="2"/>
     </row>
     <row r="636" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A636" s="2"/>
-      <c r="B636" s="2"/>
-      <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
-      <c r="E636" s="2"/>
-      <c r="F636" s="2"/>
-      <c r="G636" s="2"/>
-      <c r="H636" s="2"/>
-      <c r="I636" s="2"/>
-      <c r="J636" s="2"/>
-      <c r="K636" s="2"/>
-      <c r="L636" s="2"/>
-      <c r="M636" s="2"/>
-      <c r="N636" s="2"/>
-      <c r="O636" s="2"/>
-      <c r="P636" s="2"/>
+      <c r="A636" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B636" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C636" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D636" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E636" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F636" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G636" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H636" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I636" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J636" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K636" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L636" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M636" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N636" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O636" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P636" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q636" s="2"/>
       <c r="R636" s="2"/>
       <c r="S636" s="2"/>
@@ -40699,22 +42081,54 @@
       <c r="Z636" s="2"/>
     </row>
     <row r="637" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A637" s="2"/>
-      <c r="B637" s="2"/>
-      <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
-      <c r="E637" s="2"/>
-      <c r="F637" s="2"/>
-      <c r="G637" s="2"/>
-      <c r="H637" s="2"/>
-      <c r="I637" s="2"/>
-      <c r="J637" s="2"/>
-      <c r="K637" s="2"/>
-      <c r="L637" s="2"/>
-      <c r="M637" s="2"/>
-      <c r="N637" s="2"/>
-      <c r="O637" s="2"/>
-      <c r="P637" s="2"/>
+      <c r="A637" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B637" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D637" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E637" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F637" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G637" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H637" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I637" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J637" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K637" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L637" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M637" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N637" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O637" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P637" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q637" s="2"/>
       <c r="R637" s="2"/>
       <c r="S637" s="2"/>
@@ -40727,22 +42141,54 @@
       <c r="Z637" s="2"/>
     </row>
     <row r="638" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A638" s="2"/>
-      <c r="B638" s="2"/>
-      <c r="C638" s="2"/>
-      <c r="D638" s="2"/>
-      <c r="E638" s="2"/>
-      <c r="F638" s="2"/>
-      <c r="G638" s="2"/>
-      <c r="H638" s="2"/>
-      <c r="I638" s="2"/>
-      <c r="J638" s="2"/>
-      <c r="K638" s="2"/>
-      <c r="L638" s="2"/>
-      <c r="M638" s="2"/>
-      <c r="N638" s="2"/>
-      <c r="O638" s="2"/>
-      <c r="P638" s="2"/>
+      <c r="A638" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B638" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C638" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D638" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E638" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F638" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G638" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H638" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I638" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J638" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="K638" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L638" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M638" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N638" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O638" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P638" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q638" s="2"/>
       <c r="R638" s="2"/>
       <c r="S638" s="2"/>
@@ -40755,22 +42201,54 @@
       <c r="Z638" s="2"/>
     </row>
     <row r="639" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A639" s="2"/>
-      <c r="B639" s="2"/>
-      <c r="C639" s="2"/>
-      <c r="D639" s="2"/>
-      <c r="E639" s="2"/>
-      <c r="F639" s="2"/>
-      <c r="G639" s="2"/>
-      <c r="H639" s="2"/>
-      <c r="I639" s="2"/>
-      <c r="J639" s="2"/>
-      <c r="K639" s="2"/>
-      <c r="L639" s="2"/>
-      <c r="M639" s="2"/>
-      <c r="N639" s="2"/>
-      <c r="O639" s="2"/>
-      <c r="P639" s="2"/>
+      <c r="A639" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B639" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D639" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E639" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F639" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G639" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H639" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I639" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J639" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="K639" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L639" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M639" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N639" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O639" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P639" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q639" s="2"/>
       <c r="R639" s="2"/>
       <c r="S639" s="2"/>
@@ -40783,22 +42261,54 @@
       <c r="Z639" s="2"/>
     </row>
     <row r="640" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A640" s="2"/>
-      <c r="B640" s="2"/>
-      <c r="C640" s="2"/>
-      <c r="D640" s="2"/>
-      <c r="E640" s="2"/>
-      <c r="F640" s="2"/>
-      <c r="G640" s="2"/>
-      <c r="H640" s="2"/>
-      <c r="I640" s="2"/>
-      <c r="J640" s="2"/>
-      <c r="K640" s="2"/>
-      <c r="L640" s="2"/>
-      <c r="M640" s="2"/>
-      <c r="N640" s="2"/>
-      <c r="O640" s="2"/>
-      <c r="P640" s="2"/>
+      <c r="A640" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B640" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C640" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D640" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E640" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F640" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G640" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H640" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I640" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J640" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K640" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L640" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M640" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N640" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O640" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P640" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q640" s="2"/>
       <c r="R640" s="2"/>
       <c r="S640" s="2"/>
@@ -40811,22 +42321,54 @@
       <c r="Z640" s="2"/>
     </row>
     <row r="641" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A641" s="2"/>
-      <c r="B641" s="2"/>
-      <c r="C641" s="2"/>
-      <c r="D641" s="2"/>
-      <c r="E641" s="2"/>
-      <c r="F641" s="2"/>
-      <c r="G641" s="2"/>
-      <c r="H641" s="2"/>
-      <c r="I641" s="2"/>
-      <c r="J641" s="2"/>
-      <c r="K641" s="2"/>
-      <c r="L641" s="2"/>
-      <c r="M641" s="2"/>
-      <c r="N641" s="2"/>
-      <c r="O641" s="2"/>
-      <c r="P641" s="2"/>
+      <c r="A641" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B641" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D641" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E641" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F641" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G641" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H641" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I641" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J641" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K641" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L641" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M641" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N641" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O641" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P641" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q641" s="2"/>
       <c r="R641" s="2"/>
       <c r="S641" s="2"/>
@@ -40839,22 +42381,54 @@
       <c r="Z641" s="2"/>
     </row>
     <row r="642" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A642" s="2"/>
-      <c r="B642" s="2"/>
-      <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
-      <c r="E642" s="2"/>
-      <c r="F642" s="2"/>
-      <c r="G642" s="2"/>
-      <c r="H642" s="2"/>
-      <c r="I642" s="2"/>
-      <c r="J642" s="2"/>
-      <c r="K642" s="2"/>
-      <c r="L642" s="2"/>
-      <c r="M642" s="2"/>
-      <c r="N642" s="2"/>
-      <c r="O642" s="2"/>
-      <c r="P642" s="2"/>
+      <c r="A642" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B642" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C642" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D642" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E642" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F642" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G642" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H642" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I642" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J642" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K642" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L642" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M642" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N642" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O642" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P642" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q642" s="2"/>
       <c r="R642" s="2"/>
       <c r="S642" s="2"/>
@@ -40867,22 +42441,54 @@
       <c r="Z642" s="2"/>
     </row>
     <row r="643" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A643" s="2"/>
-      <c r="B643" s="2"/>
-      <c r="C643" s="2"/>
-      <c r="D643" s="2"/>
-      <c r="E643" s="2"/>
-      <c r="F643" s="2"/>
-      <c r="G643" s="2"/>
-      <c r="H643" s="2"/>
-      <c r="I643" s="2"/>
-      <c r="J643" s="2"/>
-      <c r="K643" s="2"/>
-      <c r="L643" s="2"/>
-      <c r="M643" s="2"/>
-      <c r="N643" s="2"/>
-      <c r="O643" s="2"/>
-      <c r="P643" s="2"/>
+      <c r="A643" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B643" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D643" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E643" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F643" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G643" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H643" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I643" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="J643" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K643" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L643" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M643" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N643" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O643" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P643" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q643" s="2"/>
       <c r="R643" s="2"/>
       <c r="S643" s="2"/>
@@ -40895,22 +42501,54 @@
       <c r="Z643" s="2"/>
     </row>
     <row r="644" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A644" s="2"/>
-      <c r="B644" s="2"/>
-      <c r="C644" s="2"/>
-      <c r="D644" s="2"/>
-      <c r="E644" s="2"/>
-      <c r="F644" s="2"/>
-      <c r="G644" s="2"/>
-      <c r="H644" s="2"/>
-      <c r="I644" s="2"/>
-      <c r="J644" s="2"/>
-      <c r="K644" s="2"/>
-      <c r="L644" s="2"/>
-      <c r="M644" s="2"/>
-      <c r="N644" s="2"/>
-      <c r="O644" s="2"/>
-      <c r="P644" s="2"/>
+      <c r="A644" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B644" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D644" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E644" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F644" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G644" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H644" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I644" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J644" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K644" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L644" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M644" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N644" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O644" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P644" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q644" s="2"/>
       <c r="R644" s="2"/>
       <c r="S644" s="2"/>
@@ -40923,22 +42561,54 @@
       <c r="Z644" s="2"/>
     </row>
     <row r="645" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A645" s="2"/>
-      <c r="B645" s="2"/>
-      <c r="C645" s="2"/>
-      <c r="D645" s="2"/>
-      <c r="E645" s="2"/>
-      <c r="F645" s="2"/>
-      <c r="G645" s="2"/>
-      <c r="H645" s="2"/>
-      <c r="I645" s="2"/>
-      <c r="J645" s="2"/>
-      <c r="K645" s="2"/>
-      <c r="L645" s="2"/>
-      <c r="M645" s="2"/>
-      <c r="N645" s="2"/>
-      <c r="O645" s="2"/>
-      <c r="P645" s="2"/>
+      <c r="A645" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D645" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E645" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F645" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G645" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H645" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I645" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J645" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="K645" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P645" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q645" s="2"/>
       <c r="R645" s="2"/>
       <c r="S645" s="2"/>
@@ -40951,22 +42621,54 @@
       <c r="Z645" s="2"/>
     </row>
     <row r="646" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A646" s="2"/>
-      <c r="B646" s="2"/>
-      <c r="C646" s="2"/>
-      <c r="D646" s="2"/>
-      <c r="E646" s="2"/>
-      <c r="F646" s="2"/>
-      <c r="G646" s="2"/>
-      <c r="H646" s="2"/>
-      <c r="I646" s="2"/>
-      <c r="J646" s="2"/>
-      <c r="K646" s="2"/>
-      <c r="L646" s="2"/>
-      <c r="M646" s="2"/>
-      <c r="N646" s="2"/>
-      <c r="O646" s="2"/>
-      <c r="P646" s="2"/>
+      <c r="A646" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B646" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C646" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D646" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E646" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F646" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G646" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H646" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I646" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J646" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K646" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L646" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M646" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N646" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O646" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P646" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q646" s="2"/>
       <c r="R646" s="2"/>
       <c r="S646" s="2"/>
@@ -40979,22 +42681,54 @@
       <c r="Z646" s="2"/>
     </row>
     <row r="647" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A647" s="2"/>
-      <c r="B647" s="2"/>
-      <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
-      <c r="E647" s="2"/>
-      <c r="F647" s="2"/>
-      <c r="G647" s="2"/>
-      <c r="H647" s="2"/>
-      <c r="I647" s="2"/>
-      <c r="J647" s="2"/>
-      <c r="K647" s="2"/>
-      <c r="L647" s="2"/>
-      <c r="M647" s="2"/>
-      <c r="N647" s="2"/>
-      <c r="O647" s="2"/>
-      <c r="P647" s="2"/>
+      <c r="A647" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B647" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D647" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E647" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F647" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G647" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H647" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I647" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J647" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K647" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L647" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M647" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N647" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O647" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P647" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q647" s="2"/>
       <c r="R647" s="2"/>
       <c r="S647" s="2"/>
@@ -41007,22 +42741,54 @@
       <c r="Z647" s="2"/>
     </row>
     <row r="648" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A648" s="2"/>
-      <c r="B648" s="2"/>
-      <c r="C648" s="2"/>
-      <c r="D648" s="2"/>
-      <c r="E648" s="2"/>
-      <c r="F648" s="2"/>
-      <c r="G648" s="2"/>
-      <c r="H648" s="2"/>
-      <c r="I648" s="2"/>
-      <c r="J648" s="2"/>
-      <c r="K648" s="2"/>
-      <c r="L648" s="2"/>
-      <c r="M648" s="2"/>
-      <c r="N648" s="2"/>
-      <c r="O648" s="2"/>
-      <c r="P648" s="2"/>
+      <c r="A648" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B648" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D648" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E648" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F648" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G648" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H648" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I648" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J648" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K648" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L648" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M648" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N648" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O648" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P648" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q648" s="2"/>
       <c r="R648" s="2"/>
       <c r="S648" s="2"/>
@@ -41035,22 +42801,54 @@
       <c r="Z648" s="2"/>
     </row>
     <row r="649" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A649" s="2"/>
-      <c r="B649" s="2"/>
-      <c r="C649" s="2"/>
-      <c r="D649" s="2"/>
-      <c r="E649" s="2"/>
-      <c r="F649" s="2"/>
-      <c r="G649" s="2"/>
-      <c r="H649" s="2"/>
-      <c r="I649" s="2"/>
-      <c r="J649" s="2"/>
-      <c r="K649" s="2"/>
-      <c r="L649" s="2"/>
-      <c r="M649" s="2"/>
-      <c r="N649" s="2"/>
-      <c r="O649" s="2"/>
-      <c r="P649" s="2"/>
+      <c r="A649" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B649" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D649" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E649" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F649" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G649" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H649" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I649" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J649" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="K649" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L649" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M649" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N649" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O649" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P649" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q649" s="2"/>
       <c r="R649" s="2"/>
       <c r="S649" s="2"/>
@@ -41063,22 +42861,54 @@
       <c r="Z649" s="2"/>
     </row>
     <row r="650" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A650" s="2"/>
-      <c r="B650" s="2"/>
-      <c r="C650" s="2"/>
-      <c r="D650" s="2"/>
-      <c r="E650" s="2"/>
-      <c r="F650" s="2"/>
-      <c r="G650" s="2"/>
-      <c r="H650" s="2"/>
-      <c r="I650" s="2"/>
-      <c r="J650" s="2"/>
-      <c r="K650" s="2"/>
-      <c r="L650" s="2"/>
-      <c r="M650" s="2"/>
-      <c r="N650" s="2"/>
-      <c r="O650" s="2"/>
-      <c r="P650" s="2"/>
+      <c r="A650" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B650" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D650" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E650" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F650" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G650" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="H650" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I650" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J650" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K650" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L650" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M650" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N650" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O650" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P650" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q650" s="2"/>
       <c r="R650" s="2"/>
       <c r="S650" s="2"/>
@@ -41091,22 +42921,54 @@
       <c r="Z650" s="2"/>
     </row>
     <row r="651" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A651" s="2"/>
-      <c r="B651" s="2"/>
-      <c r="C651" s="2"/>
-      <c r="D651" s="2"/>
-      <c r="E651" s="2"/>
-      <c r="F651" s="2"/>
-      <c r="G651" s="2"/>
-      <c r="H651" s="2"/>
-      <c r="I651" s="2"/>
-      <c r="J651" s="2"/>
-      <c r="K651" s="2"/>
-      <c r="L651" s="2"/>
-      <c r="M651" s="2"/>
-      <c r="N651" s="2"/>
-      <c r="O651" s="2"/>
-      <c r="P651" s="2"/>
+      <c r="A651" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B651" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D651" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E651" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F651" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G651" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H651" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I651" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J651" s="5" t="s">
+        <v>1241</v>
+      </c>
+      <c r="K651" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L651" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M651" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N651" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O651" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P651" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q651" s="2"/>
       <c r="R651" s="2"/>
       <c r="S651" s="2"/>
@@ -41119,22 +42981,54 @@
       <c r="Z651" s="2"/>
     </row>
     <row r="652" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A652" s="2"/>
-      <c r="B652" s="2"/>
-      <c r="C652" s="2"/>
-      <c r="D652" s="2"/>
-      <c r="E652" s="2"/>
-      <c r="F652" s="2"/>
-      <c r="G652" s="2"/>
-      <c r="H652" s="2"/>
-      <c r="I652" s="2"/>
-      <c r="J652" s="2"/>
-      <c r="K652" s="2"/>
-      <c r="L652" s="2"/>
-      <c r="M652" s="2"/>
-      <c r="N652" s="2"/>
-      <c r="O652" s="2"/>
-      <c r="P652" s="2"/>
+      <c r="A652" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B652" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C652" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D652" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E652" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F652" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G652" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H652" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I652" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J652" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K652" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L652" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M652" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N652" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O652" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P652" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q652" s="2"/>
       <c r="R652" s="2"/>
       <c r="S652" s="2"/>
@@ -41147,22 +43041,54 @@
       <c r="Z652" s="2"/>
     </row>
     <row r="653" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A653" s="2"/>
-      <c r="B653" s="2"/>
-      <c r="C653" s="2"/>
-      <c r="D653" s="2"/>
-      <c r="E653" s="2"/>
-      <c r="F653" s="2"/>
-      <c r="G653" s="2"/>
-      <c r="H653" s="2"/>
-      <c r="I653" s="2"/>
-      <c r="J653" s="2"/>
-      <c r="K653" s="2"/>
-      <c r="L653" s="2"/>
-      <c r="M653" s="2"/>
-      <c r="N653" s="2"/>
-      <c r="O653" s="2"/>
-      <c r="P653" s="2"/>
+      <c r="A653" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B653" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E653" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F653" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G653" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H653" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I653" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J653" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K653" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L653" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M653" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N653" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O653" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P653" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q653" s="2"/>
       <c r="R653" s="2"/>
       <c r="S653" s="2"/>
@@ -41175,22 +43101,54 @@
       <c r="Z653" s="2"/>
     </row>
     <row r="654" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A654" s="2"/>
-      <c r="B654" s="2"/>
-      <c r="C654" s="2"/>
-      <c r="D654" s="2"/>
-      <c r="E654" s="2"/>
-      <c r="F654" s="2"/>
-      <c r="G654" s="2"/>
-      <c r="H654" s="2"/>
-      <c r="I654" s="2"/>
-      <c r="J654" s="2"/>
-      <c r="K654" s="2"/>
-      <c r="L654" s="2"/>
-      <c r="M654" s="2"/>
-      <c r="N654" s="2"/>
-      <c r="O654" s="2"/>
-      <c r="P654" s="2"/>
+      <c r="A654" s="5" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B654" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D654" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E654" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F654" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G654" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H654" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I654" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J654" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="K654" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L654" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M654" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N654" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O654" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P654" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q654" s="2"/>
       <c r="R654" s="2"/>
       <c r="S654" s="2"/>
@@ -41203,22 +43161,54 @@
       <c r="Z654" s="2"/>
     </row>
     <row r="655" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A655" s="2"/>
-      <c r="B655" s="2"/>
-      <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
-      <c r="E655" s="2"/>
-      <c r="F655" s="2"/>
-      <c r="G655" s="2"/>
-      <c r="H655" s="2"/>
-      <c r="I655" s="2"/>
-      <c r="J655" s="2"/>
-      <c r="K655" s="2"/>
-      <c r="L655" s="2"/>
-      <c r="M655" s="2"/>
-      <c r="N655" s="2"/>
-      <c r="O655" s="2"/>
-      <c r="P655" s="2"/>
+      <c r="A655" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B655" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D655" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E655" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F655" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G655" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H655" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I655" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J655" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K655" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L655" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M655" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N655" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O655" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P655" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q655" s="2"/>
       <c r="R655" s="2"/>
       <c r="S655" s="2"/>
@@ -41231,22 +43221,54 @@
       <c r="Z655" s="2"/>
     </row>
     <row r="656" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A656" s="2"/>
-      <c r="B656" s="2"/>
-      <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
-      <c r="E656" s="2"/>
-      <c r="F656" s="2"/>
-      <c r="G656" s="2"/>
-      <c r="H656" s="2"/>
-      <c r="I656" s="2"/>
-      <c r="J656" s="2"/>
-      <c r="K656" s="2"/>
-      <c r="L656" s="2"/>
-      <c r="M656" s="2"/>
-      <c r="N656" s="2"/>
-      <c r="O656" s="2"/>
-      <c r="P656" s="2"/>
+      <c r="A656" s="5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B656" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D656" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F656" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G656" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H656" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I656" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J656" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K656" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L656" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M656" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N656" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O656" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P656" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q656" s="2"/>
       <c r="R656" s="2"/>
       <c r="S656" s="2"/>
@@ -41259,22 +43281,54 @@
       <c r="Z656" s="2"/>
     </row>
     <row r="657" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A657" s="2"/>
-      <c r="B657" s="2"/>
-      <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
-      <c r="E657" s="2"/>
-      <c r="F657" s="2"/>
-      <c r="G657" s="2"/>
-      <c r="H657" s="2"/>
-      <c r="I657" s="2"/>
-      <c r="J657" s="2"/>
-      <c r="K657" s="2"/>
-      <c r="L657" s="2"/>
-      <c r="M657" s="2"/>
-      <c r="N657" s="2"/>
-      <c r="O657" s="2"/>
-      <c r="P657" s="2"/>
+      <c r="A657" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B657" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E657" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H657" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="I657" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J657" s="5" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K657" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L657" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M657" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N657" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O657" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P657" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q657" s="2"/>
       <c r="R657" s="2"/>
       <c r="S657" s="2"/>
@@ -41287,22 +43341,54 @@
       <c r="Z657" s="2"/>
     </row>
     <row r="658" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A658" s="2"/>
-      <c r="B658" s="2"/>
-      <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
-      <c r="E658" s="2"/>
-      <c r="F658" s="2"/>
-      <c r="G658" s="2"/>
-      <c r="H658" s="2"/>
-      <c r="I658" s="2"/>
-      <c r="J658" s="2"/>
-      <c r="K658" s="2"/>
-      <c r="L658" s="2"/>
-      <c r="M658" s="2"/>
-      <c r="N658" s="2"/>
-      <c r="O658" s="2"/>
-      <c r="P658" s="2"/>
+      <c r="A658" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B658" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D658" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E658" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H658" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I658" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J658" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K658" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L658" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M658" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N658" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O658" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P658" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q658" s="2"/>
       <c r="R658" s="2"/>
       <c r="S658" s="2"/>
@@ -41315,22 +43401,54 @@
       <c r="Z658" s="2"/>
     </row>
     <row r="659" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A659" s="2"/>
-      <c r="B659" s="2"/>
-      <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
-      <c r="E659" s="2"/>
-      <c r="F659" s="2"/>
-      <c r="G659" s="2"/>
-      <c r="H659" s="2"/>
-      <c r="I659" s="2"/>
-      <c r="J659" s="2"/>
-      <c r="K659" s="2"/>
-      <c r="L659" s="2"/>
-      <c r="M659" s="2"/>
-      <c r="N659" s="2"/>
-      <c r="O659" s="2"/>
-      <c r="P659" s="2"/>
+      <c r="A659" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B659" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D659" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E659" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F659" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G659" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H659" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I659" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J659" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K659" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L659" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M659" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N659" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O659" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P659" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q659" s="2"/>
       <c r="R659" s="2"/>
       <c r="S659" s="2"/>
@@ -41343,22 +43461,54 @@
       <c r="Z659" s="2"/>
     </row>
     <row r="660" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A660" s="2"/>
-      <c r="B660" s="2"/>
-      <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
-      <c r="E660" s="2"/>
-      <c r="F660" s="2"/>
-      <c r="G660" s="2"/>
-      <c r="H660" s="2"/>
-      <c r="I660" s="2"/>
-      <c r="J660" s="2"/>
-      <c r="K660" s="2"/>
-      <c r="L660" s="2"/>
-      <c r="M660" s="2"/>
-      <c r="N660" s="2"/>
-      <c r="O660" s="2"/>
-      <c r="P660" s="2"/>
+      <c r="A660" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B660" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D660" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E660" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F660" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G660" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H660" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I660" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J660" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K660" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L660" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M660" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N660" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O660" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P660" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q660" s="2"/>
       <c r="R660" s="2"/>
       <c r="S660" s="2"/>
@@ -41371,22 +43521,54 @@
       <c r="Z660" s="2"/>
     </row>
     <row r="661" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A661" s="2"/>
-      <c r="B661" s="2"/>
-      <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
-      <c r="E661" s="2"/>
-      <c r="F661" s="2"/>
-      <c r="G661" s="2"/>
-      <c r="H661" s="2"/>
-      <c r="I661" s="2"/>
-      <c r="J661" s="2"/>
-      <c r="K661" s="2"/>
-      <c r="L661" s="2"/>
-      <c r="M661" s="2"/>
-      <c r="N661" s="2"/>
-      <c r="O661" s="2"/>
-      <c r="P661" s="2"/>
+      <c r="A661" s="5" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B661" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D661" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E661" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F661" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G661" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H661" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I661" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J661" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K661" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L661" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M661" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N661" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O661" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P661" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q661" s="2"/>
       <c r="R661" s="2"/>
       <c r="S661" s="2"/>
@@ -41399,22 +43581,54 @@
       <c r="Z661" s="2"/>
     </row>
     <row r="662" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A662" s="2"/>
-      <c r="B662" s="2"/>
-      <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
-      <c r="E662" s="2"/>
-      <c r="F662" s="2"/>
-      <c r="G662" s="2"/>
-      <c r="H662" s="2"/>
-      <c r="I662" s="2"/>
-      <c r="J662" s="2"/>
-      <c r="K662" s="2"/>
-      <c r="L662" s="2"/>
-      <c r="M662" s="2"/>
-      <c r="N662" s="2"/>
-      <c r="O662" s="2"/>
-      <c r="P662" s="2"/>
+      <c r="A662" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B662" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C662" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D662" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E662" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F662" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G662" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H662" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I662" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J662" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K662" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P662" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q662" s="2"/>
       <c r="R662" s="2"/>
       <c r="S662" s="2"/>
@@ -41427,22 +43641,54 @@
       <c r="Z662" s="2"/>
     </row>
     <row r="663" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A663" s="2"/>
-      <c r="B663" s="2"/>
-      <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
-      <c r="E663" s="2"/>
-      <c r="F663" s="2"/>
-      <c r="G663" s="2"/>
-      <c r="H663" s="2"/>
-      <c r="I663" s="2"/>
-      <c r="J663" s="2"/>
-      <c r="K663" s="2"/>
-      <c r="L663" s="2"/>
-      <c r="M663" s="2"/>
-      <c r="N663" s="2"/>
-      <c r="O663" s="2"/>
-      <c r="P663" s="2"/>
+      <c r="A663" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B663" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D663" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E663" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F663" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G663" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H663" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I663" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J663" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K663" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L663" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M663" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N663" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O663" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P663" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q663" s="2"/>
       <c r="R663" s="2"/>
       <c r="S663" s="2"/>
@@ -41455,22 +43701,54 @@
       <c r="Z663" s="2"/>
     </row>
     <row r="664" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A664" s="2"/>
-      <c r="B664" s="2"/>
-      <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
-      <c r="E664" s="2"/>
-      <c r="F664" s="2"/>
-      <c r="G664" s="2"/>
-      <c r="H664" s="2"/>
-      <c r="I664" s="2"/>
-      <c r="J664" s="2"/>
-      <c r="K664" s="2"/>
-      <c r="L664" s="2"/>
-      <c r="M664" s="2"/>
-      <c r="N664" s="2"/>
-      <c r="O664" s="2"/>
-      <c r="P664" s="2"/>
+      <c r="A664" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="B664" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D664" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E664" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F664" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G664" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H664" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I664" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J664" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K664" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L664" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M664" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N664" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O664" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P664" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q664" s="2"/>
       <c r="R664" s="2"/>
       <c r="S664" s="2"/>
@@ -41483,22 +43761,54 @@
       <c r="Z664" s="2"/>
     </row>
     <row r="665" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A665" s="2"/>
-      <c r="B665" s="2"/>
-      <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
-      <c r="E665" s="2"/>
-      <c r="F665" s="2"/>
-      <c r="G665" s="2"/>
-      <c r="H665" s="2"/>
-      <c r="I665" s="2"/>
-      <c r="J665" s="2"/>
-      <c r="K665" s="2"/>
-      <c r="L665" s="2"/>
-      <c r="M665" s="2"/>
-      <c r="N665" s="2"/>
-      <c r="O665" s="2"/>
-      <c r="P665" s="2"/>
+      <c r="A665" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="B665" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D665" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E665" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F665" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G665" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H665" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I665" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J665" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="K665" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L665" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M665" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N665" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O665" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P665" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q665" s="2"/>
       <c r="R665" s="2"/>
       <c r="S665" s="2"/>
@@ -41511,22 +43821,54 @@
       <c r="Z665" s="2"/>
     </row>
     <row r="666" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A666" s="2"/>
-      <c r="B666" s="2"/>
-      <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
-      <c r="E666" s="2"/>
-      <c r="F666" s="2"/>
-      <c r="G666" s="2"/>
-      <c r="H666" s="2"/>
-      <c r="I666" s="2"/>
-      <c r="J666" s="2"/>
-      <c r="K666" s="2"/>
-      <c r="L666" s="2"/>
-      <c r="M666" s="2"/>
-      <c r="N666" s="2"/>
-      <c r="O666" s="2"/>
-      <c r="P666" s="2"/>
+      <c r="A666" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B666" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D666" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E666" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F666" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G666" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H666" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I666" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J666" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K666" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L666" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M666" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N666" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O666" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P666" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q666" s="2"/>
       <c r="R666" s="2"/>
       <c r="S666" s="2"/>
@@ -41539,22 +43881,54 @@
       <c r="Z666" s="2"/>
     </row>
     <row r="667" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A667" s="2"/>
-      <c r="B667" s="2"/>
-      <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
-      <c r="E667" s="2"/>
-      <c r="F667" s="2"/>
-      <c r="G667" s="2"/>
-      <c r="H667" s="2"/>
-      <c r="I667" s="2"/>
-      <c r="J667" s="2"/>
-      <c r="K667" s="2"/>
-      <c r="L667" s="2"/>
-      <c r="M667" s="2"/>
-      <c r="N667" s="2"/>
-      <c r="O667" s="2"/>
-      <c r="P667" s="2"/>
+      <c r="A667" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B667" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D667" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E667" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F667" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G667" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H667" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I667" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J667" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K667" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L667" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M667" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N667" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O667" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P667" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q667" s="2"/>
       <c r="R667" s="2"/>
       <c r="S667" s="2"/>
@@ -41567,22 +43941,54 @@
       <c r="Z667" s="2"/>
     </row>
     <row r="668" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A668" s="2"/>
-      <c r="B668" s="2"/>
-      <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
-      <c r="E668" s="2"/>
-      <c r="F668" s="2"/>
-      <c r="G668" s="2"/>
-      <c r="H668" s="2"/>
-      <c r="I668" s="2"/>
-      <c r="J668" s="2"/>
-      <c r="K668" s="2"/>
-      <c r="L668" s="2"/>
-      <c r="M668" s="2"/>
-      <c r="N668" s="2"/>
-      <c r="O668" s="2"/>
-      <c r="P668" s="2"/>
+      <c r="A668" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B668" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D668" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E668" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F668" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G668" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="H668" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I668" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J668" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="K668" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L668" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M668" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N668" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O668" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P668" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q668" s="2"/>
       <c r="R668" s="2"/>
       <c r="S668" s="2"/>
@@ -41595,22 +44001,54 @@
       <c r="Z668" s="2"/>
     </row>
     <row r="669" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A669" s="2"/>
-      <c r="B669" s="2"/>
-      <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
-      <c r="E669" s="2"/>
-      <c r="F669" s="2"/>
-      <c r="G669" s="2"/>
-      <c r="H669" s="2"/>
-      <c r="I669" s="2"/>
-      <c r="J669" s="2"/>
-      <c r="K669" s="2"/>
-      <c r="L669" s="2"/>
-      <c r="M669" s="2"/>
-      <c r="N669" s="2"/>
-      <c r="O669" s="2"/>
-      <c r="P669" s="2"/>
+      <c r="A669" s="5" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B669" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D669" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E669" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F669" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G669" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H669" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I669" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J669" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K669" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L669" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M669" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N669" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O669" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P669" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q669" s="2"/>
       <c r="R669" s="2"/>
       <c r="S669" s="2"/>
@@ -41623,22 +44061,54 @@
       <c r="Z669" s="2"/>
     </row>
     <row r="670" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A670" s="2"/>
-      <c r="B670" s="2"/>
-      <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
-      <c r="E670" s="2"/>
-      <c r="F670" s="2"/>
-      <c r="G670" s="2"/>
-      <c r="H670" s="2"/>
-      <c r="I670" s="2"/>
-      <c r="J670" s="2"/>
-      <c r="K670" s="2"/>
-      <c r="L670" s="2"/>
-      <c r="M670" s="2"/>
-      <c r="N670" s="2"/>
-      <c r="O670" s="2"/>
-      <c r="P670" s="2"/>
+      <c r="A670" s="5" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B670" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D670" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E670" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F670" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G670" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H670" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I670" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J670" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K670" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L670" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M670" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N670" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O670" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P670" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q670" s="2"/>
       <c r="R670" s="2"/>
       <c r="S670" s="2"/>
@@ -41651,22 +44121,54 @@
       <c r="Z670" s="2"/>
     </row>
     <row r="671" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A671" s="2"/>
-      <c r="B671" s="2"/>
-      <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
-      <c r="E671" s="2"/>
-      <c r="F671" s="2"/>
-      <c r="G671" s="2"/>
-      <c r="H671" s="2"/>
-      <c r="I671" s="2"/>
-      <c r="J671" s="2"/>
-      <c r="K671" s="2"/>
-      <c r="L671" s="2"/>
-      <c r="M671" s="2"/>
-      <c r="N671" s="2"/>
-      <c r="O671" s="2"/>
-      <c r="P671" s="2"/>
+      <c r="A671" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B671" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D671" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E671" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F671" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G671" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H671" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="I671" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J671" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K671" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L671" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M671" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N671" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O671" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P671" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q671" s="2"/>
       <c r="R671" s="2"/>
       <c r="S671" s="2"/>
@@ -41679,22 +44181,54 @@
       <c r="Z671" s="2"/>
     </row>
     <row r="672" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A672" s="2"/>
-      <c r="B672" s="2"/>
-      <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
-      <c r="E672" s="2"/>
-      <c r="F672" s="2"/>
-      <c r="G672" s="2"/>
-      <c r="H672" s="2"/>
-      <c r="I672" s="2"/>
-      <c r="J672" s="2"/>
-      <c r="K672" s="2"/>
-      <c r="L672" s="2"/>
-      <c r="M672" s="2"/>
-      <c r="N672" s="2"/>
-      <c r="O672" s="2"/>
-      <c r="P672" s="2"/>
+      <c r="A672" s="5" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B672" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D672" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E672" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F672" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G672" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H672" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I672" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J672" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K672" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L672" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M672" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N672" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O672" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P672" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q672" s="2"/>
       <c r="R672" s="2"/>
       <c r="S672" s="2"/>
@@ -41707,22 +44241,54 @@
       <c r="Z672" s="2"/>
     </row>
     <row r="673" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A673" s="2"/>
-      <c r="B673" s="2"/>
-      <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
-      <c r="E673" s="2"/>
-      <c r="F673" s="2"/>
-      <c r="G673" s="2"/>
-      <c r="H673" s="2"/>
-      <c r="I673" s="2"/>
-      <c r="J673" s="2"/>
-      <c r="K673" s="2"/>
-      <c r="L673" s="2"/>
-      <c r="M673" s="2"/>
-      <c r="N673" s="2"/>
-      <c r="O673" s="2"/>
-      <c r="P673" s="2"/>
+      <c r="A673" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B673" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D673" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E673" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F673" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G673" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H673" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I673" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J673" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K673" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L673" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M673" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N673" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O673" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P673" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q673" s="2"/>
       <c r="R673" s="2"/>
       <c r="S673" s="2"/>
@@ -41735,22 +44301,54 @@
       <c r="Z673" s="2"/>
     </row>
     <row r="674" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A674" s="2"/>
-      <c r="B674" s="2"/>
-      <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
-      <c r="E674" s="2"/>
-      <c r="F674" s="2"/>
-      <c r="G674" s="2"/>
-      <c r="H674" s="2"/>
-      <c r="I674" s="2"/>
-      <c r="J674" s="2"/>
-      <c r="K674" s="2"/>
-      <c r="L674" s="2"/>
-      <c r="M674" s="2"/>
-      <c r="N674" s="2"/>
-      <c r="O674" s="2"/>
-      <c r="P674" s="2"/>
+      <c r="A674" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B674" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D674" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E674" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F674" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G674" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H674" s="5" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I674" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J674" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K674" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L674" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M674" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N674" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O674" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P674" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q674" s="2"/>
       <c r="R674" s="2"/>
       <c r="S674" s="2"/>
@@ -41763,22 +44361,54 @@
       <c r="Z674" s="2"/>
     </row>
     <row r="675" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A675" s="2"/>
-      <c r="B675" s="2"/>
-      <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
-      <c r="E675" s="2"/>
-      <c r="F675" s="2"/>
-      <c r="G675" s="2"/>
-      <c r="H675" s="2"/>
-      <c r="I675" s="2"/>
-      <c r="J675" s="2"/>
-      <c r="K675" s="2"/>
-      <c r="L675" s="2"/>
-      <c r="M675" s="2"/>
-      <c r="N675" s="2"/>
-      <c r="O675" s="2"/>
-      <c r="P675" s="2"/>
+      <c r="A675" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B675" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D675" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F675" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G675" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H675" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I675" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J675" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="K675" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L675" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M675" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N675" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O675" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P675" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q675" s="2"/>
       <c r="R675" s="2"/>
       <c r="S675" s="2"/>
@@ -41791,22 +44421,54 @@
       <c r="Z675" s="2"/>
     </row>
     <row r="676" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A676" s="2"/>
-      <c r="B676" s="2"/>
-      <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
-      <c r="E676" s="2"/>
-      <c r="F676" s="2"/>
-      <c r="G676" s="2"/>
-      <c r="H676" s="2"/>
-      <c r="I676" s="2"/>
-      <c r="J676" s="2"/>
-      <c r="K676" s="2"/>
-      <c r="L676" s="2"/>
-      <c r="M676" s="2"/>
-      <c r="N676" s="2"/>
-      <c r="O676" s="2"/>
-      <c r="P676" s="2"/>
+      <c r="A676" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D676" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E676" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F676" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G676" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H676" s="5" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I676" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="J676" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="K676" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L676" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M676" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N676" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O676" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P676" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q676" s="2"/>
       <c r="R676" s="2"/>
       <c r="S676" s="2"/>
@@ -41819,22 +44481,54 @@
       <c r="Z676" s="2"/>
     </row>
     <row r="677" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A677" s="2"/>
-      <c r="B677" s="2"/>
-      <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
-      <c r="E677" s="2"/>
-      <c r="F677" s="2"/>
-      <c r="G677" s="2"/>
-      <c r="H677" s="2"/>
-      <c r="I677" s="2"/>
-      <c r="J677" s="2"/>
-      <c r="K677" s="2"/>
-      <c r="L677" s="2"/>
-      <c r="M677" s="2"/>
-      <c r="N677" s="2"/>
-      <c r="O677" s="2"/>
-      <c r="P677" s="2"/>
+      <c r="A677" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D677" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E677" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F677" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G677" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H677" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I677" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J677" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K677" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L677" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M677" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N677" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O677" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P677" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q677" s="2"/>
       <c r="R677" s="2"/>
       <c r="S677" s="2"/>
@@ -41847,22 +44541,54 @@
       <c r="Z677" s="2"/>
     </row>
     <row r="678" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A678" s="2"/>
-      <c r="B678" s="2"/>
-      <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
-      <c r="E678" s="2"/>
-      <c r="F678" s="2"/>
-      <c r="G678" s="2"/>
-      <c r="H678" s="2"/>
-      <c r="I678" s="2"/>
-      <c r="J678" s="2"/>
-      <c r="K678" s="2"/>
-      <c r="L678" s="2"/>
-      <c r="M678" s="2"/>
-      <c r="N678" s="2"/>
-      <c r="O678" s="2"/>
-      <c r="P678" s="2"/>
+      <c r="A678" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D678" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E678" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F678" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G678" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H678" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I678" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J678" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K678" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P678" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q678" s="2"/>
       <c r="R678" s="2"/>
       <c r="S678" s="2"/>
@@ -41875,22 +44601,52 @@
       <c r="Z678" s="2"/>
     </row>
     <row r="679" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A679" s="2"/>
-      <c r="B679" s="2"/>
-      <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
-      <c r="E679" s="2"/>
-      <c r="F679" s="2"/>
-      <c r="G679" s="2"/>
-      <c r="H679" s="2"/>
-      <c r="I679" s="2"/>
-      <c r="J679" s="2"/>
-      <c r="K679" s="2"/>
-      <c r="L679" s="2"/>
-      <c r="M679" s="2"/>
-      <c r="N679" s="2"/>
-      <c r="O679" s="2"/>
-      <c r="P679" s="2"/>
+      <c r="A679" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D679" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F679" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G679" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H679" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I679" s="6"/>
+      <c r="J679" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K679" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P679" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q679" s="2"/>
       <c r="R679" s="2"/>
       <c r="S679" s="2"/>
@@ -41903,22 +44659,52 @@
       <c r="Z679" s="2"/>
     </row>
     <row r="680" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A680" s="2"/>
-      <c r="B680" s="2"/>
-      <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
-      <c r="E680" s="2"/>
-      <c r="F680" s="2"/>
-      <c r="G680" s="2"/>
-      <c r="H680" s="2"/>
-      <c r="I680" s="2"/>
-      <c r="J680" s="2"/>
-      <c r="K680" s="2"/>
-      <c r="L680" s="2"/>
-      <c r="M680" s="2"/>
-      <c r="N680" s="2"/>
-      <c r="O680" s="2"/>
-      <c r="P680" s="2"/>
+      <c r="A680" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B680" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C680" s="6"/>
+      <c r="D680" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F680" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G680" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H680" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I680" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J680" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="K680" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P680" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q680" s="2"/>
       <c r="R680" s="2"/>
       <c r="S680" s="2"/>
@@ -41931,22 +44717,54 @@
       <c r="Z680" s="2"/>
     </row>
     <row r="681" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A681" s="2"/>
-      <c r="B681" s="2"/>
-      <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
-      <c r="E681" s="2"/>
-      <c r="F681" s="2"/>
-      <c r="G681" s="2"/>
-      <c r="H681" s="2"/>
-      <c r="I681" s="2"/>
-      <c r="J681" s="2"/>
-      <c r="K681" s="2"/>
-      <c r="L681" s="2"/>
-      <c r="M681" s="2"/>
-      <c r="N681" s="2"/>
-      <c r="O681" s="2"/>
-      <c r="P681" s="2"/>
+      <c r="A681" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D681" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E681" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F681" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G681" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H681" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I681" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J681" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="K681" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L681" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M681" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N681" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O681" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P681" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q681" s="2"/>
       <c r="R681" s="2"/>
       <c r="S681" s="2"/>
@@ -41959,22 +44777,54 @@
       <c r="Z681" s="2"/>
     </row>
     <row r="682" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A682" s="2"/>
-      <c r="B682" s="2"/>
-      <c r="C682" s="2"/>
-      <c r="D682" s="2"/>
-      <c r="E682" s="2"/>
-      <c r="F682" s="2"/>
-      <c r="G682" s="2"/>
-      <c r="H682" s="2"/>
-      <c r="I682" s="2"/>
-      <c r="J682" s="2"/>
-      <c r="K682" s="2"/>
-      <c r="L682" s="2"/>
-      <c r="M682" s="2"/>
-      <c r="N682" s="2"/>
-      <c r="O682" s="2"/>
-      <c r="P682" s="2"/>
+      <c r="A682" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D682" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E682" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F682" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G682" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H682" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="I682" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J682" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K682" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L682" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M682" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N682" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O682" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P682" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q682" s="2"/>
       <c r="R682" s="2"/>
       <c r="S682" s="2"/>
@@ -41987,22 +44837,54 @@
       <c r="Z682" s="2"/>
     </row>
     <row r="683" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A683" s="2"/>
-      <c r="B683" s="2"/>
-      <c r="C683" s="2"/>
-      <c r="D683" s="2"/>
-      <c r="E683" s="2"/>
-      <c r="F683" s="2"/>
-      <c r="G683" s="2"/>
-      <c r="H683" s="2"/>
-      <c r="I683" s="2"/>
-      <c r="J683" s="2"/>
-      <c r="K683" s="2"/>
-      <c r="L683" s="2"/>
-      <c r="M683" s="2"/>
-      <c r="N683" s="2"/>
-      <c r="O683" s="2"/>
-      <c r="P683" s="2"/>
+      <c r="A683" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D683" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E683" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H683" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I683" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J683" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K683" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L683" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M683" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N683" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O683" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P683" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q683" s="2"/>
       <c r="R683" s="2"/>
       <c r="S683" s="2"/>
@@ -42015,22 +44897,52 @@
       <c r="Z683" s="2"/>
     </row>
     <row r="684" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A684" s="2"/>
-      <c r="B684" s="2"/>
-      <c r="C684" s="2"/>
-      <c r="D684" s="2"/>
-      <c r="E684" s="2"/>
-      <c r="F684" s="2"/>
-      <c r="G684" s="2"/>
-      <c r="H684" s="2"/>
-      <c r="I684" s="2"/>
-      <c r="J684" s="2"/>
-      <c r="K684" s="2"/>
-      <c r="L684" s="2"/>
-      <c r="M684" s="2"/>
-      <c r="N684" s="2"/>
-      <c r="O684" s="2"/>
-      <c r="P684" s="2"/>
+      <c r="A684" s="5" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D684" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E684" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H684" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I684" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J684" s="6"/>
+      <c r="K684" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L684" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M684" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N684" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O684" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P684" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="Q684" s="2"/>
       <c r="R684" s="2"/>
       <c r="S684" s="2"/>
